--- a/new_tables.xlsx
+++ b/new_tables.xlsx
@@ -8,15 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/maxsalvatore/Documents/projects/covid/new_cancer/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{651E842F-76AD-8B4E-BF5E-41CA3C91FE54}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A8A2CFCF-2936-6044-A826-1C8C32713F3D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="14400" yWindow="500" windowWidth="14400" windowHeight="17500" xr2:uid="{23B5B348-4D99-B540-995F-50D24F235ACD}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="18000" activeTab="1" xr2:uid="{23B5B348-4D99-B540-995F-50D24F235ACD}"/>
   </bookViews>
   <sheets>
     <sheet name="table 1" sheetId="1" r:id="rId1"/>
     <sheet name="table 2" sheetId="2" r:id="rId2"/>
-    <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
-    <sheet name="Sheet4" sheetId="4" r:id="rId4"/>
+    <sheet name="table 3" sheetId="3" r:id="rId3"/>
+    <sheet name="table 4" sheetId="5" r:id="rId4"/>
+    <sheet name="table 5" sheetId="4" r:id="rId5"/>
   </sheets>
   <calcPr calcId="181029"/>
   <extLst>
@@ -38,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="894" uniqueCount="679">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="969" uniqueCount="719">
   <si>
     <t>Age</t>
   </si>
@@ -1857,27 +1858,6 @@
 Bolded point estimates represents statistical significance at the 95% confidence level.</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Helvetica Neue"/>
-        <family val="2"/>
-      </rPr>
-      <t>Table 2</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Helvetica Neue"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">. Logistic regression odds ratios (95% CI) for COVID-19 outcomes by cancer and by cancer treatment type, among patients with a cancer diagnosis. </t>
-    </r>
-  </si>
-  <si>
     <t>Melanoma</t>
   </si>
   <si>
@@ -2265,14 +2245,127 @@
     <t>1.47 (1.12, 1.92)</t>
   </si>
   <si>
+    <t>-</t>
+  </si>
+  <si>
+    <t>Outcome</t>
+  </si>
+  <si>
+    <t>Fully vaccinated and boosted</t>
+  </si>
+  <si>
+    <t>Hospitalization</t>
+  </si>
+  <si>
+    <t>ICU admission</t>
+  </si>
+  <si>
+    <t>Fatality</t>
+  </si>
+  <si>
+    <t>Cancer Status</t>
+  </si>
+  <si>
+    <t>Cancer</t>
+  </si>
+  <si>
+    <t>No cancer</t>
+  </si>
+  <si>
+    <t>OR (95% CI)</t>
+  </si>
+  <si>
+    <t>P-values</t>
+  </si>
+  <si>
+    <t>Interaction</t>
+  </si>
+  <si>
+    <t>0.48 (0.34, 0.65)</t>
+  </si>
+  <si>
+    <t>0.54 (0.38, 0.74)</t>
+  </si>
+  <si>
+    <t>0.14 (0.03, 0.40)</t>
+  </si>
+  <si>
+    <t>0.04 (0.00, 0.26)</t>
+  </si>
+  <si>
+    <t>0.57 (0.39, 0.80)</t>
+  </si>
+  <si>
+    <t>0.62 (0.42, 0.88)</t>
+  </si>
+  <si>
+    <t>0.37 (0.12, 0.83)</t>
+  </si>
+  <si>
+    <t>0.17 (0.02, 0.62)</t>
+  </si>
+  <si>
+    <t>0.31 (0.21, 0.43)</t>
+  </si>
+  <si>
+    <t>0.35 (0.24, 0.49)</t>
+  </si>
+  <si>
+    <t>0.29 (0.12, 0.58)</t>
+  </si>
+  <si>
+    <t>0.09 (0.01, 0.32)</t>
+  </si>
+  <si>
+    <t>&lt;0.01</t>
+  </si>
+  <si>
+    <t>0.35 (0.26, 0.46)</t>
+  </si>
+  <si>
+    <t>0.37 (0.27, 0.49)</t>
+  </si>
+  <si>
+    <t>0.35 (0.17, 0.62)</t>
+  </si>
+  <si>
+    <t>0.33 (0.17, 0.58)</t>
+  </si>
+  <si>
+    <t>0.61 (0.45, 0.80)</t>
+  </si>
+  <si>
+    <t>0.70 (0.52, 0.93)</t>
+  </si>
+  <si>
+    <t>0.51 (0.24, 0.92)</t>
+  </si>
+  <si>
+    <t>0.11 (0.02, 0.30)</t>
+  </si>
+  <si>
+    <t>0.76 (0.51, 1.09)</t>
+  </si>
+  <si>
+    <t>0.87 (0.58, 1.26)</t>
+  </si>
+  <si>
+    <t>0.27 (0.06, 0.77)</t>
+  </si>
+  <si>
+    <t>0.24 (0.05, 0.70)</t>
+  </si>
+  <si>
+    <t>0.80</t>
+  </si>
+  <si>
+    <t>0.01</t>
+  </si>
+  <si>
+    <t>Models were adjusted for age, race/ethnicity, sex, Disadvantage Index (quartile) and comorbidity score (i.e., adjustment set 3)</t>
+  </si>
+  <si>
     <r>
-      <rPr>
-        <b/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Helvetica Neue"/>
-        <family val="2"/>
-      </rPr>
       <t xml:space="preserve">Table 4. </t>
     </r>
     <r>
@@ -2282,11 +2375,50 @@
         <rFont val="Helvetica Neue"/>
         <family val="2"/>
       </rPr>
-      <t>Logistic regression odds ratios (95% CI) for COVID-19 susceptibility and outcomes by chemotherapy treatment (without hematologic malignancy patients)</t>
+      <t>Vaccination status odds ratios (95% CI) for COVID-19 outcomes by cancer status strata and p-value for vaccination status-cancer status interaction</t>
     </r>
   </si>
   <si>
-    <t>-</t>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Helvetica Neue"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">Table 5. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Helvetica Neue"/>
+        <family val="2"/>
+      </rPr>
+      <t>Logistic regression odds ratios (95% CI) for COVID-19 outcomes by chemotherapy treatment (without hematologic malignancy patients)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Helvetica Neue"/>
+        <family val="2"/>
+      </rPr>
+      <t>Table 2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Helvetica Neue"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">. Logistic regression odds ratios (95% CI) for COVID-19 outcomes by cancer and by cancer treatment type. </t>
+    </r>
   </si>
 </sst>
 </file>
@@ -2489,7 +2621,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="82">
+  <cellXfs count="92">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
@@ -2656,14 +2788,8 @@
     <xf numFmtId="0" fontId="11" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -2676,6 +2802,15 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -2691,6 +2826,31 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="11" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -3017,30 +3177,30 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:9" x14ac:dyDescent="0.15">
-      <c r="B2" s="76" t="s">
+      <c r="B2" s="74" t="s">
         <v>449</v>
       </c>
-      <c r="C2" s="76"/>
-      <c r="D2" s="76"/>
-      <c r="E2" s="76"/>
-      <c r="F2" s="76"/>
-      <c r="G2" s="76"/>
-      <c r="H2" s="76"/>
-      <c r="I2" s="76"/>
+      <c r="C2" s="74"/>
+      <c r="D2" s="74"/>
+      <c r="E2" s="74"/>
+      <c r="F2" s="74"/>
+      <c r="G2" s="74"/>
+      <c r="H2" s="74"/>
+      <c r="I2" s="74"/>
     </row>
     <row r="3" spans="2:9" x14ac:dyDescent="0.15">
       <c r="B3" s="4"/>
-      <c r="C3" s="73" t="s">
+      <c r="C3" s="71" t="s">
         <v>445</v>
       </c>
-      <c r="D3" s="73"/>
-      <c r="E3" s="73"/>
-      <c r="F3" s="74" t="s">
+      <c r="D3" s="71"/>
+      <c r="E3" s="71"/>
+      <c r="F3" s="72" t="s">
         <v>446</v>
       </c>
-      <c r="G3" s="75"/>
-      <c r="H3" s="75"/>
-      <c r="I3" s="75"/>
+      <c r="G3" s="73"/>
+      <c r="H3" s="73"/>
+      <c r="I3" s="73"/>
     </row>
     <row r="4" spans="2:9" x14ac:dyDescent="0.15">
       <c r="B4" s="4"/>
@@ -4807,10 +4967,10 @@
         <v>73</v>
       </c>
       <c r="C81" s="11" t="s">
-        <v>678</v>
+        <v>676</v>
       </c>
       <c r="D81" s="11" t="s">
-        <v>678</v>
+        <v>676</v>
       </c>
       <c r="E81" s="11" t="s">
         <v>395</v>
@@ -4833,10 +4993,10 @@
         <v>65</v>
       </c>
       <c r="C82" s="11" t="s">
-        <v>678</v>
+        <v>676</v>
       </c>
       <c r="D82" s="11" t="s">
-        <v>678</v>
+        <v>676</v>
       </c>
       <c r="E82" s="11" t="s">
         <v>397</v>
@@ -4859,10 +5019,10 @@
         <v>96</v>
       </c>
       <c r="C83" s="11" t="s">
-        <v>678</v>
+        <v>676</v>
       </c>
       <c r="D83" s="11" t="s">
-        <v>678</v>
+        <v>676</v>
       </c>
       <c r="E83" s="11" t="s">
         <v>402</v>
@@ -4897,10 +5057,10 @@
         <v>404</v>
       </c>
       <c r="C85" s="13" t="s">
-        <v>678</v>
+        <v>676</v>
       </c>
       <c r="D85" s="13" t="s">
-        <v>678</v>
+        <v>676</v>
       </c>
       <c r="E85" s="13" t="s">
         <v>405</v>
@@ -4923,10 +5083,10 @@
         <v>410</v>
       </c>
       <c r="C86" s="13" t="s">
-        <v>678</v>
+        <v>676</v>
       </c>
       <c r="D86" s="13" t="s">
-        <v>678</v>
+        <v>676</v>
       </c>
       <c r="E86" s="13" t="s">
         <v>411</v>
@@ -4949,10 +5109,10 @@
         <v>415</v>
       </c>
       <c r="C87" s="13" t="s">
-        <v>678</v>
+        <v>676</v>
       </c>
       <c r="D87" s="13" t="s">
-        <v>678</v>
+        <v>676</v>
       </c>
       <c r="E87" s="13" t="s">
         <v>416</v>
@@ -4975,10 +5135,10 @@
         <v>421</v>
       </c>
       <c r="C88" s="13" t="s">
-        <v>678</v>
+        <v>676</v>
       </c>
       <c r="D88" s="13" t="s">
-        <v>678</v>
+        <v>676</v>
       </c>
       <c r="E88" s="13" t="s">
         <v>422</v>
@@ -5001,10 +5161,10 @@
         <v>96</v>
       </c>
       <c r="C89" s="19" t="s">
-        <v>678</v>
+        <v>676</v>
       </c>
       <c r="D89" s="19" t="s">
-        <v>678</v>
+        <v>676</v>
       </c>
       <c r="E89" s="19" t="s">
         <v>427</v>
@@ -5023,75 +5183,75 @@
       </c>
     </row>
     <row r="90" spans="2:9" x14ac:dyDescent="0.15">
-      <c r="B90" s="70" t="s">
+      <c r="B90" s="75" t="s">
         <v>450</v>
       </c>
-      <c r="C90" s="70"/>
-      <c r="D90" s="70"/>
-      <c r="E90" s="70"/>
-      <c r="F90" s="70"/>
-      <c r="G90" s="70"/>
-      <c r="H90" s="70"/>
-      <c r="I90" s="70"/>
+      <c r="C90" s="75"/>
+      <c r="D90" s="75"/>
+      <c r="E90" s="75"/>
+      <c r="F90" s="75"/>
+      <c r="G90" s="75"/>
+      <c r="H90" s="75"/>
+      <c r="I90" s="75"/>
     </row>
     <row r="91" spans="2:9" ht="13" x14ac:dyDescent="0.15">
-      <c r="B91" s="71" t="s">
+      <c r="B91" s="76" t="s">
         <v>451</v>
       </c>
-      <c r="C91" s="71"/>
-      <c r="D91" s="71"/>
-      <c r="E91" s="71"/>
-      <c r="F91" s="71"/>
-      <c r="G91" s="71"/>
-      <c r="H91" s="71"/>
-      <c r="I91" s="71"/>
+      <c r="C91" s="76"/>
+      <c r="D91" s="76"/>
+      <c r="E91" s="76"/>
+      <c r="F91" s="76"/>
+      <c r="G91" s="76"/>
+      <c r="H91" s="76"/>
+      <c r="I91" s="76"/>
     </row>
     <row r="92" spans="2:9" ht="37" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B92" s="72" t="s">
+      <c r="B92" s="77" t="s">
         <v>452</v>
       </c>
-      <c r="C92" s="72"/>
-      <c r="D92" s="72"/>
-      <c r="E92" s="72"/>
-      <c r="F92" s="72"/>
-      <c r="G92" s="72"/>
-      <c r="H92" s="72"/>
-      <c r="I92" s="72"/>
+      <c r="C92" s="77"/>
+      <c r="D92" s="77"/>
+      <c r="E92" s="77"/>
+      <c r="F92" s="77"/>
+      <c r="G92" s="77"/>
+      <c r="H92" s="77"/>
+      <c r="I92" s="77"/>
     </row>
     <row r="93" spans="2:9" ht="26" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B93" s="72" t="s">
+      <c r="B93" s="77" t="s">
         <v>453</v>
       </c>
-      <c r="C93" s="72"/>
-      <c r="D93" s="72"/>
-      <c r="E93" s="72"/>
-      <c r="F93" s="72"/>
-      <c r="G93" s="72"/>
-      <c r="H93" s="72"/>
-      <c r="I93" s="72"/>
+      <c r="C93" s="77"/>
+      <c r="D93" s="77"/>
+      <c r="E93" s="77"/>
+      <c r="F93" s="77"/>
+      <c r="G93" s="77"/>
+      <c r="H93" s="77"/>
+      <c r="I93" s="77"/>
     </row>
     <row r="94" spans="2:9" ht="25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B94" s="72" t="s">
+      <c r="B94" s="77" t="s">
         <v>454</v>
       </c>
-      <c r="C94" s="72"/>
-      <c r="D94" s="72"/>
-      <c r="E94" s="72"/>
-      <c r="F94" s="72"/>
-      <c r="G94" s="72"/>
-      <c r="H94" s="72"/>
-      <c r="I94" s="72"/>
+      <c r="C94" s="77"/>
+      <c r="D94" s="77"/>
+      <c r="E94" s="77"/>
+      <c r="F94" s="77"/>
+      <c r="G94" s="77"/>
+      <c r="H94" s="77"/>
+      <c r="I94" s="77"/>
     </row>
   </sheetData>
   <mergeCells count="8">
+    <mergeCell ref="B92:I92"/>
+    <mergeCell ref="B93:I93"/>
+    <mergeCell ref="B94:I94"/>
     <mergeCell ref="C3:E3"/>
     <mergeCell ref="F3:I3"/>
     <mergeCell ref="B2:I2"/>
     <mergeCell ref="B90:I90"/>
     <mergeCell ref="B91:I91"/>
-    <mergeCell ref="B92:I92"/>
-    <mergeCell ref="B93:I93"/>
-    <mergeCell ref="B94:I94"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -5113,30 +5273,30 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:10" ht="32" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B2" s="79" t="s">
-        <v>554</v>
-      </c>
-      <c r="C2" s="79"/>
-      <c r="D2" s="79"/>
-      <c r="E2" s="79"/>
-      <c r="F2" s="79"/>
-      <c r="G2" s="79"/>
-      <c r="H2" s="79"/>
-      <c r="I2" s="79"/>
-      <c r="J2" s="79"/>
+      <c r="B2" s="80" t="s">
+        <v>718</v>
+      </c>
+      <c r="C2" s="80"/>
+      <c r="D2" s="80"/>
+      <c r="E2" s="80"/>
+      <c r="F2" s="80"/>
+      <c r="G2" s="80"/>
+      <c r="H2" s="80"/>
+      <c r="I2" s="80"/>
+      <c r="J2" s="80"/>
     </row>
     <row r="3" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="D3" s="77" t="s">
+      <c r="D3" s="78" t="s">
         <v>549</v>
       </c>
-      <c r="E3" s="78"/>
-      <c r="F3" s="78"/>
-      <c r="G3" s="78"/>
+      <c r="E3" s="79"/>
+      <c r="F3" s="79"/>
+      <c r="G3" s="79"/>
       <c r="H3" s="31"/>
-      <c r="I3" s="78" t="s">
+      <c r="I3" s="79" t="s">
         <v>552</v>
       </c>
-      <c r="J3" s="78"/>
+      <c r="J3" s="79"/>
     </row>
     <row r="4" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B4" s="32" t="s">
@@ -5750,17 +5910,17 @@
       </c>
     </row>
     <row r="29" spans="2:10" ht="65" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B29" s="80" t="s">
+      <c r="B29" s="81" t="s">
         <v>553</v>
       </c>
-      <c r="C29" s="81"/>
-      <c r="D29" s="81"/>
-      <c r="E29" s="81"/>
-      <c r="F29" s="81"/>
-      <c r="G29" s="81"/>
-      <c r="H29" s="81"/>
-      <c r="I29" s="81"/>
-      <c r="J29" s="81"/>
+      <c r="C29" s="82"/>
+      <c r="D29" s="82"/>
+      <c r="E29" s="82"/>
+      <c r="F29" s="82"/>
+      <c r="G29" s="82"/>
+      <c r="H29" s="82"/>
+      <c r="I29" s="82"/>
+      <c r="J29" s="82"/>
     </row>
   </sheetData>
   <mergeCells count="4">
@@ -5789,30 +5949,30 @@
   </cols>
   <sheetData>
     <row r="3" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="B3" s="79" t="s">
-        <v>657</v>
-      </c>
-      <c r="C3" s="79"/>
-      <c r="D3" s="79"/>
-      <c r="E3" s="79"/>
-      <c r="F3" s="79"/>
-      <c r="G3" s="79"/>
-      <c r="H3" s="79"/>
-      <c r="I3" s="79"/>
-      <c r="J3" s="79"/>
+      <c r="B3" s="80" t="s">
+        <v>656</v>
+      </c>
+      <c r="C3" s="80"/>
+      <c r="D3" s="80"/>
+      <c r="E3" s="80"/>
+      <c r="F3" s="80"/>
+      <c r="G3" s="80"/>
+      <c r="H3" s="80"/>
+      <c r="I3" s="80"/>
+      <c r="J3" s="80"/>
     </row>
     <row r="4" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="D4" s="77" t="s">
+      <c r="D4" s="78" t="s">
         <v>549</v>
       </c>
-      <c r="E4" s="78"/>
-      <c r="F4" s="78"/>
-      <c r="G4" s="78"/>
+      <c r="E4" s="79"/>
+      <c r="F4" s="79"/>
+      <c r="G4" s="79"/>
       <c r="H4" s="31"/>
-      <c r="I4" s="78" t="s">
+      <c r="I4" s="79" t="s">
         <v>552</v>
       </c>
-      <c r="J4" s="78"/>
+      <c r="J4" s="79"/>
     </row>
     <row r="5" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B5" s="32" t="s">
@@ -5843,7 +6003,7 @@
     </row>
     <row r="6" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B6" s="50" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="C6" s="41"/>
       <c r="D6" s="41"/>
@@ -5859,19 +6019,19 @@
         <v>544</v>
       </c>
       <c r="C7" s="38" t="s">
+        <v>554</v>
+      </c>
+      <c r="D7" s="52" t="s">
         <v>555</v>
       </c>
-      <c r="D7" s="52" t="s">
+      <c r="E7" s="3" t="s">
         <v>556</v>
       </c>
-      <c r="E7" s="3" t="s">
+      <c r="F7" s="3" t="s">
         <v>557</v>
       </c>
-      <c r="F7" s="3" t="s">
+      <c r="G7" s="3" t="s">
         <v>558</v>
-      </c>
-      <c r="G7" s="3" t="s">
-        <v>559</v>
       </c>
       <c r="H7" s="38"/>
       <c r="I7" s="39">
@@ -5886,19 +6046,19 @@
         <v>545</v>
       </c>
       <c r="C8" s="38" t="s">
+        <v>554</v>
+      </c>
+      <c r="D8" s="52" t="s">
         <v>555</v>
       </c>
-      <c r="D8" s="52" t="s">
+      <c r="E8" s="3" t="s">
         <v>556</v>
       </c>
-      <c r="E8" s="3" t="s">
-        <v>557</v>
-      </c>
       <c r="F8" s="3" t="s">
+        <v>559</v>
+      </c>
+      <c r="G8" s="3" t="s">
         <v>560</v>
-      </c>
-      <c r="G8" s="3" t="s">
-        <v>561</v>
       </c>
       <c r="H8" s="38"/>
       <c r="I8" s="39">
@@ -5913,19 +6073,19 @@
         <v>546</v>
       </c>
       <c r="C9" s="38" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="D9" s="52" t="s">
+        <v>561</v>
+      </c>
+      <c r="E9" s="3" t="s">
         <v>562</v>
       </c>
-      <c r="E9" s="3" t="s">
+      <c r="F9" s="3" t="s">
         <v>563</v>
       </c>
-      <c r="F9" s="3" t="s">
+      <c r="G9" s="3" t="s">
         <v>564</v>
-      </c>
-      <c r="G9" s="3" t="s">
-        <v>565</v>
       </c>
       <c r="H9" s="38"/>
       <c r="I9" s="39">
@@ -5940,19 +6100,19 @@
         <v>547</v>
       </c>
       <c r="C10" s="38" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="D10" s="52" t="s">
+        <v>565</v>
+      </c>
+      <c r="E10" s="3" t="s">
         <v>566</v>
       </c>
-      <c r="E10" s="3" t="s">
+      <c r="F10" s="3" t="s">
         <v>567</v>
       </c>
-      <c r="F10" s="3" t="s">
+      <c r="G10" s="3" t="s">
         <v>568</v>
-      </c>
-      <c r="G10" s="3" t="s">
-        <v>569</v>
       </c>
       <c r="H10" s="38"/>
       <c r="I10" s="39">
@@ -5967,19 +6127,19 @@
         <v>548</v>
       </c>
       <c r="C11" s="41" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="D11" s="53" t="s">
+        <v>569</v>
+      </c>
+      <c r="E11" s="42" t="s">
         <v>570</v>
       </c>
-      <c r="E11" s="42" t="s">
+      <c r="F11" s="42" t="s">
         <v>571</v>
       </c>
-      <c r="F11" s="42" t="s">
+      <c r="G11" s="42" t="s">
         <v>572</v>
-      </c>
-      <c r="G11" s="42" t="s">
-        <v>573</v>
       </c>
       <c r="H11" s="41"/>
       <c r="I11" s="43">
@@ -5991,7 +6151,7 @@
     </row>
     <row r="12" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B12" s="32" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" s="44"/>
@@ -6007,19 +6167,19 @@
         <v>544</v>
       </c>
       <c r="C13" s="56" t="s">
+        <v>573</v>
+      </c>
+      <c r="D13" s="59" t="s">
         <v>574</v>
       </c>
-      <c r="D13" s="59" t="s">
+      <c r="E13" s="60" t="s">
         <v>575</v>
       </c>
-      <c r="E13" s="60" t="s">
+      <c r="F13" s="60" t="s">
         <v>576</v>
       </c>
-      <c r="F13" s="60" t="s">
+      <c r="G13" s="60" t="s">
         <v>577</v>
-      </c>
-      <c r="G13" s="60" t="s">
-        <v>578</v>
       </c>
       <c r="I13" s="48">
         <v>2410</v>
@@ -6033,19 +6193,19 @@
         <v>545</v>
       </c>
       <c r="C14" s="56" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="D14" s="59" t="s">
+        <v>578</v>
+      </c>
+      <c r="E14" s="60" t="s">
+        <v>575</v>
+      </c>
+      <c r="F14" s="60" t="s">
         <v>579</v>
       </c>
-      <c r="E14" s="60" t="s">
-        <v>576</v>
-      </c>
-      <c r="F14" s="60" t="s">
+      <c r="G14" s="60" t="s">
         <v>580</v>
-      </c>
-      <c r="G14" s="60" t="s">
-        <v>581</v>
       </c>
       <c r="I14" s="48">
         <v>2410</v>
@@ -6059,19 +6219,19 @@
         <v>546</v>
       </c>
       <c r="C15" s="56" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="D15" s="59" t="s">
+        <v>581</v>
+      </c>
+      <c r="E15" s="60" t="s">
         <v>582</v>
       </c>
-      <c r="E15" s="60" t="s">
+      <c r="F15" s="60" t="s">
         <v>583</v>
       </c>
-      <c r="F15" s="60" t="s">
+      <c r="G15" s="60" t="s">
         <v>584</v>
-      </c>
-      <c r="G15" s="60" t="s">
-        <v>585</v>
       </c>
       <c r="I15" s="48">
         <v>2410</v>
@@ -6085,19 +6245,19 @@
         <v>547</v>
       </c>
       <c r="C16" s="56" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="D16" s="59" t="s">
+        <v>585</v>
+      </c>
+      <c r="E16" s="60" t="s">
         <v>586</v>
       </c>
-      <c r="E16" s="60" t="s">
+      <c r="F16" s="60" t="s">
         <v>587</v>
       </c>
-      <c r="F16" s="60" t="s">
+      <c r="G16" s="60" t="s">
         <v>588</v>
-      </c>
-      <c r="G16" s="60" t="s">
-        <v>589</v>
       </c>
       <c r="I16" s="48">
         <v>2154</v>
@@ -6111,19 +6271,19 @@
         <v>548</v>
       </c>
       <c r="C17" s="57" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="D17" s="61" t="s">
+        <v>589</v>
+      </c>
+      <c r="E17" s="62" t="s">
         <v>590</v>
       </c>
-      <c r="E17" s="62" t="s">
+      <c r="F17" s="62" t="s">
         <v>591</v>
       </c>
-      <c r="F17" s="62" t="s">
+      <c r="G17" s="62" t="s">
         <v>592</v>
-      </c>
-      <c r="G17" s="62" t="s">
-        <v>593</v>
       </c>
       <c r="H17" s="2"/>
       <c r="I17" s="45">
@@ -6135,7 +6295,7 @@
     </row>
     <row r="18" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B18" s="63" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="C18" s="41"/>
       <c r="D18" s="42"/>
@@ -6151,19 +6311,19 @@
         <v>544</v>
       </c>
       <c r="C19" s="64" t="s">
+        <v>593</v>
+      </c>
+      <c r="D19" s="65" t="s">
         <v>594</v>
       </c>
-      <c r="D19" s="65" t="s">
+      <c r="E19" s="66" t="s">
         <v>595</v>
       </c>
-      <c r="E19" s="66" t="s">
+      <c r="F19" s="66" t="s">
         <v>596</v>
       </c>
-      <c r="F19" s="66" t="s">
+      <c r="G19" s="66" t="s">
         <v>597</v>
-      </c>
-      <c r="G19" s="66" t="s">
-        <v>598</v>
       </c>
       <c r="H19" s="38"/>
       <c r="I19" s="39">
@@ -6178,19 +6338,19 @@
         <v>545</v>
       </c>
       <c r="C20" s="64" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="D20" s="65" t="s">
+        <v>598</v>
+      </c>
+      <c r="E20" s="66" t="s">
         <v>599</v>
       </c>
-      <c r="E20" s="66" t="s">
+      <c r="F20" s="66" t="s">
         <v>600</v>
       </c>
-      <c r="F20" s="66" t="s">
+      <c r="G20" s="66" t="s">
         <v>601</v>
-      </c>
-      <c r="G20" s="66" t="s">
-        <v>602</v>
       </c>
       <c r="H20" s="38"/>
       <c r="I20" s="39">
@@ -6205,19 +6365,19 @@
         <v>546</v>
       </c>
       <c r="C21" s="64" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="D21" s="65" t="s">
+        <v>602</v>
+      </c>
+      <c r="E21" s="66" t="s">
         <v>603</v>
       </c>
-      <c r="E21" s="66" t="s">
+      <c r="F21" s="66" t="s">
         <v>604</v>
       </c>
-      <c r="F21" s="66" t="s">
+      <c r="G21" s="66" t="s">
         <v>605</v>
-      </c>
-      <c r="G21" s="66" t="s">
-        <v>606</v>
       </c>
       <c r="H21" s="38"/>
       <c r="I21" s="39">
@@ -6232,19 +6392,19 @@
         <v>547</v>
       </c>
       <c r="C22" s="64" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="D22" s="65" t="s">
+        <v>606</v>
+      </c>
+      <c r="E22" s="66" t="s">
         <v>607</v>
       </c>
-      <c r="E22" s="66" t="s">
+      <c r="F22" s="66" t="s">
         <v>608</v>
       </c>
-      <c r="F22" s="66" t="s">
+      <c r="G22" s="66" t="s">
         <v>609</v>
-      </c>
-      <c r="G22" s="66" t="s">
-        <v>610</v>
       </c>
       <c r="H22" s="38"/>
       <c r="I22" s="39">
@@ -6259,19 +6419,19 @@
         <v>548</v>
       </c>
       <c r="C23" s="67" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="D23" s="68" t="s">
+        <v>610</v>
+      </c>
+      <c r="E23" s="69" t="s">
         <v>611</v>
       </c>
-      <c r="E23" s="69" t="s">
+      <c r="F23" s="69" t="s">
         <v>612</v>
       </c>
-      <c r="F23" s="69" t="s">
+      <c r="G23" s="69" t="s">
         <v>613</v>
-      </c>
-      <c r="G23" s="69" t="s">
-        <v>614</v>
       </c>
       <c r="H23" s="41"/>
       <c r="I23" s="43">
@@ -6283,7 +6443,7 @@
     </row>
     <row r="24" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B24" s="58" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" s="44"/>
@@ -6299,19 +6459,19 @@
         <v>544</v>
       </c>
       <c r="C25" s="56" t="s">
+        <v>614</v>
+      </c>
+      <c r="D25" s="59" t="s">
         <v>615</v>
       </c>
-      <c r="D25" s="59" t="s">
+      <c r="E25" s="60" t="s">
         <v>616</v>
       </c>
-      <c r="E25" s="60" t="s">
+      <c r="F25" s="60" t="s">
         <v>617</v>
       </c>
-      <c r="F25" s="60" t="s">
+      <c r="G25" s="60" t="s">
         <v>618</v>
-      </c>
-      <c r="G25" s="60" t="s">
-        <v>619</v>
       </c>
       <c r="I25" s="48">
         <v>1058</v>
@@ -6325,19 +6485,19 @@
         <v>545</v>
       </c>
       <c r="C26" s="56" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="D26" s="59" t="s">
+        <v>619</v>
+      </c>
+      <c r="E26" s="60" t="s">
         <v>620</v>
       </c>
-      <c r="E26" s="60" t="s">
+      <c r="F26" s="60" t="s">
         <v>621</v>
       </c>
-      <c r="F26" s="60" t="s">
+      <c r="G26" s="60" t="s">
         <v>622</v>
-      </c>
-      <c r="G26" s="60" t="s">
-        <v>623</v>
       </c>
       <c r="I26" s="48">
         <v>1058</v>
@@ -6351,19 +6511,19 @@
         <v>546</v>
       </c>
       <c r="C27" s="56" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="D27" s="59" t="s">
+        <v>623</v>
+      </c>
+      <c r="E27" s="60" t="s">
         <v>624</v>
       </c>
-      <c r="E27" s="60" t="s">
+      <c r="F27" s="60" t="s">
         <v>625</v>
       </c>
-      <c r="F27" s="60" t="s">
+      <c r="G27" s="60" t="s">
         <v>626</v>
-      </c>
-      <c r="G27" s="60" t="s">
-        <v>627</v>
       </c>
       <c r="I27" s="48">
         <v>1058</v>
@@ -6377,19 +6537,19 @@
         <v>547</v>
       </c>
       <c r="C28" s="56" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="D28" s="59" t="s">
+        <v>627</v>
+      </c>
+      <c r="E28" s="60" t="s">
         <v>628</v>
       </c>
-      <c r="E28" s="60" t="s">
+      <c r="F28" s="60" t="s">
         <v>629</v>
       </c>
-      <c r="F28" s="60" t="s">
+      <c r="G28" s="60" t="s">
         <v>630</v>
-      </c>
-      <c r="G28" s="60" t="s">
-        <v>631</v>
       </c>
       <c r="I28" s="48">
         <v>908</v>
@@ -6403,19 +6563,19 @@
         <v>548</v>
       </c>
       <c r="C29" s="57" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="D29" s="61" t="s">
+        <v>631</v>
+      </c>
+      <c r="E29" s="62" t="s">
         <v>632</v>
       </c>
-      <c r="E29" s="62" t="s">
+      <c r="F29" s="62" t="s">
         <v>633</v>
       </c>
-      <c r="F29" s="62" t="s">
+      <c r="G29" s="62" t="s">
         <v>634</v>
-      </c>
-      <c r="G29" s="62" t="s">
-        <v>635</v>
       </c>
       <c r="H29" s="2"/>
       <c r="I29" s="45">
@@ -6427,7 +6587,7 @@
     </row>
     <row r="30" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B30" s="63" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="C30" s="41"/>
       <c r="D30" s="42"/>
@@ -6443,19 +6603,19 @@
         <v>544</v>
       </c>
       <c r="C31" s="64" t="s">
+        <v>635</v>
+      </c>
+      <c r="D31" s="65" t="s">
         <v>636</v>
       </c>
-      <c r="D31" s="65" t="s">
+      <c r="E31" s="66" t="s">
         <v>637</v>
       </c>
-      <c r="E31" s="66" t="s">
+      <c r="F31" s="66" t="s">
         <v>638</v>
       </c>
-      <c r="F31" s="66" t="s">
+      <c r="G31" s="66" t="s">
         <v>639</v>
-      </c>
-      <c r="G31" s="66" t="s">
-        <v>640</v>
       </c>
       <c r="H31" s="38"/>
       <c r="I31" s="39">
@@ -6470,19 +6630,19 @@
         <v>545</v>
       </c>
       <c r="C32" s="64" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="D32" s="65" t="s">
+        <v>640</v>
+      </c>
+      <c r="E32" s="66" t="s">
         <v>641</v>
       </c>
-      <c r="E32" s="66" t="s">
+      <c r="F32" s="66" t="s">
         <v>642</v>
       </c>
-      <c r="F32" s="66" t="s">
+      <c r="G32" s="66" t="s">
         <v>643</v>
-      </c>
-      <c r="G32" s="66" t="s">
-        <v>644</v>
       </c>
       <c r="H32" s="38"/>
       <c r="I32" s="39">
@@ -6497,19 +6657,19 @@
         <v>546</v>
       </c>
       <c r="C33" s="64" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="D33" s="65" t="s">
+        <v>644</v>
+      </c>
+      <c r="E33" s="66" t="s">
         <v>645</v>
       </c>
-      <c r="E33" s="66" t="s">
+      <c r="F33" s="66" t="s">
         <v>646</v>
       </c>
-      <c r="F33" s="66" t="s">
+      <c r="G33" s="66" t="s">
         <v>647</v>
-      </c>
-      <c r="G33" s="66" t="s">
-        <v>648</v>
       </c>
       <c r="H33" s="38"/>
       <c r="I33" s="39">
@@ -6524,19 +6684,19 @@
         <v>547</v>
       </c>
       <c r="C34" s="64" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="D34" s="65" t="s">
+        <v>648</v>
+      </c>
+      <c r="E34" s="66" t="s">
         <v>649</v>
       </c>
-      <c r="E34" s="66" t="s">
+      <c r="F34" s="66" t="s">
         <v>650</v>
       </c>
-      <c r="F34" s="66" t="s">
+      <c r="G34" s="66" t="s">
         <v>651</v>
-      </c>
-      <c r="G34" s="66" t="s">
-        <v>652</v>
       </c>
       <c r="H34" s="38"/>
       <c r="I34" s="39">
@@ -6551,19 +6711,19 @@
         <v>548</v>
       </c>
       <c r="C35" s="67" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="D35" s="68" t="s">
+        <v>652</v>
+      </c>
+      <c r="E35" s="69" t="s">
         <v>653</v>
       </c>
-      <c r="E35" s="69" t="s">
+      <c r="F35" s="69" t="s">
         <v>654</v>
       </c>
-      <c r="F35" s="69" t="s">
+      <c r="G35" s="69" t="s">
         <v>655</v>
-      </c>
-      <c r="G35" s="69" t="s">
-        <v>656</v>
       </c>
       <c r="H35" s="41"/>
       <c r="I35" s="43">
@@ -6574,17 +6734,17 @@
       </c>
     </row>
     <row r="36" spans="2:10" ht="66" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B36" s="80" t="s">
-        <v>658</v>
-      </c>
-      <c r="C36" s="80"/>
-      <c r="D36" s="80"/>
-      <c r="E36" s="80"/>
-      <c r="F36" s="80"/>
-      <c r="G36" s="80"/>
-      <c r="H36" s="80"/>
-      <c r="I36" s="80"/>
-      <c r="J36" s="80"/>
+      <c r="B36" s="81" t="s">
+        <v>657</v>
+      </c>
+      <c r="C36" s="81"/>
+      <c r="D36" s="81"/>
+      <c r="E36" s="81"/>
+      <c r="F36" s="81"/>
+      <c r="G36" s="81"/>
+      <c r="H36" s="81"/>
+      <c r="I36" s="81"/>
+      <c r="J36" s="81"/>
     </row>
   </sheetData>
   <mergeCells count="4">
@@ -6598,6 +6758,506 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{457F983B-817E-E543-AB6D-7D7F0D0BC862}">
+  <dimension ref="B2:K22"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="10.83203125" style="1"/>
+    <col min="2" max="2" width="30.1640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="15.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="1.83203125" style="1" customWidth="1"/>
+    <col min="6" max="6" width="8.1640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.1640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.83203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="1.83203125" style="1" customWidth="1"/>
+    <col min="10" max="10" width="10.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="6.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="16384" width="10.83203125" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:11" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B2" s="91" t="s">
+        <v>716</v>
+      </c>
+      <c r="C2" s="91"/>
+      <c r="D2" s="91"/>
+      <c r="E2" s="91"/>
+      <c r="F2" s="91"/>
+      <c r="G2" s="91"/>
+      <c r="H2" s="91"/>
+      <c r="I2" s="91"/>
+      <c r="J2" s="91"/>
+      <c r="K2" s="91"/>
+    </row>
+    <row r="3" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="B3" s="31"/>
+      <c r="C3" s="79" t="s">
+        <v>682</v>
+      </c>
+      <c r="D3" s="79"/>
+      <c r="E3" s="83"/>
+      <c r="F3" s="83"/>
+      <c r="G3" s="83"/>
+      <c r="H3" s="83"/>
+    </row>
+    <row r="4" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="B4" s="31"/>
+      <c r="C4" s="83" t="s">
+        <v>683</v>
+      </c>
+      <c r="D4" s="83" t="s">
+        <v>684</v>
+      </c>
+      <c r="E4" s="83"/>
+      <c r="F4" s="79" t="s">
+        <v>686</v>
+      </c>
+      <c r="G4" s="79"/>
+      <c r="H4" s="79"/>
+      <c r="J4" s="79" t="s">
+        <v>552</v>
+      </c>
+      <c r="K4" s="79"/>
+    </row>
+    <row r="5" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="B5" s="32" t="s">
+        <v>677</v>
+      </c>
+      <c r="C5" s="70" t="s">
+        <v>685</v>
+      </c>
+      <c r="D5" s="70" t="s">
+        <v>685</v>
+      </c>
+      <c r="E5" s="70"/>
+      <c r="F5" s="70" t="s">
+        <v>683</v>
+      </c>
+      <c r="G5" s="70" t="s">
+        <v>684</v>
+      </c>
+      <c r="H5" s="70" t="s">
+        <v>687</v>
+      </c>
+      <c r="I5" s="2"/>
+      <c r="J5" s="70" t="s">
+        <v>677</v>
+      </c>
+      <c r="K5" s="70" t="s">
+        <v>551</v>
+      </c>
+    </row>
+    <row r="6" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="B6" s="50" t="s">
+        <v>437</v>
+      </c>
+      <c r="C6" s="41"/>
+      <c r="D6" s="41"/>
+      <c r="E6" s="41"/>
+      <c r="F6" s="41"/>
+      <c r="G6" s="41"/>
+      <c r="H6" s="41"/>
+      <c r="I6" s="41"/>
+      <c r="J6" s="42"/>
+      <c r="K6" s="42"/>
+    </row>
+    <row r="7" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="B7" s="37" t="s">
+        <v>415</v>
+      </c>
+      <c r="C7" s="38" t="s">
+        <v>709</v>
+      </c>
+      <c r="D7" s="38" t="s">
+        <v>692</v>
+      </c>
+      <c r="E7" s="38"/>
+      <c r="F7" s="3">
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="G7" s="87" t="s">
+        <v>700</v>
+      </c>
+      <c r="H7" s="3">
+        <v>0.28999999999999998</v>
+      </c>
+      <c r="I7" s="38"/>
+      <c r="J7" s="3">
+        <v>64</v>
+      </c>
+      <c r="K7" s="39">
+        <v>2806</v>
+      </c>
+    </row>
+    <row r="8" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="B8" s="37" t="s">
+        <v>410</v>
+      </c>
+      <c r="C8" s="38" t="s">
+        <v>705</v>
+      </c>
+      <c r="D8" s="38" t="s">
+        <v>688</v>
+      </c>
+      <c r="E8" s="38"/>
+      <c r="F8" s="3" t="s">
+        <v>700</v>
+      </c>
+      <c r="G8" s="3" t="s">
+        <v>700</v>
+      </c>
+      <c r="H8" s="3">
+        <v>0.27</v>
+      </c>
+      <c r="I8" s="38"/>
+      <c r="J8" s="3">
+        <v>96</v>
+      </c>
+      <c r="K8" s="39">
+        <v>2806</v>
+      </c>
+    </row>
+    <row r="9" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="B9" s="40" t="s">
+        <v>678</v>
+      </c>
+      <c r="C9" s="41" t="s">
+        <v>701</v>
+      </c>
+      <c r="D9" s="41" t="s">
+        <v>696</v>
+      </c>
+      <c r="E9" s="41"/>
+      <c r="F9" s="42" t="s">
+        <v>700</v>
+      </c>
+      <c r="G9" s="42" t="s">
+        <v>700</v>
+      </c>
+      <c r="H9" s="42">
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="I9" s="41"/>
+      <c r="J9" s="42">
+        <v>88</v>
+      </c>
+      <c r="K9" s="43">
+        <v>2806</v>
+      </c>
+    </row>
+    <row r="10" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="B10" s="84" t="s">
+        <v>679</v>
+      </c>
+      <c r="C10" s="2"/>
+      <c r="D10" s="2"/>
+      <c r="E10" s="2"/>
+      <c r="F10" s="2"/>
+      <c r="G10" s="2"/>
+      <c r="H10" s="2"/>
+      <c r="I10" s="2"/>
+      <c r="J10" s="44"/>
+      <c r="K10" s="44"/>
+    </row>
+    <row r="11" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="B11" s="46" t="s">
+        <v>415</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>710</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>693</v>
+      </c>
+      <c r="F11" s="47">
+        <v>0.46</v>
+      </c>
+      <c r="G11" s="47" t="s">
+        <v>700</v>
+      </c>
+      <c r="H11" s="47">
+        <v>0.22</v>
+      </c>
+      <c r="J11" s="47">
+        <v>62</v>
+      </c>
+      <c r="K11" s="48">
+        <v>2531</v>
+      </c>
+    </row>
+    <row r="12" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="B12" s="46" t="s">
+        <v>410</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>706</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>689</v>
+      </c>
+      <c r="F12" s="88" t="s">
+        <v>714</v>
+      </c>
+      <c r="G12" s="47" t="s">
+        <v>700</v>
+      </c>
+      <c r="H12" s="47">
+        <v>0.24</v>
+      </c>
+      <c r="J12" s="47">
+        <v>94</v>
+      </c>
+      <c r="K12" s="48">
+        <v>2531</v>
+      </c>
+    </row>
+    <row r="13" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="B13" s="85" t="s">
+        <v>678</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>702</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>697</v>
+      </c>
+      <c r="E13" s="86"/>
+      <c r="F13" s="89" t="s">
+        <v>700</v>
+      </c>
+      <c r="G13" s="89" t="s">
+        <v>700</v>
+      </c>
+      <c r="H13" s="90" t="s">
+        <v>713</v>
+      </c>
+      <c r="I13" s="2"/>
+      <c r="J13" s="44">
+        <v>82</v>
+      </c>
+      <c r="K13" s="45">
+        <v>2531</v>
+      </c>
+    </row>
+    <row r="14" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="B14" s="50" t="s">
+        <v>680</v>
+      </c>
+      <c r="C14" s="41"/>
+      <c r="D14" s="41"/>
+      <c r="E14" s="41"/>
+      <c r="F14" s="41"/>
+      <c r="G14" s="41"/>
+      <c r="H14" s="41"/>
+      <c r="I14" s="41"/>
+      <c r="J14" s="42"/>
+      <c r="K14" s="42"/>
+    </row>
+    <row r="15" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="B15" s="37" t="s">
+        <v>415</v>
+      </c>
+      <c r="C15" s="38" t="s">
+        <v>711</v>
+      </c>
+      <c r="D15" s="38" t="s">
+        <v>694</v>
+      </c>
+      <c r="E15" s="38"/>
+      <c r="F15" s="3">
+        <v>0.01</v>
+      </c>
+      <c r="G15" s="3">
+        <v>0.01</v>
+      </c>
+      <c r="H15" s="3">
+        <v>0.69</v>
+      </c>
+      <c r="I15" s="38"/>
+      <c r="J15" s="3">
+        <v>6</v>
+      </c>
+      <c r="K15" s="3">
+        <v>602</v>
+      </c>
+    </row>
+    <row r="16" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="B16" s="37" t="s">
+        <v>410</v>
+      </c>
+      <c r="C16" s="38" t="s">
+        <v>707</v>
+      </c>
+      <c r="D16" s="38" t="s">
+        <v>690</v>
+      </c>
+      <c r="E16" s="38"/>
+      <c r="F16" s="3">
+        <v>0.02</v>
+      </c>
+      <c r="G16" s="3" t="s">
+        <v>700</v>
+      </c>
+      <c r="H16" s="3">
+        <v>0.52</v>
+      </c>
+      <c r="I16" s="38"/>
+      <c r="J16" s="3">
+        <v>11</v>
+      </c>
+      <c r="K16" s="3">
+        <v>602</v>
+      </c>
+    </row>
+    <row r="17" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="B17" s="40" t="s">
+        <v>678</v>
+      </c>
+      <c r="C17" s="41" t="s">
+        <v>703</v>
+      </c>
+      <c r="D17" s="41" t="s">
+        <v>698</v>
+      </c>
+      <c r="E17" s="41"/>
+      <c r="F17" s="42" t="s">
+        <v>700</v>
+      </c>
+      <c r="G17" s="42" t="s">
+        <v>700</v>
+      </c>
+      <c r="H17" s="42">
+        <v>0.73</v>
+      </c>
+      <c r="I17" s="41"/>
+      <c r="J17" s="42">
+        <v>16</v>
+      </c>
+      <c r="K17" s="42">
+        <v>602</v>
+      </c>
+    </row>
+    <row r="18" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="B18" s="32" t="s">
+        <v>681</v>
+      </c>
+      <c r="C18" s="2"/>
+      <c r="D18" s="2"/>
+      <c r="E18" s="2"/>
+      <c r="F18" s="44"/>
+      <c r="G18" s="44"/>
+      <c r="H18" s="44"/>
+      <c r="I18" s="2"/>
+      <c r="J18" s="44"/>
+      <c r="K18" s="44"/>
+    </row>
+    <row r="19" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="B19" s="46" t="s">
+        <v>415</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>712</v>
+      </c>
+      <c r="D19" s="1" t="s">
+        <v>695</v>
+      </c>
+      <c r="F19" s="47" t="s">
+        <v>700</v>
+      </c>
+      <c r="G19" s="47" t="s">
+        <v>700</v>
+      </c>
+      <c r="H19" s="47">
+        <v>0.74</v>
+      </c>
+      <c r="J19" s="47">
+        <v>3</v>
+      </c>
+      <c r="K19" s="47">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="20" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="B20" s="46" t="s">
+        <v>410</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>708</v>
+      </c>
+      <c r="D20" s="1" t="s">
+        <v>691</v>
+      </c>
+      <c r="F20" s="47" t="s">
+        <v>700</v>
+      </c>
+      <c r="G20" s="47" t="s">
+        <v>700</v>
+      </c>
+      <c r="H20" s="47">
+        <v>0.47</v>
+      </c>
+      <c r="J20" s="47">
+        <v>2</v>
+      </c>
+      <c r="K20" s="47">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="21" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="B21" s="49" t="s">
+        <v>678</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>704</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>699</v>
+      </c>
+      <c r="E21" s="2"/>
+      <c r="F21" s="44" t="s">
+        <v>700</v>
+      </c>
+      <c r="G21" s="44" t="s">
+        <v>700</v>
+      </c>
+      <c r="H21" s="44">
+        <v>0.08</v>
+      </c>
+      <c r="I21" s="2"/>
+      <c r="J21" s="44">
+        <v>12</v>
+      </c>
+      <c r="K21" s="44">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="22" spans="2:11" ht="32" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B22" s="81" t="s">
+        <v>715</v>
+      </c>
+      <c r="C22" s="81"/>
+      <c r="D22" s="81"/>
+      <c r="E22" s="81"/>
+      <c r="F22" s="81"/>
+      <c r="G22" s="81"/>
+      <c r="H22" s="81"/>
+      <c r="I22" s="81"/>
+      <c r="J22" s="81"/>
+      <c r="K22" s="81"/>
+    </row>
+  </sheetData>
+  <mergeCells count="5">
+    <mergeCell ref="B22:K22"/>
+    <mergeCell ref="C3:D3"/>
+    <mergeCell ref="F4:H4"/>
+    <mergeCell ref="J4:K4"/>
+    <mergeCell ref="B2:K2"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{628CFEDD-ACB0-D742-8DB5-0C1AC5AF6C14}">
   <dimension ref="B2:J11"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
@@ -6609,32 +7269,32 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:10" ht="32" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B2" s="79" t="s">
-        <v>677</v>
-      </c>
-      <c r="C2" s="79"/>
-      <c r="D2" s="79"/>
-      <c r="E2" s="79"/>
-      <c r="F2" s="79"/>
-      <c r="G2" s="79"/>
-      <c r="H2" s="79"/>
-      <c r="I2" s="79"/>
-      <c r="J2" s="79"/>
+      <c r="B2" s="80" t="s">
+        <v>717</v>
+      </c>
+      <c r="C2" s="80"/>
+      <c r="D2" s="80"/>
+      <c r="E2" s="80"/>
+      <c r="F2" s="80"/>
+      <c r="G2" s="80"/>
+      <c r="H2" s="80"/>
+      <c r="I2" s="80"/>
+      <c r="J2" s="80"/>
     </row>
     <row r="3" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B3" s="1"/>
       <c r="C3" s="1"/>
-      <c r="D3" s="77" t="s">
+      <c r="D3" s="78" t="s">
         <v>549</v>
       </c>
-      <c r="E3" s="78"/>
-      <c r="F3" s="78"/>
-      <c r="G3" s="78"/>
+      <c r="E3" s="79"/>
+      <c r="F3" s="79"/>
+      <c r="G3" s="79"/>
       <c r="H3" s="31"/>
-      <c r="I3" s="78" t="s">
+      <c r="I3" s="79" t="s">
         <v>552</v>
       </c>
-      <c r="J3" s="78"/>
+      <c r="J3" s="79"/>
     </row>
     <row r="4" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B4" s="32" t="s">
@@ -6684,16 +7344,16 @@
         <v>462</v>
       </c>
       <c r="D6" s="52" t="s">
+        <v>658</v>
+      </c>
+      <c r="E6" s="3" t="s">
         <v>659</v>
       </c>
-      <c r="E6" s="3" t="s">
+      <c r="F6" s="3" t="s">
         <v>660</v>
       </c>
-      <c r="F6" s="3" t="s">
+      <c r="G6" s="3" t="s">
         <v>661</v>
-      </c>
-      <c r="G6" s="3" t="s">
-        <v>662</v>
       </c>
       <c r="H6" s="38"/>
       <c r="I6" s="39">
@@ -6711,16 +7371,16 @@
         <v>462</v>
       </c>
       <c r="D7" s="52" t="s">
+        <v>658</v>
+      </c>
+      <c r="E7" s="3" t="s">
         <v>659</v>
       </c>
-      <c r="E7" s="3" t="s">
-        <v>660</v>
-      </c>
       <c r="F7" s="3" t="s">
+        <v>662</v>
+      </c>
+      <c r="G7" s="3" t="s">
         <v>663</v>
-      </c>
-      <c r="G7" s="3" t="s">
-        <v>664</v>
       </c>
       <c r="H7" s="38"/>
       <c r="I7" s="39">
@@ -6738,16 +7398,16 @@
         <v>462</v>
       </c>
       <c r="D8" s="52" t="s">
+        <v>664</v>
+      </c>
+      <c r="E8" s="3" t="s">
         <v>665</v>
       </c>
-      <c r="E8" s="3" t="s">
+      <c r="F8" s="3" t="s">
         <v>666</v>
       </c>
-      <c r="F8" s="3" t="s">
+      <c r="G8" s="3" t="s">
         <v>667</v>
-      </c>
-      <c r="G8" s="3" t="s">
-        <v>668</v>
       </c>
       <c r="H8" s="38"/>
       <c r="I8" s="39">
@@ -6765,16 +7425,16 @@
         <v>462</v>
       </c>
       <c r="D9" s="52" t="s">
+        <v>668</v>
+      </c>
+      <c r="E9" s="3" t="s">
         <v>669</v>
       </c>
-      <c r="E9" s="3" t="s">
+      <c r="F9" s="3" t="s">
         <v>670</v>
       </c>
-      <c r="F9" s="3" t="s">
+      <c r="G9" s="3" t="s">
         <v>671</v>
-      </c>
-      <c r="G9" s="3" t="s">
-        <v>672</v>
       </c>
       <c r="H9" s="38"/>
       <c r="I9" s="39">
@@ -6792,16 +7452,16 @@
         <v>462</v>
       </c>
       <c r="D10" s="53" t="s">
+        <v>672</v>
+      </c>
+      <c r="E10" s="42" t="s">
         <v>673</v>
       </c>
-      <c r="E10" s="42" t="s">
+      <c r="F10" s="42" t="s">
         <v>674</v>
       </c>
-      <c r="F10" s="42" t="s">
+      <c r="G10" s="42" t="s">
         <v>675</v>
-      </c>
-      <c r="G10" s="42" t="s">
-        <v>676</v>
       </c>
       <c r="H10" s="41"/>
       <c r="I10" s="43">
@@ -6812,17 +7472,17 @@
       </c>
     </row>
     <row r="11" spans="2:10" ht="66" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B11" s="80" t="s">
+      <c r="B11" s="81" t="s">
         <v>553</v>
       </c>
-      <c r="C11" s="81"/>
-      <c r="D11" s="81"/>
-      <c r="E11" s="81"/>
-      <c r="F11" s="81"/>
-      <c r="G11" s="81"/>
-      <c r="H11" s="81"/>
-      <c r="I11" s="81"/>
-      <c r="J11" s="81"/>
+      <c r="C11" s="82"/>
+      <c r="D11" s="82"/>
+      <c r="E11" s="82"/>
+      <c r="F11" s="82"/>
+      <c r="G11" s="82"/>
+      <c r="H11" s="82"/>
+      <c r="I11" s="82"/>
+      <c r="J11" s="82"/>
     </row>
   </sheetData>
   <mergeCells count="4">

--- a/new_tables.xlsx
+++ b/new_tables.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/maxsalvatore/Documents/projects/covid/new_cancer/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A8A2CFCF-2936-6044-A826-1C8C32713F3D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ED8E8BD2-3063-264F-B081-68FD5B39248D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="18000" activeTab="1" xr2:uid="{23B5B348-4D99-B540-995F-50D24F235ACD}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="17500" activeTab="5" xr2:uid="{23B5B348-4D99-B540-995F-50D24F235ACD}"/>
   </bookViews>
   <sheets>
     <sheet name="table 1" sheetId="1" r:id="rId1"/>
@@ -18,6 +18,7 @@
     <sheet name="table 3" sheetId="3" r:id="rId3"/>
     <sheet name="table 4" sheetId="5" r:id="rId4"/>
     <sheet name="table 5" sheetId="4" r:id="rId5"/>
+    <sheet name="cancer_counts" sheetId="6" r:id="rId6"/>
   </sheets>
   <calcPr calcId="181029"/>
   <extLst>
@@ -39,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="969" uniqueCount="719">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1181" uniqueCount="923">
   <si>
     <t>Age</t>
   </si>
@@ -2418,6 +2419,636 @@
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">. Logistic regression odds ratios (95% CI) for COVID-19 outcomes by cancer and by cancer treatment type. </t>
+    </r>
+  </si>
+  <si>
+    <t>145</t>
+  </si>
+  <si>
+    <t>Cancer of mouth</t>
+  </si>
+  <si>
+    <t>145.1</t>
+  </si>
+  <si>
+    <t>Cancer of lip</t>
+  </si>
+  <si>
+    <t>145.2</t>
+  </si>
+  <si>
+    <t>Cancer of tongue</t>
+  </si>
+  <si>
+    <t>145.3</t>
+  </si>
+  <si>
+    <t>Cancer of major salivary glands</t>
+  </si>
+  <si>
+    <t>145.4</t>
+  </si>
+  <si>
+    <t>Cancer of the gums</t>
+  </si>
+  <si>
+    <t>145.5</t>
+  </si>
+  <si>
+    <t>Cancer of the mouth floor</t>
+  </si>
+  <si>
+    <t>149</t>
+  </si>
+  <si>
+    <t>Cancer of larynx, pharynx, nasal cavities</t>
+  </si>
+  <si>
+    <t>149.1</t>
+  </si>
+  <si>
+    <t>Cancer of oropharynx</t>
+  </si>
+  <si>
+    <t>149.2</t>
+  </si>
+  <si>
+    <t>Cancer of nasopharynx</t>
+  </si>
+  <si>
+    <t>149.3</t>
+  </si>
+  <si>
+    <t>Cancer of hypopharynx</t>
+  </si>
+  <si>
+    <t>149.4</t>
+  </si>
+  <si>
+    <t>Cancer of larynx</t>
+  </si>
+  <si>
+    <t>149.5</t>
+  </si>
+  <si>
+    <t>Hx of malignant neoplasm of oral cavity and pharynx</t>
+  </si>
+  <si>
+    <t>149.9</t>
+  </si>
+  <si>
+    <t>Cancer of of nasal cavities</t>
+  </si>
+  <si>
+    <t>150</t>
+  </si>
+  <si>
+    <t>Cancer of esophagus</t>
+  </si>
+  <si>
+    <t>151</t>
+  </si>
+  <si>
+    <t>Cancer of stomach</t>
+  </si>
+  <si>
+    <t>153</t>
+  </si>
+  <si>
+    <t>Colorectal cancer</t>
+  </si>
+  <si>
+    <t>153.2</t>
+  </si>
+  <si>
+    <t>Colon cancer</t>
+  </si>
+  <si>
+    <t>153.3</t>
+  </si>
+  <si>
+    <t>Malignant neoplasm of rectum, rectosigmoid junction, and anus</t>
+  </si>
+  <si>
+    <t>155</t>
+  </si>
+  <si>
+    <t>Cancer of liver and intrahepatic bile duct</t>
+  </si>
+  <si>
+    <t>155.1</t>
+  </si>
+  <si>
+    <t>Malignant neoplasm of liver, primary</t>
+  </si>
+  <si>
+    <t>157</t>
+  </si>
+  <si>
+    <t>Pancreatic cancer</t>
+  </si>
+  <si>
+    <t>158</t>
+  </si>
+  <si>
+    <t>Neoplasm of unspecified nature of digestive system</t>
+  </si>
+  <si>
+    <t>159</t>
+  </si>
+  <si>
+    <t>Malignant neoplasm of other and ill-defined sites within the digestive organs and peritoneum</t>
+  </si>
+  <si>
+    <t>159.2</t>
+  </si>
+  <si>
+    <t>Malignant neoplasm of small intestine, including duodenum</t>
+  </si>
+  <si>
+    <t>159.3</t>
+  </si>
+  <si>
+    <t>Malignant neoplasm of gallbladder and extrahepatic bile ducts</t>
+  </si>
+  <si>
+    <t>159.4</t>
+  </si>
+  <si>
+    <t>Malignant neoplasm of retroperitoneum and peritoneum</t>
+  </si>
+  <si>
+    <t>164</t>
+  </si>
+  <si>
+    <t>Cancer of intrathoracic organs</t>
+  </si>
+  <si>
+    <t>165</t>
+  </si>
+  <si>
+    <t>Cancer within the respiratory system</t>
+  </si>
+  <si>
+    <t>165.1</t>
+  </si>
+  <si>
+    <t>Cancer of bronchus; lung</t>
+  </si>
+  <si>
+    <t>170</t>
+  </si>
+  <si>
+    <t>Cancer of bone and connective tissue</t>
+  </si>
+  <si>
+    <t>170.1</t>
+  </si>
+  <si>
+    <t>Bone cancer</t>
+  </si>
+  <si>
+    <t>170.2</t>
+  </si>
+  <si>
+    <t>Cancer of connective tissue</t>
+  </si>
+  <si>
+    <t>172.1</t>
+  </si>
+  <si>
+    <t>Melanomas of skin, dx or hx</t>
+  </si>
+  <si>
+    <t>172.11</t>
+  </si>
+  <si>
+    <t>Melanomas of skin</t>
+  </si>
+  <si>
+    <t>174</t>
+  </si>
+  <si>
+    <t>174.1</t>
+  </si>
+  <si>
+    <t>Breast cancer [female]</t>
+  </si>
+  <si>
+    <t>174.11</t>
+  </si>
+  <si>
+    <t>Malignant neoplasm of female breast</t>
+  </si>
+  <si>
+    <t>174.2</t>
+  </si>
+  <si>
+    <t>Breast cancer [male]</t>
+  </si>
+  <si>
+    <t>174.3</t>
+  </si>
+  <si>
+    <t>Neoplasm of uncertain behavior of breast</t>
+  </si>
+  <si>
+    <t>175</t>
+  </si>
+  <si>
+    <t>Acquired absence of breast</t>
+  </si>
+  <si>
+    <t>180</t>
+  </si>
+  <si>
+    <t>Cervical cancer and dysplasia</t>
+  </si>
+  <si>
+    <t>180.1</t>
+  </si>
+  <si>
+    <t>Cervical cancer</t>
+  </si>
+  <si>
+    <t>180.3</t>
+  </si>
+  <si>
+    <t>Cervical intraepithelial neoplasia [CIN] [Cervical dysplasia]</t>
+  </si>
+  <si>
+    <t>182</t>
+  </si>
+  <si>
+    <t>Malignant neoplasm of uterus</t>
+  </si>
+  <si>
+    <t>184</t>
+  </si>
+  <si>
+    <t>Cancer of other female genital organs</t>
+  </si>
+  <si>
+    <t>184.1</t>
+  </si>
+  <si>
+    <t>Malignant neoplasm of ovary and other uterine adnexa</t>
+  </si>
+  <si>
+    <t>184.11</t>
+  </si>
+  <si>
+    <t>Malignant neoplasm of ovary</t>
+  </si>
+  <si>
+    <t>184.2</t>
+  </si>
+  <si>
+    <t>Cancer of other female genital organs (excluding uterus and ovary)</t>
+  </si>
+  <si>
+    <t>185</t>
+  </si>
+  <si>
+    <t>Cancer of prostate</t>
+  </si>
+  <si>
+    <t>187</t>
+  </si>
+  <si>
+    <t>Cancer of other male genital organs</t>
+  </si>
+  <si>
+    <t>187.1</t>
+  </si>
+  <si>
+    <t>Malignant neoplasm of unspecified male genital organ</t>
+  </si>
+  <si>
+    <t>187.2</t>
+  </si>
+  <si>
+    <t>Malignant neoplasm of testis</t>
+  </si>
+  <si>
+    <t>187.8</t>
+  </si>
+  <si>
+    <t>Neoplasm of uncertain behavior of male genital organs</t>
+  </si>
+  <si>
+    <t>189</t>
+  </si>
+  <si>
+    <t>Cancer of urinary organs (incl. kidney and bladder)</t>
+  </si>
+  <si>
+    <t>189.1</t>
+  </si>
+  <si>
+    <t>Cancer of kidney and renal pelvis</t>
+  </si>
+  <si>
+    <t>189.11</t>
+  </si>
+  <si>
+    <t>Malignant neoplasm of kidney, except pelvis</t>
+  </si>
+  <si>
+    <t>189.12</t>
+  </si>
+  <si>
+    <t>Malignant neoplasm of renal pelvis</t>
+  </si>
+  <si>
+    <t>189.2</t>
+  </si>
+  <si>
+    <t>Cancer of bladder</t>
+  </si>
+  <si>
+    <t>189.21</t>
+  </si>
+  <si>
+    <t>Malignant neoplasm of bladder</t>
+  </si>
+  <si>
+    <t>189.4</t>
+  </si>
+  <si>
+    <t>Malignant neoplasm of other urinary organs</t>
+  </si>
+  <si>
+    <t>190</t>
+  </si>
+  <si>
+    <t>Cancer of eye</t>
+  </si>
+  <si>
+    <t>191</t>
+  </si>
+  <si>
+    <t>Manlignant and unknown neoplasms of brain and nervous system</t>
+  </si>
+  <si>
+    <t>191.1</t>
+  </si>
+  <si>
+    <t>Cancer of brain and nervous system</t>
+  </si>
+  <si>
+    <t>191.11</t>
+  </si>
+  <si>
+    <t>Cancer of brain</t>
+  </si>
+  <si>
+    <t>193</t>
+  </si>
+  <si>
+    <t>Thyroid cancer</t>
+  </si>
+  <si>
+    <t>194</t>
+  </si>
+  <si>
+    <t>Cancer of other endocrine glands</t>
+  </si>
+  <si>
+    <t>195</t>
+  </si>
+  <si>
+    <t>Cancer, suspected or other</t>
+  </si>
+  <si>
+    <t>195.1</t>
+  </si>
+  <si>
+    <t>Malignant neoplasm, other</t>
+  </si>
+  <si>
+    <t>195.3</t>
+  </si>
+  <si>
+    <t>Malignant neoplasm of head, face, and neck</t>
+  </si>
+  <si>
+    <t>196</t>
+  </si>
+  <si>
+    <t>Radiotherapy</t>
+  </si>
+  <si>
+    <t>197</t>
+  </si>
+  <si>
+    <t>198</t>
+  </si>
+  <si>
+    <t>Secondary malignant neoplasm</t>
+  </si>
+  <si>
+    <t>198.1</t>
+  </si>
+  <si>
+    <t>Secondary malignancy of lymph nodes</t>
+  </si>
+  <si>
+    <t>198.2</t>
+  </si>
+  <si>
+    <t>Secondary malignancy of respiratory organs</t>
+  </si>
+  <si>
+    <t>198.3</t>
+  </si>
+  <si>
+    <t>Secondary malignant neoplasm of digestive systems</t>
+  </si>
+  <si>
+    <t>198.4</t>
+  </si>
+  <si>
+    <t>Secondary malignant neoplasm of liver</t>
+  </si>
+  <si>
+    <t>198.5</t>
+  </si>
+  <si>
+    <t>Secondary malignancy of brain/spine</t>
+  </si>
+  <si>
+    <t>198.6</t>
+  </si>
+  <si>
+    <t>Secondary malignancy of bone</t>
+  </si>
+  <si>
+    <t>198.7</t>
+  </si>
+  <si>
+    <t>Secondary malignant neoplasm of skin</t>
+  </si>
+  <si>
+    <t>199</t>
+  </si>
+  <si>
+    <t>Neoplasm of uncertain behavior</t>
+  </si>
+  <si>
+    <t>199.4</t>
+  </si>
+  <si>
+    <t>Neurofibromatosis</t>
+  </si>
+  <si>
+    <t>200</t>
+  </si>
+  <si>
+    <t>Myeloproliferative disease</t>
+  </si>
+  <si>
+    <t>200.1</t>
+  </si>
+  <si>
+    <t>Polycythemia vera</t>
+  </si>
+  <si>
+    <t>201</t>
+  </si>
+  <si>
+    <t>Hodgkin's disease</t>
+  </si>
+  <si>
+    <t>202</t>
+  </si>
+  <si>
+    <t>Cancer of other lymphoid, histiocytic tissue</t>
+  </si>
+  <si>
+    <t>202.2</t>
+  </si>
+  <si>
+    <t>Non-Hodgkins lymphoma</t>
+  </si>
+  <si>
+    <t>202.21</t>
+  </si>
+  <si>
+    <t>Nodular lymphoma</t>
+  </si>
+  <si>
+    <t>202.22</t>
+  </si>
+  <si>
+    <t>Reticulosarcoma</t>
+  </si>
+  <si>
+    <t>202.23</t>
+  </si>
+  <si>
+    <t>Lymphosarcoma</t>
+  </si>
+  <si>
+    <t>202.24</t>
+  </si>
+  <si>
+    <t>Large cell lymphoma</t>
+  </si>
+  <si>
+    <t>204</t>
+  </si>
+  <si>
+    <t>Leukemia</t>
+  </si>
+  <si>
+    <t>204.1</t>
+  </si>
+  <si>
+    <t>Lymphoid leukemia</t>
+  </si>
+  <si>
+    <t>204.11</t>
+  </si>
+  <si>
+    <t>Lymphoid leukemia, acute</t>
+  </si>
+  <si>
+    <t>204.12</t>
+  </si>
+  <si>
+    <t>Lymphoid leukemia, chronic</t>
+  </si>
+  <si>
+    <t>204.2</t>
+  </si>
+  <si>
+    <t>Myeloid leukemia</t>
+  </si>
+  <si>
+    <t>204.21</t>
+  </si>
+  <si>
+    <t>Myeloid leukemia, acute</t>
+  </si>
+  <si>
+    <t>204.22</t>
+  </si>
+  <si>
+    <t>Myeloid leukemia, chronic</t>
+  </si>
+  <si>
+    <t>204.3</t>
+  </si>
+  <si>
+    <t>Monocytic leukemia</t>
+  </si>
+  <si>
+    <t>204.4</t>
+  </si>
+  <si>
+    <t>Multiple myeloma</t>
+  </si>
+  <si>
+    <t>209</t>
+  </si>
+  <si>
+    <t>Neuroendocrine tumors</t>
+  </si>
+  <si>
+    <t>860</t>
+  </si>
+  <si>
+    <t>Bone marrow or stem cell transplant</t>
+  </si>
+  <si>
+    <t>Phecode</t>
+  </si>
+  <si>
+    <t>Phenotype</t>
+  </si>
+  <si>
+    <t>Count</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Helvetica Neue"/>
+        <family val="2"/>
+      </rPr>
+      <t>Table X</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Helvetica Neue"/>
+        <family val="2"/>
+      </rPr>
+      <t>. Phecodes used to identify individuals with cancer, along with their phenotype description and the number of individuals in the tested positive cohort with the corresponding phecode.</t>
     </r>
   </si>
 </sst>
@@ -2621,7 +3252,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="92">
+  <cellXfs count="94">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
@@ -2791,41 +3422,8 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -2849,8 +3447,47 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -3177,30 +3814,30 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:9" x14ac:dyDescent="0.15">
-      <c r="B2" s="74" t="s">
+      <c r="B2" s="84" t="s">
         <v>449</v>
       </c>
-      <c r="C2" s="74"/>
-      <c r="D2" s="74"/>
-      <c r="E2" s="74"/>
-      <c r="F2" s="74"/>
-      <c r="G2" s="74"/>
-      <c r="H2" s="74"/>
-      <c r="I2" s="74"/>
+      <c r="C2" s="84"/>
+      <c r="D2" s="84"/>
+      <c r="E2" s="84"/>
+      <c r="F2" s="84"/>
+      <c r="G2" s="84"/>
+      <c r="H2" s="84"/>
+      <c r="I2" s="84"/>
     </row>
     <row r="3" spans="2:9" x14ac:dyDescent="0.15">
       <c r="B3" s="4"/>
-      <c r="C3" s="71" t="s">
+      <c r="C3" s="81" t="s">
         <v>445</v>
       </c>
-      <c r="D3" s="71"/>
-      <c r="E3" s="71"/>
-      <c r="F3" s="72" t="s">
+      <c r="D3" s="81"/>
+      <c r="E3" s="81"/>
+      <c r="F3" s="82" t="s">
         <v>446</v>
       </c>
-      <c r="G3" s="73"/>
-      <c r="H3" s="73"/>
-      <c r="I3" s="73"/>
+      <c r="G3" s="83"/>
+      <c r="H3" s="83"/>
+      <c r="I3" s="83"/>
     </row>
     <row r="4" spans="2:9" x14ac:dyDescent="0.15">
       <c r="B4" s="4"/>
@@ -5183,75 +5820,75 @@
       </c>
     </row>
     <row r="90" spans="2:9" x14ac:dyDescent="0.15">
-      <c r="B90" s="75" t="s">
+      <c r="B90" s="85" t="s">
         <v>450</v>
       </c>
-      <c r="C90" s="75"/>
-      <c r="D90" s="75"/>
-      <c r="E90" s="75"/>
-      <c r="F90" s="75"/>
-      <c r="G90" s="75"/>
-      <c r="H90" s="75"/>
-      <c r="I90" s="75"/>
+      <c r="C90" s="85"/>
+      <c r="D90" s="85"/>
+      <c r="E90" s="85"/>
+      <c r="F90" s="85"/>
+      <c r="G90" s="85"/>
+      <c r="H90" s="85"/>
+      <c r="I90" s="85"/>
     </row>
     <row r="91" spans="2:9" ht="13" x14ac:dyDescent="0.15">
-      <c r="B91" s="76" t="s">
+      <c r="B91" s="86" t="s">
         <v>451</v>
       </c>
-      <c r="C91" s="76"/>
-      <c r="D91" s="76"/>
-      <c r="E91" s="76"/>
-      <c r="F91" s="76"/>
-      <c r="G91" s="76"/>
-      <c r="H91" s="76"/>
-      <c r="I91" s="76"/>
+      <c r="C91" s="86"/>
+      <c r="D91" s="86"/>
+      <c r="E91" s="86"/>
+      <c r="F91" s="86"/>
+      <c r="G91" s="86"/>
+      <c r="H91" s="86"/>
+      <c r="I91" s="86"/>
     </row>
     <row r="92" spans="2:9" ht="37" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B92" s="77" t="s">
+      <c r="B92" s="80" t="s">
         <v>452</v>
       </c>
-      <c r="C92" s="77"/>
-      <c r="D92" s="77"/>
-      <c r="E92" s="77"/>
-      <c r="F92" s="77"/>
-      <c r="G92" s="77"/>
-      <c r="H92" s="77"/>
-      <c r="I92" s="77"/>
+      <c r="C92" s="80"/>
+      <c r="D92" s="80"/>
+      <c r="E92" s="80"/>
+      <c r="F92" s="80"/>
+      <c r="G92" s="80"/>
+      <c r="H92" s="80"/>
+      <c r="I92" s="80"/>
     </row>
     <row r="93" spans="2:9" ht="26" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B93" s="77" t="s">
+      <c r="B93" s="80" t="s">
         <v>453</v>
       </c>
-      <c r="C93" s="77"/>
-      <c r="D93" s="77"/>
-      <c r="E93" s="77"/>
-      <c r="F93" s="77"/>
-      <c r="G93" s="77"/>
-      <c r="H93" s="77"/>
-      <c r="I93" s="77"/>
+      <c r="C93" s="80"/>
+      <c r="D93" s="80"/>
+      <c r="E93" s="80"/>
+      <c r="F93" s="80"/>
+      <c r="G93" s="80"/>
+      <c r="H93" s="80"/>
+      <c r="I93" s="80"/>
     </row>
     <row r="94" spans="2:9" ht="25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B94" s="77" t="s">
+      <c r="B94" s="80" t="s">
         <v>454</v>
       </c>
-      <c r="C94" s="77"/>
-      <c r="D94" s="77"/>
-      <c r="E94" s="77"/>
-      <c r="F94" s="77"/>
-      <c r="G94" s="77"/>
-      <c r="H94" s="77"/>
-      <c r="I94" s="77"/>
+      <c r="C94" s="80"/>
+      <c r="D94" s="80"/>
+      <c r="E94" s="80"/>
+      <c r="F94" s="80"/>
+      <c r="G94" s="80"/>
+      <c r="H94" s="80"/>
+      <c r="I94" s="80"/>
     </row>
   </sheetData>
   <mergeCells count="8">
+    <mergeCell ref="B2:I2"/>
+    <mergeCell ref="B90:I90"/>
+    <mergeCell ref="B91:I91"/>
     <mergeCell ref="B92:I92"/>
     <mergeCell ref="B93:I93"/>
     <mergeCell ref="B94:I94"/>
     <mergeCell ref="C3:E3"/>
     <mergeCell ref="F3:I3"/>
-    <mergeCell ref="B2:I2"/>
-    <mergeCell ref="B90:I90"/>
-    <mergeCell ref="B91:I91"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -5273,30 +5910,30 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:10" ht="32" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B2" s="80" t="s">
+      <c r="B2" s="89" t="s">
         <v>718</v>
       </c>
-      <c r="C2" s="80"/>
-      <c r="D2" s="80"/>
-      <c r="E2" s="80"/>
-      <c r="F2" s="80"/>
-      <c r="G2" s="80"/>
-      <c r="H2" s="80"/>
-      <c r="I2" s="80"/>
-      <c r="J2" s="80"/>
+      <c r="C2" s="89"/>
+      <c r="D2" s="89"/>
+      <c r="E2" s="89"/>
+      <c r="F2" s="89"/>
+      <c r="G2" s="89"/>
+      <c r="H2" s="89"/>
+      <c r="I2" s="89"/>
+      <c r="J2" s="89"/>
     </row>
     <row r="3" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="D3" s="78" t="s">
+      <c r="D3" s="87" t="s">
         <v>549</v>
       </c>
-      <c r="E3" s="79"/>
-      <c r="F3" s="79"/>
-      <c r="G3" s="79"/>
+      <c r="E3" s="88"/>
+      <c r="F3" s="88"/>
+      <c r="G3" s="88"/>
       <c r="H3" s="31"/>
-      <c r="I3" s="79" t="s">
+      <c r="I3" s="88" t="s">
         <v>552</v>
       </c>
-      <c r="J3" s="79"/>
+      <c r="J3" s="88"/>
     </row>
     <row r="4" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B4" s="32" t="s">
@@ -5910,17 +6547,17 @@
       </c>
     </row>
     <row r="29" spans="2:10" ht="65" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B29" s="81" t="s">
+      <c r="B29" s="90" t="s">
         <v>553</v>
       </c>
-      <c r="C29" s="82"/>
-      <c r="D29" s="82"/>
-      <c r="E29" s="82"/>
-      <c r="F29" s="82"/>
-      <c r="G29" s="82"/>
-      <c r="H29" s="82"/>
-      <c r="I29" s="82"/>
-      <c r="J29" s="82"/>
+      <c r="C29" s="91"/>
+      <c r="D29" s="91"/>
+      <c r="E29" s="91"/>
+      <c r="F29" s="91"/>
+      <c r="G29" s="91"/>
+      <c r="H29" s="91"/>
+      <c r="I29" s="91"/>
+      <c r="J29" s="91"/>
     </row>
   </sheetData>
   <mergeCells count="4">
@@ -5949,30 +6586,30 @@
   </cols>
   <sheetData>
     <row r="3" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="B3" s="80" t="s">
+      <c r="B3" s="89" t="s">
         <v>656</v>
       </c>
-      <c r="C3" s="80"/>
-      <c r="D3" s="80"/>
-      <c r="E3" s="80"/>
-      <c r="F3" s="80"/>
-      <c r="G3" s="80"/>
-      <c r="H3" s="80"/>
-      <c r="I3" s="80"/>
-      <c r="J3" s="80"/>
+      <c r="C3" s="89"/>
+      <c r="D3" s="89"/>
+      <c r="E3" s="89"/>
+      <c r="F3" s="89"/>
+      <c r="G3" s="89"/>
+      <c r="H3" s="89"/>
+      <c r="I3" s="89"/>
+      <c r="J3" s="89"/>
     </row>
     <row r="4" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="D4" s="78" t="s">
+      <c r="D4" s="87" t="s">
         <v>549</v>
       </c>
-      <c r="E4" s="79"/>
-      <c r="F4" s="79"/>
-      <c r="G4" s="79"/>
+      <c r="E4" s="88"/>
+      <c r="F4" s="88"/>
+      <c r="G4" s="88"/>
       <c r="H4" s="31"/>
-      <c r="I4" s="79" t="s">
+      <c r="I4" s="88" t="s">
         <v>552</v>
       </c>
-      <c r="J4" s="79"/>
+      <c r="J4" s="88"/>
     </row>
     <row r="5" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B5" s="32" t="s">
@@ -6734,17 +7371,17 @@
       </c>
     </row>
     <row r="36" spans="2:10" ht="66" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B36" s="81" t="s">
+      <c r="B36" s="90" t="s">
         <v>657</v>
       </c>
-      <c r="C36" s="81"/>
-      <c r="D36" s="81"/>
-      <c r="E36" s="81"/>
-      <c r="F36" s="81"/>
-      <c r="G36" s="81"/>
-      <c r="H36" s="81"/>
-      <c r="I36" s="81"/>
-      <c r="J36" s="81"/>
+      <c r="C36" s="90"/>
+      <c r="D36" s="90"/>
+      <c r="E36" s="90"/>
+      <c r="F36" s="90"/>
+      <c r="G36" s="90"/>
+      <c r="H36" s="90"/>
+      <c r="I36" s="90"/>
+      <c r="J36" s="90"/>
     </row>
   </sheetData>
   <mergeCells count="4">
@@ -6776,48 +7413,48 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:11" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B2" s="91" t="s">
+      <c r="B2" s="92" t="s">
         <v>716</v>
       </c>
-      <c r="C2" s="91"/>
-      <c r="D2" s="91"/>
-      <c r="E2" s="91"/>
-      <c r="F2" s="91"/>
-      <c r="G2" s="91"/>
-      <c r="H2" s="91"/>
-      <c r="I2" s="91"/>
-      <c r="J2" s="91"/>
-      <c r="K2" s="91"/>
+      <c r="C2" s="92"/>
+      <c r="D2" s="92"/>
+      <c r="E2" s="92"/>
+      <c r="F2" s="92"/>
+      <c r="G2" s="92"/>
+      <c r="H2" s="92"/>
+      <c r="I2" s="92"/>
+      <c r="J2" s="92"/>
+      <c r="K2" s="92"/>
     </row>
     <row r="3" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B3" s="31"/>
-      <c r="C3" s="79" t="s">
+      <c r="C3" s="88" t="s">
         <v>682</v>
       </c>
-      <c r="D3" s="79"/>
-      <c r="E3" s="83"/>
-      <c r="F3" s="83"/>
-      <c r="G3" s="83"/>
-      <c r="H3" s="83"/>
+      <c r="D3" s="88"/>
+      <c r="E3" s="72"/>
+      <c r="F3" s="72"/>
+      <c r="G3" s="72"/>
+      <c r="H3" s="72"/>
     </row>
     <row r="4" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B4" s="31"/>
-      <c r="C4" s="83" t="s">
+      <c r="C4" s="72" t="s">
         <v>683</v>
       </c>
-      <c r="D4" s="83" t="s">
+      <c r="D4" s="72" t="s">
         <v>684</v>
       </c>
-      <c r="E4" s="83"/>
-      <c r="F4" s="79" t="s">
+      <c r="E4" s="72"/>
+      <c r="F4" s="88" t="s">
         <v>686</v>
       </c>
-      <c r="G4" s="79"/>
-      <c r="H4" s="79"/>
-      <c r="J4" s="79" t="s">
+      <c r="G4" s="88"/>
+      <c r="H4" s="88"/>
+      <c r="J4" s="88" t="s">
         <v>552</v>
       </c>
-      <c r="K4" s="79"/>
+      <c r="K4" s="88"/>
     </row>
     <row r="5" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B5" s="32" t="s">
@@ -6875,7 +7512,7 @@
       <c r="F7" s="3">
         <v>0.14000000000000001</v>
       </c>
-      <c r="G7" s="87" t="s">
+      <c r="G7" s="76" t="s">
         <v>700</v>
       </c>
       <c r="H7" s="3">
@@ -6946,7 +7583,7 @@
       </c>
     </row>
     <row r="10" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="B10" s="84" t="s">
+      <c r="B10" s="73" t="s">
         <v>679</v>
       </c>
       <c r="C10" s="2"/>
@@ -6995,7 +7632,7 @@
       <c r="D12" s="1" t="s">
         <v>689</v>
       </c>
-      <c r="F12" s="88" t="s">
+      <c r="F12" s="77" t="s">
         <v>714</v>
       </c>
       <c r="G12" s="47" t="s">
@@ -7012,7 +7649,7 @@
       </c>
     </row>
     <row r="13" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="B13" s="85" t="s">
+      <c r="B13" s="74" t="s">
         <v>678</v>
       </c>
       <c r="C13" s="2" t="s">
@@ -7021,14 +7658,14 @@
       <c r="D13" s="2" t="s">
         <v>697</v>
       </c>
-      <c r="E13" s="86"/>
-      <c r="F13" s="89" t="s">
+      <c r="E13" s="75"/>
+      <c r="F13" s="78" t="s">
         <v>700</v>
       </c>
-      <c r="G13" s="89" t="s">
+      <c r="G13" s="78" t="s">
         <v>700</v>
       </c>
-      <c r="H13" s="90" t="s">
+      <c r="H13" s="79" t="s">
         <v>713</v>
       </c>
       <c r="I13" s="2"/>
@@ -7232,18 +7869,18 @@
       </c>
     </row>
     <row r="22" spans="2:11" ht="32" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B22" s="81" t="s">
+      <c r="B22" s="90" t="s">
         <v>715</v>
       </c>
-      <c r="C22" s="81"/>
-      <c r="D22" s="81"/>
-      <c r="E22" s="81"/>
-      <c r="F22" s="81"/>
-      <c r="G22" s="81"/>
-      <c r="H22" s="81"/>
-      <c r="I22" s="81"/>
-      <c r="J22" s="81"/>
-      <c r="K22" s="81"/>
+      <c r="C22" s="90"/>
+      <c r="D22" s="90"/>
+      <c r="E22" s="90"/>
+      <c r="F22" s="90"/>
+      <c r="G22" s="90"/>
+      <c r="H22" s="90"/>
+      <c r="I22" s="90"/>
+      <c r="J22" s="90"/>
+      <c r="K22" s="90"/>
     </row>
   </sheetData>
   <mergeCells count="5">
@@ -7269,32 +7906,32 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:10" ht="32" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B2" s="80" t="s">
+      <c r="B2" s="89" t="s">
         <v>717</v>
       </c>
-      <c r="C2" s="80"/>
-      <c r="D2" s="80"/>
-      <c r="E2" s="80"/>
-      <c r="F2" s="80"/>
-      <c r="G2" s="80"/>
-      <c r="H2" s="80"/>
-      <c r="I2" s="80"/>
-      <c r="J2" s="80"/>
+      <c r="C2" s="89"/>
+      <c r="D2" s="89"/>
+      <c r="E2" s="89"/>
+      <c r="F2" s="89"/>
+      <c r="G2" s="89"/>
+      <c r="H2" s="89"/>
+      <c r="I2" s="89"/>
+      <c r="J2" s="89"/>
     </row>
     <row r="3" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B3" s="1"/>
       <c r="C3" s="1"/>
-      <c r="D3" s="78" t="s">
+      <c r="D3" s="87" t="s">
         <v>549</v>
       </c>
-      <c r="E3" s="79"/>
-      <c r="F3" s="79"/>
-      <c r="G3" s="79"/>
+      <c r="E3" s="88"/>
+      <c r="F3" s="88"/>
+      <c r="G3" s="88"/>
       <c r="H3" s="31"/>
-      <c r="I3" s="79" t="s">
+      <c r="I3" s="88" t="s">
         <v>552</v>
       </c>
-      <c r="J3" s="79"/>
+      <c r="J3" s="88"/>
     </row>
     <row r="4" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B4" s="32" t="s">
@@ -7472,17 +8109,17 @@
       </c>
     </row>
     <row r="11" spans="2:10" ht="66" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B11" s="81" t="s">
+      <c r="B11" s="90" t="s">
         <v>553</v>
       </c>
-      <c r="C11" s="82"/>
-      <c r="D11" s="82"/>
-      <c r="E11" s="82"/>
-      <c r="F11" s="82"/>
-      <c r="G11" s="82"/>
-      <c r="H11" s="82"/>
-      <c r="I11" s="82"/>
-      <c r="J11" s="82"/>
+      <c r="C11" s="91"/>
+      <c r="D11" s="91"/>
+      <c r="E11" s="91"/>
+      <c r="F11" s="91"/>
+      <c r="G11" s="91"/>
+      <c r="H11" s="91"/>
+      <c r="I11" s="91"/>
+      <c r="J11" s="91"/>
     </row>
   </sheetData>
   <mergeCells count="4">
@@ -7493,4 +8130,1060 @@
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4F22A83E-07CA-E848-8AFC-AD767CC22F85}">
+  <dimension ref="B3:L38"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="10.83203125" style="1"/>
+    <col min="2" max="2" width="9.5" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="86" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="6.83203125" style="47" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="1.83203125" style="1" customWidth="1"/>
+    <col min="6" max="6" width="9.5" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="61.5" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="6.83203125" style="47" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="1.83203125" style="1" customWidth="1"/>
+    <col min="10" max="10" width="9.5" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="49" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="6.83203125" style="47" bestFit="1" customWidth="1"/>
+    <col min="13" max="16384" width="10.83203125" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="3" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B3" s="93" t="s">
+        <v>922</v>
+      </c>
+      <c r="C3" s="93"/>
+      <c r="D3" s="93"/>
+      <c r="E3" s="93"/>
+      <c r="F3" s="93"/>
+      <c r="G3" s="93"/>
+      <c r="H3" s="93"/>
+      <c r="I3" s="93"/>
+      <c r="J3" s="93"/>
+      <c r="K3" s="93"/>
+      <c r="L3" s="93"/>
+    </row>
+    <row r="4" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B4" s="32" t="s">
+        <v>919</v>
+      </c>
+      <c r="C4" s="32" t="s">
+        <v>920</v>
+      </c>
+      <c r="D4" s="71" t="s">
+        <v>921</v>
+      </c>
+      <c r="E4" s="32"/>
+      <c r="F4" s="32" t="s">
+        <v>919</v>
+      </c>
+      <c r="G4" s="32" t="s">
+        <v>920</v>
+      </c>
+      <c r="H4" s="71" t="s">
+        <v>921</v>
+      </c>
+      <c r="I4" s="32"/>
+      <c r="J4" s="32" t="s">
+        <v>919</v>
+      </c>
+      <c r="K4" s="32" t="s">
+        <v>920</v>
+      </c>
+      <c r="L4" s="71" t="s">
+        <v>921</v>
+      </c>
+    </row>
+    <row r="5" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B5" s="38" t="s">
+        <v>719</v>
+      </c>
+      <c r="C5" s="38" t="s">
+        <v>720</v>
+      </c>
+      <c r="D5" s="39">
+        <v>284</v>
+      </c>
+      <c r="F5" s="38" t="s">
+        <v>787</v>
+      </c>
+      <c r="G5" s="38" t="s">
+        <v>593</v>
+      </c>
+      <c r="H5" s="39">
+        <v>1247</v>
+      </c>
+      <c r="J5" s="38" t="s">
+        <v>854</v>
+      </c>
+      <c r="K5" s="38" t="s">
+        <v>855</v>
+      </c>
+      <c r="L5" s="39">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="6" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B6" s="1" t="s">
+        <v>721</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>722</v>
+      </c>
+      <c r="D6" s="48">
+        <v>18</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>788</v>
+      </c>
+      <c r="G6" s="1" t="s">
+        <v>789</v>
+      </c>
+      <c r="H6" s="48">
+        <v>1177</v>
+      </c>
+      <c r="J6" s="1" t="s">
+        <v>856</v>
+      </c>
+      <c r="K6" s="1" t="s">
+        <v>857</v>
+      </c>
+      <c r="L6" s="48">
+        <v>787</v>
+      </c>
+    </row>
+    <row r="7" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B7" s="38" t="s">
+        <v>723</v>
+      </c>
+      <c r="C7" s="38" t="s">
+        <v>724</v>
+      </c>
+      <c r="D7" s="39">
+        <v>92</v>
+      </c>
+      <c r="F7" s="38" t="s">
+        <v>790</v>
+      </c>
+      <c r="G7" s="38" t="s">
+        <v>791</v>
+      </c>
+      <c r="H7" s="39">
+        <v>1144</v>
+      </c>
+      <c r="J7" s="38" t="s">
+        <v>858</v>
+      </c>
+      <c r="K7" s="38" t="s">
+        <v>480</v>
+      </c>
+      <c r="L7" s="39">
+        <v>2105</v>
+      </c>
+    </row>
+    <row r="8" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B8" s="1" t="s">
+        <v>725</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>726</v>
+      </c>
+      <c r="D8" s="48">
+        <v>76</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>792</v>
+      </c>
+      <c r="G8" s="1" t="s">
+        <v>793</v>
+      </c>
+      <c r="H8" s="48">
+        <v>9</v>
+      </c>
+      <c r="J8" s="1" t="s">
+        <v>859</v>
+      </c>
+      <c r="K8" s="1" t="s">
+        <v>860</v>
+      </c>
+      <c r="L8" s="48">
+        <v>1594</v>
+      </c>
+    </row>
+    <row r="9" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B9" s="38" t="s">
+        <v>727</v>
+      </c>
+      <c r="C9" s="38" t="s">
+        <v>728</v>
+      </c>
+      <c r="D9" s="39">
+        <v>23</v>
+      </c>
+      <c r="F9" s="38" t="s">
+        <v>794</v>
+      </c>
+      <c r="G9" s="38" t="s">
+        <v>795</v>
+      </c>
+      <c r="H9" s="39">
+        <v>89</v>
+      </c>
+      <c r="J9" s="38" t="s">
+        <v>861</v>
+      </c>
+      <c r="K9" s="38" t="s">
+        <v>862</v>
+      </c>
+      <c r="L9" s="39">
+        <v>907</v>
+      </c>
+    </row>
+    <row r="10" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B10" s="1" t="s">
+        <v>729</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>730</v>
+      </c>
+      <c r="D10" s="48">
+        <v>18</v>
+      </c>
+      <c r="F10" s="1" t="s">
+        <v>796</v>
+      </c>
+      <c r="G10" s="1" t="s">
+        <v>797</v>
+      </c>
+      <c r="H10" s="48">
+        <v>328</v>
+      </c>
+      <c r="J10" s="1" t="s">
+        <v>863</v>
+      </c>
+      <c r="K10" s="1" t="s">
+        <v>864</v>
+      </c>
+      <c r="L10" s="48">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="11" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B11" s="38" t="s">
+        <v>731</v>
+      </c>
+      <c r="C11" s="38" t="s">
+        <v>732</v>
+      </c>
+      <c r="D11" s="39">
+        <v>253</v>
+      </c>
+      <c r="F11" s="38" t="s">
+        <v>798</v>
+      </c>
+      <c r="G11" s="38" t="s">
+        <v>799</v>
+      </c>
+      <c r="H11" s="39">
+        <v>1281</v>
+      </c>
+      <c r="J11" s="38" t="s">
+        <v>865</v>
+      </c>
+      <c r="K11" s="38" t="s">
+        <v>866</v>
+      </c>
+      <c r="L11" s="39">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="12" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B12" s="1" t="s">
+        <v>733</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>734</v>
+      </c>
+      <c r="D12" s="48">
+        <v>84</v>
+      </c>
+      <c r="F12" s="1" t="s">
+        <v>800</v>
+      </c>
+      <c r="G12" s="1" t="s">
+        <v>801</v>
+      </c>
+      <c r="H12" s="48">
+        <v>193</v>
+      </c>
+      <c r="J12" s="1" t="s">
+        <v>867</v>
+      </c>
+      <c r="K12" s="1" t="s">
+        <v>868</v>
+      </c>
+      <c r="L12" s="48">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="13" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B13" s="38" t="s">
+        <v>735</v>
+      </c>
+      <c r="C13" s="38" t="s">
+        <v>736</v>
+      </c>
+      <c r="D13" s="39">
+        <v>30</v>
+      </c>
+      <c r="F13" s="38" t="s">
+        <v>802</v>
+      </c>
+      <c r="G13" s="38" t="s">
+        <v>803</v>
+      </c>
+      <c r="H13" s="39">
+        <v>1139</v>
+      </c>
+      <c r="J13" s="38" t="s">
+        <v>869</v>
+      </c>
+      <c r="K13" s="38" t="s">
+        <v>870</v>
+      </c>
+      <c r="L13" s="39">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="14" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B14" s="1" t="s">
+        <v>737</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>738</v>
+      </c>
+      <c r="D14" s="48">
+        <v>19</v>
+      </c>
+      <c r="F14" s="1" t="s">
+        <v>804</v>
+      </c>
+      <c r="G14" s="1" t="s">
+        <v>805</v>
+      </c>
+      <c r="H14" s="48">
+        <v>262</v>
+      </c>
+      <c r="J14" s="1" t="s">
+        <v>871</v>
+      </c>
+      <c r="K14" s="1" t="s">
+        <v>872</v>
+      </c>
+      <c r="L14" s="48">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="15" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B15" s="38" t="s">
+        <v>739</v>
+      </c>
+      <c r="C15" s="38" t="s">
+        <v>740</v>
+      </c>
+      <c r="D15" s="39">
+        <v>78</v>
+      </c>
+      <c r="F15" s="38" t="s">
+        <v>806</v>
+      </c>
+      <c r="G15" s="38" t="s">
+        <v>807</v>
+      </c>
+      <c r="H15" s="39">
+        <v>466</v>
+      </c>
+      <c r="J15" s="38" t="s">
+        <v>873</v>
+      </c>
+      <c r="K15" s="38" t="s">
+        <v>874</v>
+      </c>
+      <c r="L15" s="39">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="16" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B16" s="1" t="s">
+        <v>741</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>742</v>
+      </c>
+      <c r="D16" s="48">
+        <v>69</v>
+      </c>
+      <c r="F16" s="1" t="s">
+        <v>808</v>
+      </c>
+      <c r="G16" s="1" t="s">
+        <v>809</v>
+      </c>
+      <c r="H16" s="48">
+        <v>207</v>
+      </c>
+      <c r="J16" s="1" t="s">
+        <v>875</v>
+      </c>
+      <c r="K16" s="1" t="s">
+        <v>876</v>
+      </c>
+      <c r="L16" s="48">
+        <v>2595</v>
+      </c>
+    </row>
+    <row r="17" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B17" s="38" t="s">
+        <v>743</v>
+      </c>
+      <c r="C17" s="38" t="s">
+        <v>744</v>
+      </c>
+      <c r="D17" s="39">
+        <v>38</v>
+      </c>
+      <c r="F17" s="38" t="s">
+        <v>810</v>
+      </c>
+      <c r="G17" s="38" t="s">
+        <v>811</v>
+      </c>
+      <c r="H17" s="39">
+        <v>159</v>
+      </c>
+      <c r="J17" s="38" t="s">
+        <v>877</v>
+      </c>
+      <c r="K17" s="38" t="s">
+        <v>878</v>
+      </c>
+      <c r="L17" s="39">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="18" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B18" s="1" t="s">
+        <v>745</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>746</v>
+      </c>
+      <c r="D18" s="48">
+        <v>112</v>
+      </c>
+      <c r="F18" s="1" t="s">
+        <v>812</v>
+      </c>
+      <c r="G18" s="1" t="s">
+        <v>813</v>
+      </c>
+      <c r="H18" s="48">
+        <v>229</v>
+      </c>
+      <c r="J18" s="1" t="s">
+        <v>879</v>
+      </c>
+      <c r="K18" s="1" t="s">
+        <v>880</v>
+      </c>
+      <c r="L18" s="48">
+        <v>1215</v>
+      </c>
+    </row>
+    <row r="19" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B19" s="38" t="s">
+        <v>747</v>
+      </c>
+      <c r="C19" s="38" t="s">
+        <v>748</v>
+      </c>
+      <c r="D19" s="39">
+        <v>154</v>
+      </c>
+      <c r="F19" s="38" t="s">
+        <v>814</v>
+      </c>
+      <c r="G19" s="38" t="s">
+        <v>815</v>
+      </c>
+      <c r="H19" s="39">
+        <v>1058</v>
+      </c>
+      <c r="J19" s="38" t="s">
+        <v>881</v>
+      </c>
+      <c r="K19" s="38" t="s">
+        <v>882</v>
+      </c>
+      <c r="L19" s="39">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="20" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B20" s="1" t="s">
+        <v>749</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>750</v>
+      </c>
+      <c r="D20" s="48">
+        <v>637</v>
+      </c>
+      <c r="F20" s="1" t="s">
+        <v>816</v>
+      </c>
+      <c r="G20" s="1" t="s">
+        <v>817</v>
+      </c>
+      <c r="H20" s="48">
+        <v>158</v>
+      </c>
+      <c r="J20" s="1" t="s">
+        <v>883</v>
+      </c>
+      <c r="K20" s="1" t="s">
+        <v>884</v>
+      </c>
+      <c r="L20" s="48">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="21" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B21" s="38" t="s">
+        <v>751</v>
+      </c>
+      <c r="C21" s="38" t="s">
+        <v>752</v>
+      </c>
+      <c r="D21" s="39">
+        <v>499</v>
+      </c>
+      <c r="F21" s="38" t="s">
+        <v>818</v>
+      </c>
+      <c r="G21" s="38" t="s">
+        <v>819</v>
+      </c>
+      <c r="H21" s="39">
+        <v>29</v>
+      </c>
+      <c r="J21" s="38" t="s">
+        <v>885</v>
+      </c>
+      <c r="K21" s="38" t="s">
+        <v>886</v>
+      </c>
+      <c r="L21" s="39">
+        <v>984</v>
+      </c>
+    </row>
+    <row r="22" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B22" s="1" t="s">
+        <v>753</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>754</v>
+      </c>
+      <c r="D22" s="48">
+        <v>335</v>
+      </c>
+      <c r="F22" s="1" t="s">
+        <v>820</v>
+      </c>
+      <c r="G22" s="1" t="s">
+        <v>821</v>
+      </c>
+      <c r="H22" s="48">
+        <v>101</v>
+      </c>
+      <c r="J22" s="1" t="s">
+        <v>887</v>
+      </c>
+      <c r="K22" s="1" t="s">
+        <v>888</v>
+      </c>
+      <c r="L22" s="48">
+        <v>864</v>
+      </c>
+    </row>
+    <row r="23" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B23" s="38" t="s">
+        <v>755</v>
+      </c>
+      <c r="C23" s="38" t="s">
+        <v>756</v>
+      </c>
+      <c r="D23" s="39">
+        <v>219</v>
+      </c>
+      <c r="F23" s="38" t="s">
+        <v>822</v>
+      </c>
+      <c r="G23" s="38" t="s">
+        <v>823</v>
+      </c>
+      <c r="H23" s="39">
+        <v>40</v>
+      </c>
+      <c r="J23" s="38" t="s">
+        <v>889</v>
+      </c>
+      <c r="K23" s="38" t="s">
+        <v>890</v>
+      </c>
+      <c r="L23" s="39">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="24" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B24" s="1" t="s">
+        <v>757</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>758</v>
+      </c>
+      <c r="D24" s="48">
+        <v>172</v>
+      </c>
+      <c r="F24" s="1" t="s">
+        <v>824</v>
+      </c>
+      <c r="G24" s="1" t="s">
+        <v>825</v>
+      </c>
+      <c r="H24" s="48">
+        <v>852</v>
+      </c>
+      <c r="J24" s="1" t="s">
+        <v>891</v>
+      </c>
+      <c r="K24" s="1" t="s">
+        <v>892</v>
+      </c>
+      <c r="L24" s="48">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="25" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B25" s="38" t="s">
+        <v>759</v>
+      </c>
+      <c r="C25" s="38" t="s">
+        <v>760</v>
+      </c>
+      <c r="D25" s="39">
+        <v>133</v>
+      </c>
+      <c r="F25" s="38" t="s">
+        <v>826</v>
+      </c>
+      <c r="G25" s="38" t="s">
+        <v>827</v>
+      </c>
+      <c r="H25" s="39">
+        <v>449</v>
+      </c>
+      <c r="J25" s="38" t="s">
+        <v>893</v>
+      </c>
+      <c r="K25" s="38" t="s">
+        <v>894</v>
+      </c>
+      <c r="L25" s="39">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="26" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B26" s="1" t="s">
+        <v>761</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>762</v>
+      </c>
+      <c r="D26" s="48">
+        <v>645</v>
+      </c>
+      <c r="F26" s="1" t="s">
+        <v>828</v>
+      </c>
+      <c r="G26" s="1" t="s">
+        <v>829</v>
+      </c>
+      <c r="H26" s="48">
+        <v>383</v>
+      </c>
+      <c r="J26" s="1" t="s">
+        <v>895</v>
+      </c>
+      <c r="K26" s="1" t="s">
+        <v>896</v>
+      </c>
+      <c r="L26" s="48">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="27" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B27" s="38" t="s">
+        <v>763</v>
+      </c>
+      <c r="C27" s="38" t="s">
+        <v>764</v>
+      </c>
+      <c r="D27" s="39">
+        <v>669</v>
+      </c>
+      <c r="F27" s="38" t="s">
+        <v>830</v>
+      </c>
+      <c r="G27" s="38" t="s">
+        <v>831</v>
+      </c>
+      <c r="H27" s="39">
+        <v>50</v>
+      </c>
+      <c r="J27" s="38" t="s">
+        <v>897</v>
+      </c>
+      <c r="K27" s="38" t="s">
+        <v>898</v>
+      </c>
+      <c r="L27" s="39">
+        <v>802</v>
+      </c>
+    </row>
+    <row r="28" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B28" s="1" t="s">
+        <v>765</v>
+      </c>
+      <c r="C28" s="1" t="s">
+        <v>766</v>
+      </c>
+      <c r="D28" s="48">
+        <v>57</v>
+      </c>
+      <c r="F28" s="1" t="s">
+        <v>832</v>
+      </c>
+      <c r="G28" s="1" t="s">
+        <v>833</v>
+      </c>
+      <c r="H28" s="48">
+        <v>444</v>
+      </c>
+      <c r="J28" s="1" t="s">
+        <v>899</v>
+      </c>
+      <c r="K28" s="1" t="s">
+        <v>900</v>
+      </c>
+      <c r="L28" s="48">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="29" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B29" s="38" t="s">
+        <v>767</v>
+      </c>
+      <c r="C29" s="38" t="s">
+        <v>768</v>
+      </c>
+      <c r="D29" s="39">
+        <v>37</v>
+      </c>
+      <c r="F29" s="38" t="s">
+        <v>834</v>
+      </c>
+      <c r="G29" s="38" t="s">
+        <v>835</v>
+      </c>
+      <c r="H29" s="39">
+        <v>397</v>
+      </c>
+      <c r="J29" s="38" t="s">
+        <v>901</v>
+      </c>
+      <c r="K29" s="38" t="s">
+        <v>902</v>
+      </c>
+      <c r="L29" s="39">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="30" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B30" s="1" t="s">
+        <v>769</v>
+      </c>
+      <c r="C30" s="1" t="s">
+        <v>770</v>
+      </c>
+      <c r="D30" s="48">
+        <v>81</v>
+      </c>
+      <c r="F30" s="1" t="s">
+        <v>836</v>
+      </c>
+      <c r="G30" s="1" t="s">
+        <v>837</v>
+      </c>
+      <c r="H30" s="48">
+        <v>111</v>
+      </c>
+      <c r="J30" s="1" t="s">
+        <v>903</v>
+      </c>
+      <c r="K30" s="1" t="s">
+        <v>904</v>
+      </c>
+      <c r="L30" s="48">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="31" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B31" s="38" t="s">
+        <v>771</v>
+      </c>
+      <c r="C31" s="38" t="s">
+        <v>772</v>
+      </c>
+      <c r="D31" s="39">
+        <v>61</v>
+      </c>
+      <c r="F31" s="38" t="s">
+        <v>838</v>
+      </c>
+      <c r="G31" s="38" t="s">
+        <v>839</v>
+      </c>
+      <c r="H31" s="39">
+        <v>81</v>
+      </c>
+      <c r="J31" s="38" t="s">
+        <v>905</v>
+      </c>
+      <c r="K31" s="38" t="s">
+        <v>906</v>
+      </c>
+      <c r="L31" s="39">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="32" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B32" s="1" t="s">
+        <v>773</v>
+      </c>
+      <c r="C32" s="1" t="s">
+        <v>774</v>
+      </c>
+      <c r="D32" s="48">
+        <v>459</v>
+      </c>
+      <c r="F32" s="1" t="s">
+        <v>840</v>
+      </c>
+      <c r="G32" s="1" t="s">
+        <v>841</v>
+      </c>
+      <c r="H32" s="48">
+        <v>370</v>
+      </c>
+      <c r="J32" s="1" t="s">
+        <v>907</v>
+      </c>
+      <c r="K32" s="1" t="s">
+        <v>908</v>
+      </c>
+      <c r="L32" s="48">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="33" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B33" s="38" t="s">
+        <v>775</v>
+      </c>
+      <c r="C33" s="38" t="s">
+        <v>776</v>
+      </c>
+      <c r="D33" s="39">
+        <v>397</v>
+      </c>
+      <c r="F33" s="38" t="s">
+        <v>842</v>
+      </c>
+      <c r="G33" s="38" t="s">
+        <v>843</v>
+      </c>
+      <c r="H33" s="39">
+        <v>229</v>
+      </c>
+      <c r="J33" s="38" t="s">
+        <v>909</v>
+      </c>
+      <c r="K33" s="38" t="s">
+        <v>910</v>
+      </c>
+      <c r="L33" s="39">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="34" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B34" s="1" t="s">
+        <v>777</v>
+      </c>
+      <c r="C34" s="1" t="s">
+        <v>778</v>
+      </c>
+      <c r="D34" s="48">
+        <v>525</v>
+      </c>
+      <c r="F34" s="1" t="s">
+        <v>844</v>
+      </c>
+      <c r="G34" s="1" t="s">
+        <v>845</v>
+      </c>
+      <c r="H34" s="48">
+        <v>199</v>
+      </c>
+      <c r="J34" s="1" t="s">
+        <v>911</v>
+      </c>
+      <c r="K34" s="1" t="s">
+        <v>912</v>
+      </c>
+      <c r="L34" s="48">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="35" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B35" s="38" t="s">
+        <v>779</v>
+      </c>
+      <c r="C35" s="38" t="s">
+        <v>780</v>
+      </c>
+      <c r="D35" s="39">
+        <v>203</v>
+      </c>
+      <c r="F35" s="38" t="s">
+        <v>846</v>
+      </c>
+      <c r="G35" s="38" t="s">
+        <v>847</v>
+      </c>
+      <c r="H35" s="39">
+        <v>371</v>
+      </c>
+      <c r="J35" s="38" t="s">
+        <v>913</v>
+      </c>
+      <c r="K35" s="38" t="s">
+        <v>914</v>
+      </c>
+      <c r="L35" s="39">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="36" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B36" s="1" t="s">
+        <v>781</v>
+      </c>
+      <c r="C36" s="1" t="s">
+        <v>782</v>
+      </c>
+      <c r="D36" s="48">
+        <v>392</v>
+      </c>
+      <c r="F36" s="1" t="s">
+        <v>848</v>
+      </c>
+      <c r="G36" s="1" t="s">
+        <v>849</v>
+      </c>
+      <c r="H36" s="48">
+        <v>274</v>
+      </c>
+      <c r="J36" s="1" t="s">
+        <v>915</v>
+      </c>
+      <c r="K36" s="1" t="s">
+        <v>916</v>
+      </c>
+      <c r="L36" s="48">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="37" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B37" s="38" t="s">
+        <v>783</v>
+      </c>
+      <c r="C37" s="38" t="s">
+        <v>784</v>
+      </c>
+      <c r="D37" s="39">
+        <v>1958</v>
+      </c>
+      <c r="F37" s="38" t="s">
+        <v>850</v>
+      </c>
+      <c r="G37" s="38" t="s">
+        <v>851</v>
+      </c>
+      <c r="H37" s="39">
+        <v>7030</v>
+      </c>
+      <c r="J37" s="38" t="s">
+        <v>917</v>
+      </c>
+      <c r="K37" s="38" t="s">
+        <v>918</v>
+      </c>
+      <c r="L37" s="39">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="38" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B38" s="2" t="s">
+        <v>785</v>
+      </c>
+      <c r="C38" s="2" t="s">
+        <v>786</v>
+      </c>
+      <c r="D38" s="45">
+        <v>834</v>
+      </c>
+      <c r="E38" s="2"/>
+      <c r="F38" s="2" t="s">
+        <v>852</v>
+      </c>
+      <c r="G38" s="2" t="s">
+        <v>853</v>
+      </c>
+      <c r="H38" s="45">
+        <v>6897</v>
+      </c>
+      <c r="I38" s="2"/>
+      <c r="J38" s="2"/>
+      <c r="K38" s="2"/>
+      <c r="L38" s="44"/>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="B3:L3"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/new_tables.xlsx
+++ b/new_tables.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/maxsalvatore/Documents/projects/covid/new_cancer/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ED8E8BD2-3063-264F-B081-68FD5B39248D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A45EAF35-7E4D-5140-A729-B72E0E41157A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="17500" activeTab="5" xr2:uid="{23B5B348-4D99-B540-995F-50D24F235ACD}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="15940" windowHeight="18000" activeTab="4" xr2:uid="{23B5B348-4D99-B540-995F-50D24F235ACD}"/>
   </bookViews>
   <sheets>
     <sheet name="table 1" sheetId="1" r:id="rId1"/>
@@ -19,6 +19,7 @@
     <sheet name="table 4" sheetId="5" r:id="rId4"/>
     <sheet name="table 5" sheetId="4" r:id="rId5"/>
     <sheet name="cancer_counts" sheetId="6" r:id="rId6"/>
+    <sheet name="Sheet1" sheetId="7" r:id="rId7"/>
   </sheets>
   <calcPr calcId="181029"/>
   <extLst>
@@ -40,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1181" uniqueCount="923">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1176" uniqueCount="915">
   <si>
     <t>Age</t>
   </si>
@@ -660,51 +661,6 @@
     <t>Other / Non-Hispanic or Hispanic</t>
   </si>
   <si>
-    <t>35021 (10.1%)</t>
-  </si>
-  <si>
-    <t>29505 (10.0%)</t>
-  </si>
-  <si>
-    <t>5516 (10.4%)</t>
-  </si>
-  <si>
-    <t>365 (9.1%)</t>
-  </si>
-  <si>
-    <t>346 (9.5%)</t>
-  </si>
-  <si>
-    <t>86 (8.4%)</t>
-  </si>
-  <si>
-    <t>48 (7.4%)</t>
-  </si>
-  <si>
-    <t>Other / Unknown Ethnicity</t>
-  </si>
-  <si>
-    <t>22245 (6.4%)</t>
-  </si>
-  <si>
-    <t>19108 (6.5%)</t>
-  </si>
-  <si>
-    <t>3137 (5.9%)</t>
-  </si>
-  <si>
-    <t>195 (4.9%)</t>
-  </si>
-  <si>
-    <t>162 (4.4%)</t>
-  </si>
-  <si>
-    <t>81 (7.9%)</t>
-  </si>
-  <si>
-    <t>61 (9.3%)</t>
-  </si>
-  <si>
     <t>79134 (22.8%)</t>
   </si>
   <si>
@@ -1254,9 +1210,6 @@
     <t>Vaccination status</t>
   </si>
   <si>
-    <t>Boosted</t>
-  </si>
-  <si>
     <t>2786 (5.3%)</t>
   </si>
   <si>
@@ -1272,9 +1225,6 @@
     <t>14 (2.1%)</t>
   </si>
   <si>
-    <t>Fully vaccinated</t>
-  </si>
-  <si>
     <t>2136 (4.0%)</t>
   </si>
   <si>
@@ -1287,9 +1237,6 @@
     <t>2 (0.3%)</t>
   </si>
   <si>
-    <t>Partially vaccinated</t>
-  </si>
-  <si>
     <t>1453 (2.8%)</t>
   </si>
   <si>
@@ -1303,9 +1250,6 @@
   </si>
   <si>
     <t>3 (0.5%)</t>
-  </si>
-  <si>
-    <t>Unvaccinated/Unknown</t>
   </si>
   <si>
     <t>46318 (87.7%)</t>
@@ -1598,24 +1542,6 @@
     <t>1.98 (1.84, 2.12)</t>
   </si>
   <si>
-    <t>1.26 (1.17, 1.35)</t>
-  </si>
-  <si>
-    <t>1.22 (1.13, 1.32)</t>
-  </si>
-  <si>
-    <t>0.94 (0.81, 1.09)</t>
-  </si>
-  <si>
-    <t>1.31 (1.11, 1.54)</t>
-  </si>
-  <si>
-    <t>1.32 (1.21, 1.43)</t>
-  </si>
-  <si>
-    <t>1.30 (1.19, 1.41)</t>
-  </si>
-  <si>
     <t>0.96 (0.82, 1.12)</t>
   </si>
   <si>
@@ -1658,42 +1584,6 @@
     <t>4.79 (3.94, 5.79)</t>
   </si>
   <si>
-    <t>2.36 (2.15, 2.59)</t>
-  </si>
-  <si>
-    <t>2.35 (2.13, 2.58)</t>
-  </si>
-  <si>
-    <t>1.42 (1.18, 1.70)</t>
-  </si>
-  <si>
-    <t>1.90 (1.55, 2.32)</t>
-  </si>
-  <si>
-    <t>2.47 (2.23, 2.72)</t>
-  </si>
-  <si>
-    <t>2.49 (2.25, 2.76)</t>
-  </si>
-  <si>
-    <t>1.46 (1.20, 1.77)</t>
-  </si>
-  <si>
-    <t>1.80 (1.44, 2.23)</t>
-  </si>
-  <si>
-    <t>2.27 (2.04, 2.53)</t>
-  </si>
-  <si>
-    <t>2.34 (2.10, 2.62)</t>
-  </si>
-  <si>
-    <t>1.83 (1.47, 2.27)</t>
-  </si>
-  <si>
-    <t>1.63 (1.28, 2.06)</t>
-  </si>
-  <si>
     <t>Radiation only</t>
   </si>
   <si>
@@ -1727,39 +1617,15 @@
     <t>0.84 (0.58, 1.19)</t>
   </si>
   <si>
-    <t>0.78 (0.52, 1.13)</t>
-  </si>
-  <si>
     <t>0.64 (0.28, 1.25)</t>
   </si>
   <si>
     <t>1.18 (0.59, 2.12)</t>
   </si>
   <si>
-    <t>0.77 (0.49, 1.14)</t>
-  </si>
-  <si>
-    <t>0.70 (0.43, 1.07)</t>
-  </si>
-  <si>
-    <t>0.57 (0.21, 1.23)</t>
-  </si>
-  <si>
     <t>0.99 (0.43, 1.95)</t>
   </si>
   <si>
-    <t>0.80 (0.50, 1.21)</t>
-  </si>
-  <si>
-    <t>0.76 (0.45, 1.20)</t>
-  </si>
-  <si>
-    <t>0.74 (0.25, 1.70)</t>
-  </si>
-  <si>
-    <t>0.86 (0.32, 1.87)</t>
-  </si>
-  <si>
     <t>Surgery only</t>
   </si>
   <si>
@@ -1790,15 +1656,6 @@
     <t>1.56 (0.44, 3.88)</t>
   </si>
   <si>
-    <t>0.49 (0.29, 0.79)</t>
-  </si>
-  <si>
-    <t>0.49 (0.27, 0.81)</t>
-  </si>
-  <si>
-    <t>0.28 (0.06, 0.79)</t>
-  </si>
-  <si>
     <t>0.55 (0.15, 1.37)</t>
   </si>
   <si>
@@ -1815,12 +1672,6 @@
   </si>
   <si>
     <t>0.56 (0.30, 0.94)</t>
-  </si>
-  <si>
-    <t>0.55 (0.29, 0.96)</t>
-  </si>
-  <si>
-    <t>0.49 (0.10, 1.42)</t>
   </si>
   <si>
     <t>0.71 (0.20, 1.80)</t>
@@ -1880,39 +1731,18 @@
     <t>3.15 (2.20, 4.37)</t>
   </si>
   <si>
-    <t>1.02 (0.85, 1.21)</t>
-  </si>
-  <si>
-    <t>1.04 (0.86, 1.24)</t>
-  </si>
-  <si>
     <t>0.68 (0.46, 0.98)</t>
   </si>
   <si>
     <t>1.06 (0.74, 1.49)</t>
   </si>
   <si>
-    <t>1.11 (0.92, 1.33)</t>
-  </si>
-  <si>
-    <t>1.13 (0.93, 1.37)</t>
-  </si>
-  <si>
     <t>0.74 (0.49, 1.09)</t>
   </si>
   <si>
     <t>1.12 (0.76, 1.60)</t>
   </si>
   <si>
-    <t>1.11 (0.91, 1.34)</t>
-  </si>
-  <si>
-    <t>1.16 (0.95, 1.42)</t>
-  </si>
-  <si>
-    <t>0.96 (0.62, 1.43)</t>
-  </si>
-  <si>
     <t>1.08 (0.72, 1.56)</t>
   </si>
   <si>
@@ -1940,30 +1770,9 @@
     <t>3.96 (3.02, 5.13)</t>
   </si>
   <si>
-    <t>2.06 (1.81, 2.33)</t>
-  </si>
-  <si>
-    <t>2.00 (1.75, 2.27)</t>
-  </si>
-  <si>
-    <t>1.58 (1.24, 1.98)</t>
-  </si>
-  <si>
-    <t>1.97 (1.49, 2.57)</t>
-  </si>
-  <si>
-    <t>2.19 (1.91, 2.50)</t>
-  </si>
-  <si>
-    <t>2.14 (1.86, 2.46)</t>
-  </si>
-  <si>
     <t>1.62 (1.25, 2.07)</t>
   </si>
   <si>
-    <t>1.83 (1.35, 2.44)</t>
-  </si>
-  <si>
     <t>1.95 (1.69, 2.25)</t>
   </si>
   <si>
@@ -2015,9 +1824,6 @@
     <t>1.37 (0.90, 2.01)</t>
   </si>
   <si>
-    <t>1.23 (0.99, 1.51)</t>
-  </si>
-  <si>
     <t>1.26 (1.01, 1.56)</t>
   </si>
   <si>
@@ -2027,15 +1833,9 @@
     <t>1.43 (0.92, 2.14)</t>
   </si>
   <si>
-    <t>1.24 (0.99, 1.53)</t>
-  </si>
-  <si>
     <t>1.28 (1.02, 1.60)</t>
   </si>
   <si>
-    <t>1.45 (0.91, 2.20)</t>
-  </si>
-  <si>
     <t>1.47 (0.93, 2.24)</t>
   </si>
   <si>
@@ -2075,9 +1875,6 @@
     <t>0.47 (0.31, 0.68)</t>
   </si>
   <si>
-    <t>0.66 (0.44, 0.95)</t>
-  </si>
-  <si>
     <t>0.77 (0.63, 0.95)</t>
   </si>
   <si>
@@ -2090,9 +1887,6 @@
     <t>0.69 (0.45, 1.01)</t>
   </si>
   <si>
-    <t>0.89 (0.71, 1.11)</t>
-  </si>
-  <si>
     <t>0.85 (0.66, 1.07)</t>
   </si>
   <si>
@@ -2129,34 +1923,10 @@
     <t>6.93 (4.48, 10.27)</t>
   </si>
   <si>
-    <t>2.32 (1.85, 2.89)</t>
-  </si>
-  <si>
-    <t>2.19 (1.72, 2.76)</t>
-  </si>
-  <si>
-    <t>1.26 (0.78, 1.95)</t>
-  </si>
-  <si>
-    <t>2.07 (1.32, 3.10)</t>
-  </si>
-  <si>
-    <t>2.32 (1.81, 2.95)</t>
-  </si>
-  <si>
-    <t>2.34 (1.81, 3.01)</t>
-  </si>
-  <si>
     <t>1.24 (0.73, 1.98)</t>
   </si>
   <si>
-    <t>1.52 (0.89, 2.45)</t>
-  </si>
-  <si>
     <t>2.34 (1.81, 3.00)</t>
-  </si>
-  <si>
-    <t>2.41 (1.85, 3.12)</t>
   </si>
   <si>
     <t>1.61 (0.92, 2.61)</t>
@@ -2210,39 +1980,6 @@
     <t>4.59 (3.66, 5.71)</t>
   </si>
   <si>
-    <t>2.06 (1.85, 2.29)</t>
-  </si>
-  <si>
-    <t>2.06 (1.84, 2.31)</t>
-  </si>
-  <si>
-    <t>1.24 (0.99, 1.54)</t>
-  </si>
-  <si>
-    <t>1.72 (1.36, 2.17)</t>
-  </si>
-  <si>
-    <t>2.15 (1.91, 2.41)</t>
-  </si>
-  <si>
-    <t>2.19 (1.94, 2.47)</t>
-  </si>
-  <si>
-    <t>1.28 (1.00, 1.61)</t>
-  </si>
-  <si>
-    <t>1.64 (1.27, 2.10)</t>
-  </si>
-  <si>
-    <t>1.99 (1.75, 2.25)</t>
-  </si>
-  <si>
-    <t>2.08 (1.83, 2.36)</t>
-  </si>
-  <si>
-    <t>1.62 (1.25, 2.08)</t>
-  </si>
-  <si>
     <t>1.47 (1.12, 1.92)</t>
   </si>
   <si>
@@ -2252,9 +1989,6 @@
     <t>Outcome</t>
   </si>
   <si>
-    <t>Fully vaccinated and boosted</t>
-  </si>
-  <si>
     <t>Hospitalization</t>
   </si>
   <si>
@@ -2297,9 +2031,6 @@
     <t>0.57 (0.39, 0.80)</t>
   </si>
   <si>
-    <t>0.62 (0.42, 0.88)</t>
-  </si>
-  <si>
     <t>0.37 (0.12, 0.83)</t>
   </si>
   <si>
@@ -2337,9 +2068,6 @@
   </si>
   <si>
     <t>0.70 (0.52, 0.93)</t>
-  </si>
-  <si>
-    <t>0.51 (0.24, 0.92)</t>
   </si>
   <si>
     <t>0.11 (0.02, 0.30)</t>
@@ -3050,6 +2778,255 @@
       </rPr>
       <t>. Phecodes used to identify individuals with cancer, along with their phenotype description and the number of individuals in the tested positive cohort with the corresponding phecode.</t>
     </r>
+  </si>
+  <si>
+    <t>57266 (16.5%)</t>
+  </si>
+  <si>
+    <t>48613 (16.5%)</t>
+  </si>
+  <si>
+    <t>8653 (16.4%)</t>
+  </si>
+  <si>
+    <t>508 (13.9%)</t>
+  </si>
+  <si>
+    <t>167 (16.3%)</t>
+  </si>
+  <si>
+    <t>109 (16.7%)</t>
+  </si>
+  <si>
+    <t>560 (13.9%)</t>
+  </si>
+  <si>
+    <t>Prior to vaccination</t>
+  </si>
+  <si>
+    <t>After one dose</t>
+  </si>
+  <si>
+    <t>After two doses</t>
+  </si>
+  <si>
+    <t>After booster</t>
+  </si>
+  <si>
+    <t>1.26 (1.17, 1.36)</t>
+  </si>
+  <si>
+    <t>1.23 (1.14, 1.33)</t>
+  </si>
+  <si>
+    <t>0.94 (0.81, 1.08)</t>
+  </si>
+  <si>
+    <t>1.30 (1.11, 1.54)</t>
+  </si>
+  <si>
+    <t>1.32 (1.22, 1.43)</t>
+  </si>
+  <si>
+    <t>1.30 (1.20, 1.42)</t>
+  </si>
+  <si>
+    <t>2.38 (2.17, 2.61)</t>
+  </si>
+  <si>
+    <t>2.37 (2.15, 2.61)</t>
+  </si>
+  <si>
+    <t>1.41 (1.17, 1.69)</t>
+  </si>
+  <si>
+    <t>1.89 (1.54, 2.31)</t>
+  </si>
+  <si>
+    <t>2.49 (2.25, 2.75)</t>
+  </si>
+  <si>
+    <t>2.52 (2.27, 2.79)</t>
+  </si>
+  <si>
+    <t>1.45 (1.19, 1.76)</t>
+  </si>
+  <si>
+    <t>1.79 (1.44, 2.22)</t>
+  </si>
+  <si>
+    <t>2.28 (2.05, 2.54)</t>
+  </si>
+  <si>
+    <t>2.36 (2.11, 2.63)</t>
+  </si>
+  <si>
+    <t>1.84 (1.48, 2.28)</t>
+  </si>
+  <si>
+    <t>1.63 (1.29, 2.06)</t>
+  </si>
+  <si>
+    <t>0.78 (0.51, 1.13)</t>
+  </si>
+  <si>
+    <t>0.76 (0.49, 1.13)</t>
+  </si>
+  <si>
+    <t>0.69 (0.43, 1.07)</t>
+  </si>
+  <si>
+    <t>0.58 (0.22, 1.23)</t>
+  </si>
+  <si>
+    <t>0.79 (0.49, 1.20)</t>
+  </si>
+  <si>
+    <t>0.75 (0.45, 1.19)</t>
+  </si>
+  <si>
+    <t>0.74 (0.24, 1.69)</t>
+  </si>
+  <si>
+    <t>0.86 (0.32, 1.86)</t>
+  </si>
+  <si>
+    <t>0.50 (0.29, 0.80)</t>
+  </si>
+  <si>
+    <t>0.49 (0.28, 0.81)</t>
+  </si>
+  <si>
+    <t>0.28 (0.06, 0.78)</t>
+  </si>
+  <si>
+    <t>0.55 (0.29, 0.97)</t>
+  </si>
+  <si>
+    <t>0.50 (0.10, 1.42)</t>
+  </si>
+  <si>
+    <t>1.23 (1.00, 1.51)</t>
+  </si>
+  <si>
+    <t>1.23 (0.99, 1.53)</t>
+  </si>
+  <si>
+    <t>1.44 (0.90, 2.20)</t>
+  </si>
+  <si>
+    <t>2.07 (1.82, 2.35)</t>
+  </si>
+  <si>
+    <t>2.01 (1.76, 2.29)</t>
+  </si>
+  <si>
+    <t>1.57 (1.23, 1.98)</t>
+  </si>
+  <si>
+    <t>1.96 (1.48, 2.56)</t>
+  </si>
+  <si>
+    <t>2.20 (1.92, 2.51)</t>
+  </si>
+  <si>
+    <t>2.15 (1.87, 2.47)</t>
+  </si>
+  <si>
+    <t>1.83 (1.35, 2.43)</t>
+  </si>
+  <si>
+    <t>2.33 (1.85, 2.91)</t>
+  </si>
+  <si>
+    <t>2.20 (1.73, 2.77)</t>
+  </si>
+  <si>
+    <t>1.26 (0.77, 1.94)</t>
+  </si>
+  <si>
+    <t>2.06 (1.32, 3.09)</t>
+  </si>
+  <si>
+    <t>2.32 (1.81, 2.96)</t>
+  </si>
+  <si>
+    <t>2.35 (1.82, 3.01)</t>
+  </si>
+  <si>
+    <t>1.52 (0.89, 2.44)</t>
+  </si>
+  <si>
+    <t>2.41 (1.85, 3.11)</t>
+  </si>
+  <si>
+    <t>1.01 (0.85, 1.20)</t>
+  </si>
+  <si>
+    <t>1.03 (0.86, 1.24)</t>
+  </si>
+  <si>
+    <t>1.10 (0.91, 1.33)</t>
+  </si>
+  <si>
+    <t>1.13 (0.92, 1.36)</t>
+  </si>
+  <si>
+    <t>1.10 (0.90, 1.33)</t>
+  </si>
+  <si>
+    <t>1.15 (0.94, 1.41)</t>
+  </si>
+  <si>
+    <t>0.95 (0.61, 1.42)</t>
+  </si>
+  <si>
+    <t>0.66 (0.45, 0.95)</t>
+  </si>
+  <si>
+    <t>0.89 (0.71, 1.10)</t>
+  </si>
+  <si>
+    <t>0.30</t>
+  </si>
+  <si>
+    <t>0.63 (0.43, 0.89)</t>
+  </si>
+  <si>
+    <t>0.50 (0.24, 0.92)</t>
+  </si>
+  <si>
+    <t>2.08 (1.86, 2.31)</t>
+  </si>
+  <si>
+    <t>2.09 (1.86, 2.33)</t>
+  </si>
+  <si>
+    <t>1.23 (0.98, 1.52)</t>
+  </si>
+  <si>
+    <t>1.70 (1.35, 2.14)</t>
+  </si>
+  <si>
+    <t>2.17 (1.93, 2.43)</t>
+  </si>
+  <si>
+    <t>2.21 (1.96, 2.50)</t>
+  </si>
+  <si>
+    <t>1.27 (1.00, 1.60)</t>
+  </si>
+  <si>
+    <t>1.63 (1.26, 2.08)</t>
+  </si>
+  <si>
+    <t>2.00 (1.76, 2.26)</t>
+  </si>
+  <si>
+    <t>2.09 (1.84, 2.37)</t>
+  </si>
+  <si>
+    <t>1.63 (1.26, 2.10)</t>
   </si>
 </sst>
 </file>
@@ -3252,7 +3229,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="94">
+  <cellXfs count="95">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
@@ -3447,6 +3424,15 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
@@ -3458,15 +3444,6 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -3488,6 +3465,9 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -3803,7 +3783,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7B01937B-0672-F040-B465-F2242BC58BBF}">
-  <dimension ref="B2:I94"/>
+  <dimension ref="B2:I93"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="12" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="10.83203125" style="20"/>
@@ -3814,77 +3794,77 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:9" x14ac:dyDescent="0.15">
-      <c r="B2" s="84" t="s">
-        <v>449</v>
-      </c>
-      <c r="C2" s="84"/>
-      <c r="D2" s="84"/>
-      <c r="E2" s="84"/>
-      <c r="F2" s="84"/>
-      <c r="G2" s="84"/>
-      <c r="H2" s="84"/>
-      <c r="I2" s="84"/>
+      <c r="B2" s="80" t="s">
+        <v>430</v>
+      </c>
+      <c r="C2" s="80"/>
+      <c r="D2" s="80"/>
+      <c r="E2" s="80"/>
+      <c r="F2" s="80"/>
+      <c r="G2" s="80"/>
+      <c r="H2" s="80"/>
+      <c r="I2" s="80"/>
     </row>
     <row r="3" spans="2:9" x14ac:dyDescent="0.15">
       <c r="B3" s="4"/>
-      <c r="C3" s="81" t="s">
-        <v>445</v>
-      </c>
-      <c r="D3" s="81"/>
-      <c r="E3" s="81"/>
-      <c r="F3" s="82" t="s">
-        <v>446</v>
-      </c>
-      <c r="G3" s="83"/>
-      <c r="H3" s="83"/>
-      <c r="I3" s="83"/>
+      <c r="C3" s="84" t="s">
+        <v>426</v>
+      </c>
+      <c r="D3" s="84"/>
+      <c r="E3" s="84"/>
+      <c r="F3" s="85" t="s">
+        <v>427</v>
+      </c>
+      <c r="G3" s="86"/>
+      <c r="H3" s="86"/>
+      <c r="I3" s="86"/>
     </row>
     <row r="4" spans="2:9" x14ac:dyDescent="0.15">
       <c r="B4" s="4"/>
       <c r="C4" s="5" t="s">
-        <v>431</v>
+        <v>412</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>433</v>
+        <v>414</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>435</v>
+        <v>416</v>
       </c>
       <c r="F4" s="25" t="s">
-        <v>437</v>
+        <v>418</v>
       </c>
       <c r="G4" s="21" t="s">
-        <v>439</v>
+        <v>420</v>
       </c>
       <c r="H4" s="21" t="s">
-        <v>441</v>
+        <v>422</v>
       </c>
       <c r="I4" s="21" t="s">
-        <v>443</v>
+        <v>424</v>
       </c>
     </row>
     <row r="5" spans="2:9" x14ac:dyDescent="0.15">
       <c r="B5" s="6"/>
       <c r="C5" s="7" t="s">
-        <v>432</v>
+        <v>413</v>
       </c>
       <c r="D5" s="7" t="s">
-        <v>434</v>
+        <v>415</v>
       </c>
       <c r="E5" s="7" t="s">
-        <v>436</v>
+        <v>417</v>
       </c>
       <c r="F5" s="26" t="s">
-        <v>438</v>
+        <v>419</v>
       </c>
       <c r="G5" s="7" t="s">
-        <v>440</v>
+        <v>421</v>
       </c>
       <c r="H5" s="7" t="s">
-        <v>442</v>
+        <v>423</v>
       </c>
       <c r="I5" s="7" t="s">
-        <v>444</v>
+        <v>425</v>
       </c>
     </row>
     <row r="6" spans="2:9" x14ac:dyDescent="0.15">
@@ -4081,7 +4061,7 @@
     </row>
     <row r="15" spans="2:9" x14ac:dyDescent="0.15">
       <c r="B15" s="10" t="s">
-        <v>447</v>
+        <v>428</v>
       </c>
       <c r="C15" s="11" t="s">
         <v>50</v>
@@ -4107,7 +4087,7 @@
     </row>
     <row r="16" spans="2:9" x14ac:dyDescent="0.15">
       <c r="B16" s="10" t="s">
-        <v>448</v>
+        <v>429</v>
       </c>
       <c r="C16" s="11" t="s">
         <v>57</v>
@@ -4676,1219 +4656,1193 @@
         <v>205</v>
       </c>
       <c r="C41" s="11" t="s">
+        <v>832</v>
+      </c>
+      <c r="D41" s="11" t="s">
+        <v>833</v>
+      </c>
+      <c r="E41" s="11" t="s">
+        <v>834</v>
+      </c>
+      <c r="F41" s="28" t="s">
+        <v>838</v>
+      </c>
+      <c r="G41" s="23" t="s">
+        <v>835</v>
+      </c>
+      <c r="H41" s="23" t="s">
+        <v>836</v>
+      </c>
+      <c r="I41" s="23" t="s">
+        <v>837</v>
+      </c>
+    </row>
+    <row r="42" spans="2:9" ht="13" x14ac:dyDescent="0.15">
+      <c r="B42" s="12" t="s">
+        <v>436</v>
+      </c>
+      <c r="C42" s="13"/>
+      <c r="D42" s="13"/>
+      <c r="E42" s="13"/>
+      <c r="F42" s="29"/>
+      <c r="G42" s="24"/>
+      <c r="H42" s="24"/>
+      <c r="I42" s="24"/>
+    </row>
+    <row r="43" spans="2:9" x14ac:dyDescent="0.15">
+      <c r="B43" s="15">
+        <v>1</v>
+      </c>
+      <c r="C43" s="13" t="s">
         <v>206</v>
       </c>
-      <c r="D41" s="11" t="s">
+      <c r="D43" s="13" t="s">
         <v>207</v>
       </c>
-      <c r="E41" s="11" t="s">
+      <c r="E43" s="13" t="s">
         <v>208</v>
       </c>
-      <c r="F41" s="28" t="s">
+      <c r="F43" s="29" t="s">
         <v>209</v>
       </c>
-      <c r="G41" s="23" t="s">
+      <c r="G43" s="24" t="s">
         <v>210</v>
       </c>
-      <c r="H41" s="23" t="s">
+      <c r="H43" s="24" t="s">
         <v>211</v>
       </c>
-      <c r="I41" s="23" t="s">
+      <c r="I43" s="24" t="s">
         <v>212</v>
       </c>
-    </row>
-    <row r="42" spans="2:9" x14ac:dyDescent="0.15">
-      <c r="B42" s="10" t="s">
-        <v>213</v>
-      </c>
-      <c r="C42" s="11" t="s">
-        <v>214</v>
-      </c>
-      <c r="D42" s="11" t="s">
-        <v>215</v>
-      </c>
-      <c r="E42" s="11" t="s">
-        <v>216</v>
-      </c>
-      <c r="F42" s="28" t="s">
-        <v>217</v>
-      </c>
-      <c r="G42" s="23" t="s">
-        <v>218</v>
-      </c>
-      <c r="H42" s="23" t="s">
-        <v>219</v>
-      </c>
-      <c r="I42" s="23" t="s">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="43" spans="2:9" ht="13" x14ac:dyDescent="0.15">
-      <c r="B43" s="12" t="s">
-        <v>455</v>
-      </c>
-      <c r="C43" s="13"/>
-      <c r="D43" s="13"/>
-      <c r="E43" s="13"/>
-      <c r="F43" s="29"/>
-      <c r="G43" s="24"/>
-      <c r="H43" s="24"/>
-      <c r="I43" s="24"/>
     </row>
     <row r="44" spans="2:9" x14ac:dyDescent="0.15">
       <c r="B44" s="15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C44" s="13" t="s">
-        <v>221</v>
+        <v>213</v>
       </c>
       <c r="D44" s="13" t="s">
-        <v>222</v>
+        <v>214</v>
       </c>
       <c r="E44" s="13" t="s">
-        <v>223</v>
+        <v>215</v>
       </c>
       <c r="F44" s="29" t="s">
-        <v>224</v>
+        <v>216</v>
       </c>
       <c r="G44" s="24" t="s">
-        <v>225</v>
+        <v>217</v>
       </c>
       <c r="H44" s="24" t="s">
-        <v>226</v>
+        <v>218</v>
       </c>
       <c r="I44" s="24" t="s">
-        <v>227</v>
+        <v>219</v>
       </c>
     </row>
     <row r="45" spans="2:9" x14ac:dyDescent="0.15">
       <c r="B45" s="15">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C45" s="13" t="s">
-        <v>228</v>
+        <v>220</v>
       </c>
       <c r="D45" s="13" t="s">
-        <v>229</v>
+        <v>221</v>
       </c>
       <c r="E45" s="13" t="s">
-        <v>230</v>
+        <v>222</v>
       </c>
       <c r="F45" s="29" t="s">
-        <v>231</v>
+        <v>223</v>
       </c>
       <c r="G45" s="24" t="s">
-        <v>232</v>
+        <v>224</v>
       </c>
       <c r="H45" s="24" t="s">
-        <v>233</v>
+        <v>225</v>
       </c>
       <c r="I45" s="24" t="s">
-        <v>234</v>
+        <v>226</v>
       </c>
     </row>
     <row r="46" spans="2:9" x14ac:dyDescent="0.15">
       <c r="B46" s="15">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C46" s="13" t="s">
+        <v>227</v>
+      </c>
+      <c r="D46" s="13" t="s">
+        <v>228</v>
+      </c>
+      <c r="E46" s="13" t="s">
+        <v>229</v>
+      </c>
+      <c r="F46" s="29" t="s">
+        <v>230</v>
+      </c>
+      <c r="G46" s="24" t="s">
+        <v>231</v>
+      </c>
+      <c r="H46" s="24" t="s">
+        <v>232</v>
+      </c>
+      <c r="I46" s="24" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="47" spans="2:9" x14ac:dyDescent="0.15">
+      <c r="B47" s="15" t="s">
+        <v>96</v>
+      </c>
+      <c r="C47" s="13" t="s">
+        <v>233</v>
+      </c>
+      <c r="D47" s="13" t="s">
+        <v>234</v>
+      </c>
+      <c r="E47" s="13" t="s">
         <v>235</v>
       </c>
-      <c r="D46" s="13" t="s">
+      <c r="F47" s="29" t="s">
         <v>236</v>
       </c>
-      <c r="E46" s="13" t="s">
+      <c r="G47" s="24" t="s">
         <v>237</v>
       </c>
-      <c r="F46" s="29" t="s">
+      <c r="H47" s="24" t="s">
         <v>238</v>
       </c>
-      <c r="G46" s="24" t="s">
+      <c r="I47" s="24" t="s">
         <v>239</v>
       </c>
-      <c r="H46" s="24" t="s">
+    </row>
+    <row r="48" spans="2:9" ht="13" x14ac:dyDescent="0.15">
+      <c r="B48" s="8" t="s">
+        <v>439</v>
+      </c>
+      <c r="C48" s="11"/>
+      <c r="D48" s="11"/>
+      <c r="E48" s="11"/>
+      <c r="F48" s="28"/>
+      <c r="G48" s="23"/>
+      <c r="H48" s="23"/>
+      <c r="I48" s="23"/>
+    </row>
+    <row r="49" spans="2:9" x14ac:dyDescent="0.15">
+      <c r="B49" s="16">
+        <v>1</v>
+      </c>
+      <c r="C49" s="11" t="s">
         <v>240</v>
       </c>
-      <c r="I46" s="24" t="s">
+      <c r="D49" s="11" t="s">
         <v>241</v>
       </c>
-    </row>
-    <row r="47" spans="2:9" x14ac:dyDescent="0.15">
-      <c r="B47" s="15">
-        <v>4</v>
-      </c>
-      <c r="C47" s="13" t="s">
+      <c r="E49" s="11" t="s">
         <v>242</v>
       </c>
-      <c r="D47" s="13" t="s">
+      <c r="F49" s="28" t="s">
         <v>243</v>
       </c>
-      <c r="E47" s="13" t="s">
+      <c r="G49" s="23" t="s">
+        <v>171</v>
+      </c>
+      <c r="H49" s="23" t="s">
         <v>244</v>
       </c>
-      <c r="F47" s="29" t="s">
+      <c r="I49" s="23" t="s">
         <v>245</v>
       </c>
-      <c r="G47" s="24" t="s">
-        <v>246</v>
-      </c>
-      <c r="H47" s="24" t="s">
-        <v>247</v>
-      </c>
-      <c r="I47" s="24" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="48" spans="2:9" x14ac:dyDescent="0.15">
-      <c r="B48" s="15" t="s">
-        <v>96</v>
-      </c>
-      <c r="C48" s="13" t="s">
-        <v>248</v>
-      </c>
-      <c r="D48" s="13" t="s">
-        <v>249</v>
-      </c>
-      <c r="E48" s="13" t="s">
-        <v>250</v>
-      </c>
-      <c r="F48" s="29" t="s">
-        <v>251</v>
-      </c>
-      <c r="G48" s="24" t="s">
-        <v>252</v>
-      </c>
-      <c r="H48" s="24" t="s">
-        <v>253</v>
-      </c>
-      <c r="I48" s="24" t="s">
-        <v>254</v>
-      </c>
-    </row>
-    <row r="49" spans="2:9" ht="13" x14ac:dyDescent="0.15">
-      <c r="B49" s="8" t="s">
-        <v>458</v>
-      </c>
-      <c r="C49" s="11"/>
-      <c r="D49" s="11"/>
-      <c r="E49" s="11"/>
-      <c r="F49" s="28"/>
-      <c r="G49" s="23"/>
-      <c r="H49" s="23"/>
-      <c r="I49" s="23"/>
     </row>
     <row r="50" spans="2:9" x14ac:dyDescent="0.15">
       <c r="B50" s="16">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C50" s="11" t="s">
-        <v>255</v>
+        <v>246</v>
       </c>
       <c r="D50" s="11" t="s">
-        <v>256</v>
+        <v>247</v>
       </c>
       <c r="E50" s="11" t="s">
-        <v>257</v>
+        <v>248</v>
       </c>
       <c r="F50" s="28" t="s">
-        <v>258</v>
+        <v>249</v>
       </c>
       <c r="G50" s="23" t="s">
-        <v>171</v>
+        <v>250</v>
       </c>
       <c r="H50" s="23" t="s">
-        <v>259</v>
+        <v>251</v>
       </c>
       <c r="I50" s="23" t="s">
-        <v>260</v>
+        <v>252</v>
       </c>
     </row>
     <row r="51" spans="2:9" x14ac:dyDescent="0.15">
       <c r="B51" s="16">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C51" s="11" t="s">
-        <v>261</v>
+        <v>253</v>
       </c>
       <c r="D51" s="11" t="s">
-        <v>262</v>
+        <v>254</v>
       </c>
       <c r="E51" s="11" t="s">
-        <v>263</v>
+        <v>255</v>
       </c>
       <c r="F51" s="28" t="s">
-        <v>264</v>
+        <v>201</v>
       </c>
       <c r="G51" s="23" t="s">
-        <v>265</v>
+        <v>256</v>
       </c>
       <c r="H51" s="23" t="s">
-        <v>266</v>
+        <v>257</v>
       </c>
       <c r="I51" s="23" t="s">
-        <v>267</v>
+        <v>258</v>
       </c>
     </row>
     <row r="52" spans="2:9" x14ac:dyDescent="0.15">
       <c r="B52" s="16">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C52" s="11" t="s">
+        <v>259</v>
+      </c>
+      <c r="D52" s="11" t="s">
+        <v>260</v>
+      </c>
+      <c r="E52" s="11" t="s">
+        <v>261</v>
+      </c>
+      <c r="F52" s="28" t="s">
+        <v>262</v>
+      </c>
+      <c r="G52" s="23" t="s">
+        <v>263</v>
+      </c>
+      <c r="H52" s="23" t="s">
+        <v>264</v>
+      </c>
+      <c r="I52" s="23" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="53" spans="2:9" x14ac:dyDescent="0.15">
+      <c r="B53" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="C53" s="11" t="s">
+        <v>233</v>
+      </c>
+      <c r="D53" s="11" t="s">
+        <v>234</v>
+      </c>
+      <c r="E53" s="11" t="s">
+        <v>235</v>
+      </c>
+      <c r="F53" s="28" t="s">
+        <v>236</v>
+      </c>
+      <c r="G53" s="23" t="s">
+        <v>237</v>
+      </c>
+      <c r="H53" s="23" t="s">
+        <v>238</v>
+      </c>
+      <c r="I53" s="23" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="54" spans="2:9" ht="13" x14ac:dyDescent="0.15">
+      <c r="B54" s="12" t="s">
+        <v>440</v>
+      </c>
+      <c r="C54" s="13"/>
+      <c r="D54" s="13"/>
+      <c r="E54" s="13"/>
+      <c r="F54" s="29"/>
+      <c r="G54" s="24"/>
+      <c r="H54" s="24"/>
+      <c r="I54" s="24"/>
+    </row>
+    <row r="55" spans="2:9" x14ac:dyDescent="0.15">
+      <c r="B55" s="15">
+        <v>1</v>
+      </c>
+      <c r="C55" s="13" t="s">
+        <v>266</v>
+      </c>
+      <c r="D55" s="13" t="s">
+        <v>267</v>
+      </c>
+      <c r="E55" s="13" t="s">
         <v>268</v>
       </c>
-      <c r="D52" s="11" t="s">
+      <c r="F55" s="29" t="s">
         <v>269</v>
       </c>
-      <c r="E52" s="11" t="s">
+      <c r="G55" s="24" t="s">
         <v>270</v>
       </c>
-      <c r="F52" s="28" t="s">
-        <v>201</v>
-      </c>
-      <c r="G52" s="23" t="s">
+      <c r="H55" s="24" t="s">
         <v>271</v>
       </c>
-      <c r="H52" s="23" t="s">
+      <c r="I55" s="24" t="s">
         <v>272</v>
       </c>
-      <c r="I52" s="23" t="s">
-        <v>273</v>
-      </c>
-    </row>
-    <row r="53" spans="2:9" x14ac:dyDescent="0.15">
-      <c r="B53" s="16">
-        <v>4</v>
-      </c>
-      <c r="C53" s="11" t="s">
-        <v>274</v>
-      </c>
-      <c r="D53" s="11" t="s">
-        <v>275</v>
-      </c>
-      <c r="E53" s="11" t="s">
-        <v>276</v>
-      </c>
-      <c r="F53" s="28" t="s">
-        <v>277</v>
-      </c>
-      <c r="G53" s="23" t="s">
-        <v>278</v>
-      </c>
-      <c r="H53" s="23" t="s">
-        <v>279</v>
-      </c>
-      <c r="I53" s="23" t="s">
-        <v>280</v>
-      </c>
-    </row>
-    <row r="54" spans="2:9" x14ac:dyDescent="0.15">
-      <c r="B54" s="16" t="s">
-        <v>96</v>
-      </c>
-      <c r="C54" s="11" t="s">
-        <v>248</v>
-      </c>
-      <c r="D54" s="11" t="s">
-        <v>249</v>
-      </c>
-      <c r="E54" s="11" t="s">
-        <v>250</v>
-      </c>
-      <c r="F54" s="28" t="s">
-        <v>251</v>
-      </c>
-      <c r="G54" s="23" t="s">
-        <v>252</v>
-      </c>
-      <c r="H54" s="23" t="s">
-        <v>253</v>
-      </c>
-      <c r="I54" s="23" t="s">
-        <v>254</v>
-      </c>
-    </row>
-    <row r="55" spans="2:9" ht="13" x14ac:dyDescent="0.15">
-      <c r="B55" s="12" t="s">
-        <v>459</v>
-      </c>
-      <c r="C55" s="13"/>
-      <c r="D55" s="13"/>
-      <c r="E55" s="13"/>
-      <c r="F55" s="29"/>
-      <c r="G55" s="24"/>
-      <c r="H55" s="24"/>
-      <c r="I55" s="24"/>
     </row>
     <row r="56" spans="2:9" x14ac:dyDescent="0.15">
       <c r="B56" s="15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C56" s="13" t="s">
-        <v>281</v>
+        <v>273</v>
       </c>
       <c r="D56" s="13" t="s">
-        <v>282</v>
+        <v>274</v>
       </c>
       <c r="E56" s="13" t="s">
-        <v>283</v>
+        <v>275</v>
       </c>
       <c r="F56" s="29" t="s">
-        <v>284</v>
+        <v>276</v>
       </c>
       <c r="G56" s="24" t="s">
-        <v>285</v>
+        <v>277</v>
       </c>
       <c r="H56" s="24" t="s">
-        <v>286</v>
+        <v>278</v>
       </c>
       <c r="I56" s="24" t="s">
-        <v>287</v>
+        <v>279</v>
       </c>
     </row>
     <row r="57" spans="2:9" x14ac:dyDescent="0.15">
       <c r="B57" s="15">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C57" s="13" t="s">
-        <v>288</v>
+        <v>280</v>
       </c>
       <c r="D57" s="13" t="s">
-        <v>289</v>
+        <v>281</v>
       </c>
       <c r="E57" s="13" t="s">
-        <v>290</v>
+        <v>282</v>
       </c>
       <c r="F57" s="29" t="s">
-        <v>291</v>
+        <v>283</v>
       </c>
       <c r="G57" s="24" t="s">
-        <v>292</v>
+        <v>284</v>
       </c>
       <c r="H57" s="24" t="s">
-        <v>293</v>
+        <v>285</v>
       </c>
       <c r="I57" s="24" t="s">
-        <v>294</v>
+        <v>286</v>
       </c>
     </row>
     <row r="58" spans="2:9" x14ac:dyDescent="0.15">
       <c r="B58" s="15">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C58" s="13" t="s">
+        <v>287</v>
+      </c>
+      <c r="D58" s="13" t="s">
+        <v>288</v>
+      </c>
+      <c r="E58" s="13" t="s">
+        <v>289</v>
+      </c>
+      <c r="F58" s="29" t="s">
+        <v>290</v>
+      </c>
+      <c r="G58" s="24" t="s">
+        <v>171</v>
+      </c>
+      <c r="H58" s="24" t="s">
+        <v>291</v>
+      </c>
+      <c r="I58" s="24" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="59" spans="2:9" x14ac:dyDescent="0.15">
+      <c r="B59" s="15" t="s">
+        <v>96</v>
+      </c>
+      <c r="C59" s="13" t="s">
+        <v>233</v>
+      </c>
+      <c r="D59" s="13" t="s">
+        <v>234</v>
+      </c>
+      <c r="E59" s="13" t="s">
+        <v>235</v>
+      </c>
+      <c r="F59" s="29" t="s">
+        <v>236</v>
+      </c>
+      <c r="G59" s="24" t="s">
+        <v>237</v>
+      </c>
+      <c r="H59" s="24" t="s">
+        <v>238</v>
+      </c>
+      <c r="I59" s="24" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="60" spans="2:9" ht="13" x14ac:dyDescent="0.15">
+      <c r="B60" s="8" t="s">
+        <v>437</v>
+      </c>
+      <c r="C60" s="11"/>
+      <c r="D60" s="11"/>
+      <c r="E60" s="11"/>
+      <c r="F60" s="28"/>
+      <c r="G60" s="23"/>
+      <c r="H60" s="23"/>
+      <c r="I60" s="23"/>
+    </row>
+    <row r="61" spans="2:9" x14ac:dyDescent="0.15">
+      <c r="B61" s="16">
+        <v>1</v>
+      </c>
+      <c r="C61" s="11" t="s">
+        <v>292</v>
+      </c>
+      <c r="D61" s="11" t="s">
+        <v>293</v>
+      </c>
+      <c r="E61" s="11" t="s">
+        <v>294</v>
+      </c>
+      <c r="F61" s="28" t="s">
         <v>295</v>
       </c>
-      <c r="D58" s="13" t="s">
+      <c r="G61" s="23" t="s">
         <v>296</v>
       </c>
-      <c r="E58" s="13" t="s">
+      <c r="H61" s="23" t="s">
         <v>297</v>
       </c>
-      <c r="F58" s="29" t="s">
+      <c r="I61" s="23" t="s">
         <v>298</v>
       </c>
-      <c r="G58" s="24" t="s">
-        <v>299</v>
-      </c>
-      <c r="H58" s="24" t="s">
-        <v>300</v>
-      </c>
-      <c r="I58" s="24" t="s">
-        <v>301</v>
-      </c>
-    </row>
-    <row r="59" spans="2:9" x14ac:dyDescent="0.15">
-      <c r="B59" s="15">
-        <v>4</v>
-      </c>
-      <c r="C59" s="13" t="s">
-        <v>302</v>
-      </c>
-      <c r="D59" s="13" t="s">
-        <v>303</v>
-      </c>
-      <c r="E59" s="13" t="s">
-        <v>304</v>
-      </c>
-      <c r="F59" s="29" t="s">
-        <v>305</v>
-      </c>
-      <c r="G59" s="24" t="s">
-        <v>171</v>
-      </c>
-      <c r="H59" s="24" t="s">
-        <v>306</v>
-      </c>
-      <c r="I59" s="24" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="60" spans="2:9" x14ac:dyDescent="0.15">
-      <c r="B60" s="15" t="s">
-        <v>96</v>
-      </c>
-      <c r="C60" s="13" t="s">
-        <v>248</v>
-      </c>
-      <c r="D60" s="13" t="s">
-        <v>249</v>
-      </c>
-      <c r="E60" s="13" t="s">
-        <v>250</v>
-      </c>
-      <c r="F60" s="29" t="s">
-        <v>251</v>
-      </c>
-      <c r="G60" s="24" t="s">
-        <v>252</v>
-      </c>
-      <c r="H60" s="24" t="s">
-        <v>253</v>
-      </c>
-      <c r="I60" s="24" t="s">
-        <v>254</v>
-      </c>
-    </row>
-    <row r="61" spans="2:9" ht="13" x14ac:dyDescent="0.15">
-      <c r="B61" s="8" t="s">
-        <v>456</v>
-      </c>
-      <c r="C61" s="11"/>
-      <c r="D61" s="11"/>
-      <c r="E61" s="11"/>
-      <c r="F61" s="28"/>
-      <c r="G61" s="23"/>
-      <c r="H61" s="23"/>
-      <c r="I61" s="23"/>
     </row>
     <row r="62" spans="2:9" x14ac:dyDescent="0.15">
       <c r="B62" s="16">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C62" s="11" t="s">
-        <v>307</v>
+        <v>299</v>
       </c>
       <c r="D62" s="11" t="s">
-        <v>308</v>
+        <v>300</v>
       </c>
       <c r="E62" s="11" t="s">
-        <v>309</v>
+        <v>301</v>
       </c>
       <c r="F62" s="28" t="s">
-        <v>310</v>
+        <v>302</v>
       </c>
       <c r="G62" s="23" t="s">
-        <v>311</v>
+        <v>303</v>
       </c>
       <c r="H62" s="23" t="s">
-        <v>312</v>
+        <v>304</v>
       </c>
       <c r="I62" s="23" t="s">
-        <v>313</v>
+        <v>305</v>
       </c>
     </row>
     <row r="63" spans="2:9" x14ac:dyDescent="0.15">
       <c r="B63" s="16">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C63" s="11" t="s">
-        <v>314</v>
+        <v>306</v>
       </c>
       <c r="D63" s="11" t="s">
-        <v>315</v>
+        <v>307</v>
       </c>
       <c r="E63" s="11" t="s">
-        <v>316</v>
+        <v>308</v>
       </c>
       <c r="F63" s="28" t="s">
-        <v>317</v>
+        <v>309</v>
       </c>
       <c r="G63" s="23" t="s">
-        <v>318</v>
+        <v>310</v>
       </c>
       <c r="H63" s="23" t="s">
-        <v>319</v>
+        <v>164</v>
       </c>
       <c r="I63" s="23" t="s">
-        <v>320</v>
+        <v>311</v>
       </c>
     </row>
     <row r="64" spans="2:9" x14ac:dyDescent="0.15">
       <c r="B64" s="16">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C64" s="11" t="s">
+        <v>312</v>
+      </c>
+      <c r="D64" s="11" t="s">
+        <v>313</v>
+      </c>
+      <c r="E64" s="11" t="s">
+        <v>314</v>
+      </c>
+      <c r="F64" s="28" t="s">
+        <v>315</v>
+      </c>
+      <c r="G64" s="23" t="s">
+        <v>316</v>
+      </c>
+      <c r="H64" s="23" t="s">
+        <v>317</v>
+      </c>
+      <c r="I64" s="23" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="65" spans="2:9" x14ac:dyDescent="0.15">
+      <c r="B65" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="C65" s="11" t="s">
+        <v>233</v>
+      </c>
+      <c r="D65" s="11" t="s">
+        <v>234</v>
+      </c>
+      <c r="E65" s="11" t="s">
+        <v>235</v>
+      </c>
+      <c r="F65" s="28" t="s">
+        <v>236</v>
+      </c>
+      <c r="G65" s="23" t="s">
+        <v>237</v>
+      </c>
+      <c r="H65" s="23" t="s">
+        <v>238</v>
+      </c>
+      <c r="I65" s="23" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="66" spans="2:9" ht="13" x14ac:dyDescent="0.15">
+      <c r="B66" s="17" t="s">
+        <v>438</v>
+      </c>
+      <c r="C66" s="13"/>
+      <c r="D66" s="13"/>
+      <c r="E66" s="13"/>
+      <c r="F66" s="29"/>
+      <c r="G66" s="24"/>
+      <c r="H66" s="24"/>
+      <c r="I66" s="24"/>
+    </row>
+    <row r="67" spans="2:9" x14ac:dyDescent="0.15">
+      <c r="B67" s="15">
+        <v>1</v>
+      </c>
+      <c r="C67" s="13" t="s">
+        <v>319</v>
+      </c>
+      <c r="D67" s="13" t="s">
+        <v>320</v>
+      </c>
+      <c r="E67" s="13" t="s">
         <v>321</v>
       </c>
-      <c r="D64" s="11" t="s">
+      <c r="F67" s="29" t="s">
         <v>322</v>
       </c>
-      <c r="E64" s="11" t="s">
+      <c r="G67" s="24" t="s">
         <v>323</v>
       </c>
-      <c r="F64" s="28" t="s">
+      <c r="H67" s="24" t="s">
         <v>324</v>
       </c>
-      <c r="G64" s="23" t="s">
+      <c r="I67" s="24" t="s">
         <v>325</v>
       </c>
-      <c r="H64" s="23" t="s">
-        <v>164</v>
-      </c>
-      <c r="I64" s="23" t="s">
-        <v>326</v>
-      </c>
-    </row>
-    <row r="65" spans="2:9" x14ac:dyDescent="0.15">
-      <c r="B65" s="16">
-        <v>4</v>
-      </c>
-      <c r="C65" s="11" t="s">
-        <v>327</v>
-      </c>
-      <c r="D65" s="11" t="s">
-        <v>328</v>
-      </c>
-      <c r="E65" s="11" t="s">
-        <v>329</v>
-      </c>
-      <c r="F65" s="28" t="s">
-        <v>330</v>
-      </c>
-      <c r="G65" s="23" t="s">
-        <v>331</v>
-      </c>
-      <c r="H65" s="23" t="s">
-        <v>332</v>
-      </c>
-      <c r="I65" s="23" t="s">
-        <v>333</v>
-      </c>
-    </row>
-    <row r="66" spans="2:9" x14ac:dyDescent="0.15">
-      <c r="B66" s="16" t="s">
-        <v>96</v>
-      </c>
-      <c r="C66" s="11" t="s">
-        <v>248</v>
-      </c>
-      <c r="D66" s="11" t="s">
-        <v>249</v>
-      </c>
-      <c r="E66" s="11" t="s">
-        <v>250</v>
-      </c>
-      <c r="F66" s="28" t="s">
-        <v>251</v>
-      </c>
-      <c r="G66" s="23" t="s">
-        <v>252</v>
-      </c>
-      <c r="H66" s="23" t="s">
-        <v>253</v>
-      </c>
-      <c r="I66" s="23" t="s">
-        <v>254</v>
-      </c>
-    </row>
-    <row r="67" spans="2:9" ht="13" x14ac:dyDescent="0.15">
-      <c r="B67" s="17" t="s">
-        <v>457</v>
-      </c>
-      <c r="C67" s="13"/>
-      <c r="D67" s="13"/>
-      <c r="E67" s="13"/>
-      <c r="F67" s="29"/>
-      <c r="G67" s="24"/>
-      <c r="H67" s="24"/>
-      <c r="I67" s="24"/>
     </row>
     <row r="68" spans="2:9" x14ac:dyDescent="0.15">
       <c r="B68" s="15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C68" s="13" t="s">
-        <v>334</v>
+        <v>326</v>
       </c>
       <c r="D68" s="13" t="s">
-        <v>335</v>
+        <v>327</v>
       </c>
       <c r="E68" s="13" t="s">
-        <v>336</v>
+        <v>328</v>
       </c>
       <c r="F68" s="29" t="s">
-        <v>337</v>
+        <v>329</v>
       </c>
       <c r="G68" s="24" t="s">
-        <v>338</v>
+        <v>330</v>
       </c>
       <c r="H68" s="24" t="s">
-        <v>339</v>
+        <v>331</v>
       </c>
       <c r="I68" s="24" t="s">
-        <v>340</v>
+        <v>332</v>
       </c>
     </row>
     <row r="69" spans="2:9" x14ac:dyDescent="0.15">
       <c r="B69" s="15">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C69" s="13" t="s">
-        <v>341</v>
+        <v>333</v>
       </c>
       <c r="D69" s="13" t="s">
-        <v>342</v>
+        <v>334</v>
       </c>
       <c r="E69" s="13" t="s">
-        <v>343</v>
+        <v>335</v>
       </c>
       <c r="F69" s="29" t="s">
-        <v>344</v>
+        <v>336</v>
       </c>
       <c r="G69" s="24" t="s">
-        <v>345</v>
+        <v>22</v>
       </c>
       <c r="H69" s="24" t="s">
-        <v>346</v>
+        <v>337</v>
       </c>
       <c r="I69" s="24" t="s">
-        <v>347</v>
+        <v>338</v>
       </c>
     </row>
     <row r="70" spans="2:9" x14ac:dyDescent="0.15">
       <c r="B70" s="15">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C70" s="13" t="s">
+        <v>339</v>
+      </c>
+      <c r="D70" s="13" t="s">
+        <v>340</v>
+      </c>
+      <c r="E70" s="13" t="s">
+        <v>341</v>
+      </c>
+      <c r="F70" s="29" t="s">
+        <v>342</v>
+      </c>
+      <c r="G70" s="24" t="s">
+        <v>343</v>
+      </c>
+      <c r="H70" s="24" t="s">
+        <v>344</v>
+      </c>
+      <c r="I70" s="24" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="71" spans="2:9" x14ac:dyDescent="0.15">
+      <c r="B71" s="15" t="s">
+        <v>96</v>
+      </c>
+      <c r="C71" s="13" t="s">
+        <v>233</v>
+      </c>
+      <c r="D71" s="13" t="s">
+        <v>234</v>
+      </c>
+      <c r="E71" s="13" t="s">
+        <v>235</v>
+      </c>
+      <c r="F71" s="29" t="s">
+        <v>236</v>
+      </c>
+      <c r="G71" s="24" t="s">
+        <v>237</v>
+      </c>
+      <c r="H71" s="24" t="s">
+        <v>238</v>
+      </c>
+      <c r="I71" s="24" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="72" spans="2:9" ht="13" x14ac:dyDescent="0.15">
+      <c r="B72" s="8" t="s">
+        <v>441</v>
+      </c>
+      <c r="C72" s="11"/>
+      <c r="D72" s="11"/>
+      <c r="E72" s="11"/>
+      <c r="F72" s="28"/>
+      <c r="G72" s="23"/>
+      <c r="H72" s="23"/>
+      <c r="I72" s="23"/>
+    </row>
+    <row r="73" spans="2:9" x14ac:dyDescent="0.15">
+      <c r="B73" s="10" t="s">
+        <v>1</v>
+      </c>
+      <c r="C73" s="11" t="s">
+        <v>346</v>
+      </c>
+      <c r="D73" s="11" t="s">
+        <v>347</v>
+      </c>
+      <c r="E73" s="11" t="s">
         <v>348</v>
       </c>
-      <c r="D70" s="13" t="s">
+      <c r="F73" s="28" t="s">
         <v>349</v>
       </c>
-      <c r="E70" s="13" t="s">
+      <c r="G73" s="23" t="s">
         <v>350</v>
       </c>
-      <c r="F70" s="29" t="s">
+      <c r="H73" s="23" t="s">
         <v>351</v>
       </c>
-      <c r="G70" s="24" t="s">
-        <v>22</v>
-      </c>
-      <c r="H70" s="24" t="s">
+      <c r="I73" s="23" t="s">
         <v>352</v>
       </c>
-      <c r="I70" s="24" t="s">
-        <v>353</v>
-      </c>
-    </row>
-    <row r="71" spans="2:9" x14ac:dyDescent="0.15">
-      <c r="B71" s="15">
-        <v>4</v>
-      </c>
-      <c r="C71" s="13" t="s">
-        <v>354</v>
-      </c>
-      <c r="D71" s="13" t="s">
-        <v>355</v>
-      </c>
-      <c r="E71" s="13" t="s">
-        <v>356</v>
-      </c>
-      <c r="F71" s="29" t="s">
-        <v>357</v>
-      </c>
-      <c r="G71" s="24" t="s">
-        <v>358</v>
-      </c>
-      <c r="H71" s="24" t="s">
-        <v>359</v>
-      </c>
-      <c r="I71" s="24" t="s">
-        <v>360</v>
-      </c>
-    </row>
-    <row r="72" spans="2:9" x14ac:dyDescent="0.15">
-      <c r="B72" s="15" t="s">
-        <v>96</v>
-      </c>
-      <c r="C72" s="13" t="s">
-        <v>248</v>
-      </c>
-      <c r="D72" s="13" t="s">
-        <v>249</v>
-      </c>
-      <c r="E72" s="13" t="s">
-        <v>250</v>
-      </c>
-      <c r="F72" s="29" t="s">
-        <v>251</v>
-      </c>
-      <c r="G72" s="24" t="s">
-        <v>252</v>
-      </c>
-      <c r="H72" s="24" t="s">
-        <v>253</v>
-      </c>
-      <c r="I72" s="24" t="s">
-        <v>254</v>
-      </c>
-    </row>
-    <row r="73" spans="2:9" ht="13" x14ac:dyDescent="0.15">
-      <c r="B73" s="8" t="s">
-        <v>460</v>
-      </c>
-      <c r="C73" s="11"/>
-      <c r="D73" s="11"/>
-      <c r="E73" s="11"/>
-      <c r="F73" s="28"/>
-      <c r="G73" s="23"/>
-      <c r="H73" s="23"/>
-      <c r="I73" s="23"/>
     </row>
     <row r="74" spans="2:9" x14ac:dyDescent="0.15">
       <c r="B74" s="10" t="s">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="C74" s="11" t="s">
-        <v>361</v>
+        <v>353</v>
       </c>
       <c r="D74" s="11" t="s">
-        <v>362</v>
+        <v>353</v>
       </c>
       <c r="E74" s="11" t="s">
-        <v>363</v>
+        <v>354</v>
       </c>
       <c r="F74" s="28" t="s">
-        <v>364</v>
+        <v>355</v>
       </c>
       <c r="G74" s="23" t="s">
-        <v>365</v>
+        <v>355</v>
       </c>
       <c r="H74" s="23" t="s">
-        <v>366</v>
+        <v>355</v>
       </c>
       <c r="I74" s="23" t="s">
-        <v>367</v>
+        <v>355</v>
       </c>
     </row>
     <row r="75" spans="2:9" x14ac:dyDescent="0.15">
       <c r="B75" s="10" t="s">
-        <v>9</v>
+        <v>96</v>
       </c>
       <c r="C75" s="11" t="s">
+        <v>356</v>
+      </c>
+      <c r="D75" s="11" t="s">
+        <v>357</v>
+      </c>
+      <c r="E75" s="11" t="s">
+        <v>358</v>
+      </c>
+      <c r="F75" s="28" t="s">
+        <v>359</v>
+      </c>
+      <c r="G75" s="23" t="s">
+        <v>360</v>
+      </c>
+      <c r="H75" s="23" t="s">
+        <v>361</v>
+      </c>
+      <c r="I75" s="23" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="76" spans="2:9" x14ac:dyDescent="0.15">
+      <c r="B76" s="12" t="s">
+        <v>363</v>
+      </c>
+      <c r="C76" s="13"/>
+      <c r="D76" s="13"/>
+      <c r="E76" s="13"/>
+      <c r="F76" s="29"/>
+      <c r="G76" s="24"/>
+      <c r="H76" s="24"/>
+      <c r="I76" s="24"/>
+    </row>
+    <row r="77" spans="2:9" x14ac:dyDescent="0.15">
+      <c r="B77" s="14" t="s">
+        <v>73</v>
+      </c>
+      <c r="C77" s="13" t="s">
+        <v>364</v>
+      </c>
+      <c r="D77" s="13" t="s">
+        <v>365</v>
+      </c>
+      <c r="E77" s="13" t="s">
+        <v>366</v>
+      </c>
+      <c r="F77" s="29" t="s">
+        <v>367</v>
+      </c>
+      <c r="G77" s="24" t="s">
         <v>368</v>
       </c>
-      <c r="D75" s="11" t="s">
-        <v>368</v>
-      </c>
-      <c r="E75" s="11" t="s">
+      <c r="H77" s="24" t="s">
         <v>369</v>
       </c>
-      <c r="F75" s="28" t="s">
+      <c r="I77" s="24" t="s">
         <v>370</v>
       </c>
-      <c r="G75" s="23" t="s">
-        <v>370</v>
-      </c>
-      <c r="H75" s="23" t="s">
-        <v>370</v>
-      </c>
-      <c r="I75" s="23" t="s">
-        <v>370</v>
-      </c>
-    </row>
-    <row r="76" spans="2:9" x14ac:dyDescent="0.15">
-      <c r="B76" s="10" t="s">
-        <v>96</v>
-      </c>
-      <c r="C76" s="11" t="s">
-        <v>371</v>
-      </c>
-      <c r="D76" s="11" t="s">
-        <v>372</v>
-      </c>
-      <c r="E76" s="11" t="s">
-        <v>373</v>
-      </c>
-      <c r="F76" s="28" t="s">
-        <v>374</v>
-      </c>
-      <c r="G76" s="23" t="s">
-        <v>375</v>
-      </c>
-      <c r="H76" s="23" t="s">
-        <v>376</v>
-      </c>
-      <c r="I76" s="23" t="s">
-        <v>377</v>
-      </c>
-    </row>
-    <row r="77" spans="2:9" x14ac:dyDescent="0.15">
-      <c r="B77" s="12" t="s">
-        <v>378</v>
-      </c>
-      <c r="C77" s="13"/>
-      <c r="D77" s="13"/>
-      <c r="E77" s="13"/>
-      <c r="F77" s="29"/>
-      <c r="G77" s="24"/>
-      <c r="H77" s="24"/>
-      <c r="I77" s="24"/>
     </row>
     <row r="78" spans="2:9" x14ac:dyDescent="0.15">
       <c r="B78" s="14" t="s">
+        <v>65</v>
+      </c>
+      <c r="C78" s="13" t="s">
+        <v>371</v>
+      </c>
+      <c r="D78" s="13" t="s">
+        <v>372</v>
+      </c>
+      <c r="E78" s="13" t="s">
+        <v>373</v>
+      </c>
+      <c r="F78" s="29" t="s">
+        <v>374</v>
+      </c>
+      <c r="G78" s="24" t="s">
+        <v>375</v>
+      </c>
+      <c r="H78" s="24" t="s">
+        <v>376</v>
+      </c>
+      <c r="I78" s="24" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="79" spans="2:9" x14ac:dyDescent="0.15">
+      <c r="B79" s="8" t="s">
+        <v>378</v>
+      </c>
+      <c r="C79" s="11"/>
+      <c r="D79" s="11"/>
+      <c r="E79" s="11"/>
+      <c r="F79" s="28"/>
+      <c r="G79" s="23"/>
+      <c r="H79" s="23"/>
+      <c r="I79" s="23"/>
+    </row>
+    <row r="80" spans="2:9" x14ac:dyDescent="0.15">
+      <c r="B80" s="10" t="s">
         <v>73</v>
       </c>
-      <c r="C78" s="13" t="s">
-        <v>379</v>
-      </c>
-      <c r="D78" s="13" t="s">
+      <c r="C80" s="11" t="s">
+        <v>588</v>
+      </c>
+      <c r="D80" s="11" t="s">
+        <v>588</v>
+      </c>
+      <c r="E80" s="11" t="s">
         <v>380</v>
       </c>
-      <c r="E78" s="13" t="s">
+      <c r="F80" s="28" t="s">
         <v>381</v>
       </c>
-      <c r="F78" s="29" t="s">
-        <v>382</v>
-      </c>
-      <c r="G78" s="24" t="s">
-        <v>383</v>
-      </c>
-      <c r="H78" s="24" t="s">
-        <v>384</v>
-      </c>
-      <c r="I78" s="24" t="s">
-        <v>385</v>
-      </c>
-    </row>
-    <row r="79" spans="2:9" x14ac:dyDescent="0.15">
-      <c r="B79" s="14" t="s">
-        <v>65</v>
-      </c>
-      <c r="C79" s="13" t="s">
-        <v>386</v>
-      </c>
-      <c r="D79" s="13" t="s">
-        <v>387</v>
-      </c>
-      <c r="E79" s="13" t="s">
-        <v>388</v>
-      </c>
-      <c r="F79" s="29" t="s">
-        <v>389</v>
-      </c>
-      <c r="G79" s="24" t="s">
-        <v>390</v>
-      </c>
-      <c r="H79" s="24" t="s">
-        <v>391</v>
-      </c>
-      <c r="I79" s="24" t="s">
-        <v>392</v>
-      </c>
-    </row>
-    <row r="80" spans="2:9" x14ac:dyDescent="0.15">
-      <c r="B80" s="8" t="s">
-        <v>393</v>
-      </c>
-      <c r="C80" s="11"/>
-      <c r="D80" s="11"/>
-      <c r="E80" s="11"/>
-      <c r="F80" s="28"/>
-      <c r="G80" s="23"/>
-      <c r="H80" s="23"/>
-      <c r="I80" s="23"/>
+      <c r="G80" s="23" t="s">
+        <v>202</v>
+      </c>
+      <c r="H80" s="23" t="s">
+        <v>238</v>
+      </c>
+      <c r="I80" s="23" t="s">
+        <v>325</v>
+      </c>
     </row>
     <row r="81" spans="2:9" x14ac:dyDescent="0.15">
       <c r="B81" s="10" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="C81" s="11" t="s">
-        <v>676</v>
+        <v>588</v>
       </c>
       <c r="D81" s="11" t="s">
-        <v>676</v>
+        <v>588</v>
       </c>
       <c r="E81" s="11" t="s">
-        <v>395</v>
+        <v>382</v>
       </c>
       <c r="F81" s="28" t="s">
-        <v>396</v>
+        <v>383</v>
       </c>
       <c r="G81" s="23" t="s">
-        <v>202</v>
+        <v>384</v>
       </c>
       <c r="H81" s="23" t="s">
-        <v>253</v>
+        <v>385</v>
       </c>
       <c r="I81" s="23" t="s">
-        <v>340</v>
+        <v>386</v>
       </c>
     </row>
     <row r="82" spans="2:9" x14ac:dyDescent="0.15">
       <c r="B82" s="10" t="s">
-        <v>65</v>
+        <v>96</v>
       </c>
       <c r="C82" s="11" t="s">
-        <v>676</v>
+        <v>588</v>
       </c>
       <c r="D82" s="11" t="s">
-        <v>676</v>
+        <v>588</v>
       </c>
       <c r="E82" s="11" t="s">
-        <v>397</v>
+        <v>387</v>
       </c>
       <c r="F82" s="28" t="s">
-        <v>398</v>
+        <v>379</v>
       </c>
       <c r="G82" s="23" t="s">
-        <v>399</v>
+        <v>379</v>
       </c>
       <c r="H82" s="23" t="s">
-        <v>400</v>
+        <v>379</v>
       </c>
       <c r="I82" s="23" t="s">
-        <v>401</v>
+        <v>379</v>
       </c>
     </row>
     <row r="83" spans="2:9" x14ac:dyDescent="0.15">
-      <c r="B83" s="10" t="s">
-        <v>96</v>
-      </c>
-      <c r="C83" s="11" t="s">
-        <v>676</v>
-      </c>
-      <c r="D83" s="11" t="s">
-        <v>676</v>
-      </c>
-      <c r="E83" s="11" t="s">
-        <v>402</v>
-      </c>
-      <c r="F83" s="28" t="s">
-        <v>394</v>
-      </c>
-      <c r="G83" s="23" t="s">
-        <v>394</v>
-      </c>
-      <c r="H83" s="23" t="s">
-        <v>394</v>
-      </c>
-      <c r="I83" s="23" t="s">
-        <v>394</v>
-      </c>
+      <c r="B83" s="12" t="s">
+        <v>388</v>
+      </c>
+      <c r="C83" s="13"/>
+      <c r="D83" s="13"/>
+      <c r="E83" s="13"/>
+      <c r="F83" s="29"/>
+      <c r="G83" s="24"/>
+      <c r="H83" s="24"/>
+      <c r="I83" s="24"/>
     </row>
     <row r="84" spans="2:9" x14ac:dyDescent="0.15">
-      <c r="B84" s="12" t="s">
-        <v>403</v>
-      </c>
-      <c r="C84" s="13"/>
-      <c r="D84" s="13"/>
-      <c r="E84" s="13"/>
-      <c r="F84" s="29"/>
-      <c r="G84" s="24"/>
-      <c r="H84" s="24"/>
-      <c r="I84" s="24"/>
+      <c r="B84" s="14" t="s">
+        <v>842</v>
+      </c>
+      <c r="C84" s="13" t="s">
+        <v>588</v>
+      </c>
+      <c r="D84" s="13" t="s">
+        <v>588</v>
+      </c>
+      <c r="E84" s="13" t="s">
+        <v>389</v>
+      </c>
+      <c r="F84" s="29" t="s">
+        <v>390</v>
+      </c>
+      <c r="G84" s="24" t="s">
+        <v>391</v>
+      </c>
+      <c r="H84" s="24" t="s">
+        <v>392</v>
+      </c>
+      <c r="I84" s="24" t="s">
+        <v>393</v>
+      </c>
     </row>
     <row r="85" spans="2:9" x14ac:dyDescent="0.15">
       <c r="B85" s="14" t="s">
-        <v>404</v>
+        <v>841</v>
       </c>
       <c r="C85" s="13" t="s">
-        <v>676</v>
+        <v>588</v>
       </c>
       <c r="D85" s="13" t="s">
-        <v>676</v>
+        <v>588</v>
       </c>
       <c r="E85" s="13" t="s">
-        <v>405</v>
+        <v>394</v>
       </c>
       <c r="F85" s="29" t="s">
-        <v>406</v>
+        <v>390</v>
       </c>
       <c r="G85" s="24" t="s">
-        <v>407</v>
+        <v>395</v>
       </c>
       <c r="H85" s="24" t="s">
-        <v>408</v>
+        <v>396</v>
       </c>
       <c r="I85" s="24" t="s">
-        <v>409</v>
+        <v>397</v>
       </c>
     </row>
     <row r="86" spans="2:9" x14ac:dyDescent="0.15">
       <c r="B86" s="14" t="s">
-        <v>410</v>
+        <v>840</v>
       </c>
       <c r="C86" s="13" t="s">
-        <v>676</v>
+        <v>588</v>
       </c>
       <c r="D86" s="13" t="s">
-        <v>676</v>
+        <v>588</v>
       </c>
       <c r="E86" s="13" t="s">
-        <v>411</v>
+        <v>398</v>
       </c>
       <c r="F86" s="29" t="s">
-        <v>406</v>
+        <v>399</v>
       </c>
       <c r="G86" s="24" t="s">
-        <v>412</v>
+        <v>400</v>
       </c>
       <c r="H86" s="24" t="s">
-        <v>413</v>
+        <v>401</v>
       </c>
       <c r="I86" s="24" t="s">
-        <v>414</v>
+        <v>402</v>
       </c>
     </row>
     <row r="87" spans="2:9" x14ac:dyDescent="0.15">
       <c r="B87" s="14" t="s">
-        <v>415</v>
+        <v>839</v>
       </c>
       <c r="C87" s="13" t="s">
-        <v>676</v>
+        <v>588</v>
       </c>
       <c r="D87" s="13" t="s">
-        <v>676</v>
+        <v>588</v>
       </c>
       <c r="E87" s="13" t="s">
-        <v>416</v>
+        <v>403</v>
       </c>
       <c r="F87" s="29" t="s">
-        <v>417</v>
+        <v>404</v>
       </c>
       <c r="G87" s="24" t="s">
-        <v>418</v>
+        <v>405</v>
       </c>
       <c r="H87" s="24" t="s">
-        <v>419</v>
+        <v>406</v>
       </c>
       <c r="I87" s="24" t="s">
-        <v>420</v>
+        <v>407</v>
       </c>
     </row>
     <row r="88" spans="2:9" x14ac:dyDescent="0.15">
-      <c r="B88" s="14" t="s">
-        <v>421</v>
-      </c>
-      <c r="C88" s="13" t="s">
-        <v>676</v>
-      </c>
-      <c r="D88" s="13" t="s">
-        <v>676</v>
-      </c>
-      <c r="E88" s="13" t="s">
-        <v>422</v>
-      </c>
-      <c r="F88" s="29" t="s">
-        <v>423</v>
-      </c>
-      <c r="G88" s="24" t="s">
-        <v>424</v>
-      </c>
-      <c r="H88" s="24" t="s">
-        <v>425</v>
-      </c>
-      <c r="I88" s="24" t="s">
-        <v>426</v>
+      <c r="B88" s="18" t="s">
+        <v>96</v>
+      </c>
+      <c r="C88" s="19" t="s">
+        <v>588</v>
+      </c>
+      <c r="D88" s="19" t="s">
+        <v>588</v>
+      </c>
+      <c r="E88" s="19" t="s">
+        <v>408</v>
+      </c>
+      <c r="F88" s="30" t="s">
+        <v>409</v>
+      </c>
+      <c r="G88" s="19" t="s">
+        <v>410</v>
+      </c>
+      <c r="H88" s="19" t="s">
+        <v>411</v>
+      </c>
+      <c r="I88" s="19" t="s">
+        <v>379</v>
       </c>
     </row>
     <row r="89" spans="2:9" x14ac:dyDescent="0.15">
-      <c r="B89" s="18" t="s">
-        <v>96</v>
-      </c>
-      <c r="C89" s="19" t="s">
-        <v>676</v>
-      </c>
-      <c r="D89" s="19" t="s">
-        <v>676</v>
-      </c>
-      <c r="E89" s="19" t="s">
-        <v>427</v>
-      </c>
-      <c r="F89" s="30" t="s">
-        <v>428</v>
-      </c>
-      <c r="G89" s="19" t="s">
-        <v>429</v>
-      </c>
-      <c r="H89" s="19" t="s">
-        <v>430</v>
-      </c>
-      <c r="I89" s="19" t="s">
-        <v>394</v>
-      </c>
-    </row>
-    <row r="90" spans="2:9" x14ac:dyDescent="0.15">
-      <c r="B90" s="85" t="s">
-        <v>450</v>
-      </c>
-      <c r="C90" s="85"/>
-      <c r="D90" s="85"/>
-      <c r="E90" s="85"/>
-      <c r="F90" s="85"/>
-      <c r="G90" s="85"/>
-      <c r="H90" s="85"/>
-      <c r="I90" s="85"/>
-    </row>
-    <row r="91" spans="2:9" ht="13" x14ac:dyDescent="0.15">
-      <c r="B91" s="86" t="s">
-        <v>451</v>
-      </c>
-      <c r="C91" s="86"/>
-      <c r="D91" s="86"/>
-      <c r="E91" s="86"/>
-      <c r="F91" s="86"/>
-      <c r="G91" s="86"/>
-      <c r="H91" s="86"/>
-      <c r="I91" s="86"/>
-    </row>
-    <row r="92" spans="2:9" ht="37" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B92" s="80" t="s">
-        <v>452</v>
-      </c>
-      <c r="C92" s="80"/>
-      <c r="D92" s="80"/>
-      <c r="E92" s="80"/>
-      <c r="F92" s="80"/>
-      <c r="G92" s="80"/>
-      <c r="H92" s="80"/>
-      <c r="I92" s="80"/>
-    </row>
-    <row r="93" spans="2:9" ht="26" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B93" s="80" t="s">
-        <v>453</v>
-      </c>
-      <c r="C93" s="80"/>
-      <c r="D93" s="80"/>
-      <c r="E93" s="80"/>
-      <c r="F93" s="80"/>
-      <c r="G93" s="80"/>
-      <c r="H93" s="80"/>
-      <c r="I93" s="80"/>
-    </row>
-    <row r="94" spans="2:9" ht="25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B94" s="80" t="s">
-        <v>454</v>
-      </c>
-      <c r="C94" s="80"/>
-      <c r="D94" s="80"/>
-      <c r="E94" s="80"/>
-      <c r="F94" s="80"/>
-      <c r="G94" s="80"/>
-      <c r="H94" s="80"/>
-      <c r="I94" s="80"/>
+      <c r="B89" s="81" t="s">
+        <v>431</v>
+      </c>
+      <c r="C89" s="81"/>
+      <c r="D89" s="81"/>
+      <c r="E89" s="81"/>
+      <c r="F89" s="81"/>
+      <c r="G89" s="81"/>
+      <c r="H89" s="81"/>
+      <c r="I89" s="81"/>
+    </row>
+    <row r="90" spans="2:9" ht="13" x14ac:dyDescent="0.15">
+      <c r="B90" s="82" t="s">
+        <v>432</v>
+      </c>
+      <c r="C90" s="82"/>
+      <c r="D90" s="82"/>
+      <c r="E90" s="82"/>
+      <c r="F90" s="82"/>
+      <c r="G90" s="82"/>
+      <c r="H90" s="82"/>
+      <c r="I90" s="82"/>
+    </row>
+    <row r="91" spans="2:9" ht="37" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B91" s="83" t="s">
+        <v>433</v>
+      </c>
+      <c r="C91" s="83"/>
+      <c r="D91" s="83"/>
+      <c r="E91" s="83"/>
+      <c r="F91" s="83"/>
+      <c r="G91" s="83"/>
+      <c r="H91" s="83"/>
+      <c r="I91" s="83"/>
+    </row>
+    <row r="92" spans="2:9" ht="26" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B92" s="83" t="s">
+        <v>434</v>
+      </c>
+      <c r="C92" s="83"/>
+      <c r="D92" s="83"/>
+      <c r="E92" s="83"/>
+      <c r="F92" s="83"/>
+      <c r="G92" s="83"/>
+      <c r="H92" s="83"/>
+      <c r="I92" s="83"/>
+    </row>
+    <row r="93" spans="2:9" ht="25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B93" s="83" t="s">
+        <v>435</v>
+      </c>
+      <c r="C93" s="83"/>
+      <c r="D93" s="83"/>
+      <c r="E93" s="83"/>
+      <c r="F93" s="83"/>
+      <c r="G93" s="83"/>
+      <c r="H93" s="83"/>
+      <c r="I93" s="83"/>
     </row>
   </sheetData>
   <mergeCells count="8">
+    <mergeCell ref="B93:I93"/>
+    <mergeCell ref="C3:E3"/>
+    <mergeCell ref="F3:I3"/>
     <mergeCell ref="B2:I2"/>
+    <mergeCell ref="B89:I89"/>
     <mergeCell ref="B90:I90"/>
     <mergeCell ref="B91:I91"/>
     <mergeCell ref="B92:I92"/>
-    <mergeCell ref="B93:I93"/>
-    <mergeCell ref="B94:I94"/>
-    <mergeCell ref="C3:E3"/>
-    <mergeCell ref="F3:I3"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -5911,7 +5865,7 @@
   <sheetData>
     <row r="2" spans="2:10" ht="32" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B2" s="89" t="s">
-        <v>718</v>
+        <v>627</v>
       </c>
       <c r="C2" s="89"/>
       <c r="D2" s="89"/>
@@ -5924,47 +5878,47 @@
     </row>
     <row r="3" spans="2:10" x14ac:dyDescent="0.2">
       <c r="D3" s="87" t="s">
-        <v>549</v>
+        <v>499</v>
       </c>
       <c r="E3" s="88"/>
       <c r="F3" s="88"/>
       <c r="G3" s="88"/>
       <c r="H3" s="31"/>
       <c r="I3" s="88" t="s">
-        <v>552</v>
+        <v>502</v>
       </c>
       <c r="J3" s="88"/>
     </row>
     <row r="4" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B4" s="32" t="s">
-        <v>550</v>
+        <v>500</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>461</v>
+        <v>442</v>
       </c>
       <c r="D4" s="51" t="s">
-        <v>437</v>
+        <v>418</v>
       </c>
       <c r="E4" s="33" t="s">
-        <v>439</v>
+        <v>420</v>
       </c>
       <c r="F4" s="33" t="s">
-        <v>441</v>
+        <v>422</v>
       </c>
       <c r="G4" s="33" t="s">
-        <v>443</v>
+        <v>424</v>
       </c>
       <c r="H4" s="32"/>
       <c r="I4" s="33" t="s">
-        <v>550</v>
+        <v>500</v>
       </c>
       <c r="J4" s="33" t="s">
-        <v>551</v>
+        <v>501</v>
       </c>
     </row>
     <row r="5" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B5" s="34" t="s">
-        <v>378</v>
+        <v>363</v>
       </c>
       <c r="C5" s="35"/>
       <c r="D5" s="36"/>
@@ -5977,22 +5931,22 @@
     </row>
     <row r="6" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B6" s="37" t="s">
-        <v>544</v>
+        <v>494</v>
       </c>
       <c r="C6" s="38" t="s">
-        <v>462</v>
+        <v>443</v>
       </c>
       <c r="D6" s="52" t="s">
-        <v>463</v>
+        <v>444</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>464</v>
+        <v>445</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>465</v>
+        <v>446</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>466</v>
+        <v>447</v>
       </c>
       <c r="H6" s="38"/>
       <c r="I6" s="39">
@@ -6004,22 +5958,22 @@
     </row>
     <row r="7" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B7" s="37" t="s">
-        <v>545</v>
+        <v>495</v>
       </c>
       <c r="C7" s="38" t="s">
-        <v>462</v>
+        <v>443</v>
       </c>
       <c r="D7" s="52" t="s">
-        <v>463</v>
+        <v>444</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>467</v>
+        <v>448</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>465</v>
+        <v>446</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>466</v>
+        <v>447</v>
       </c>
       <c r="H7" s="38"/>
       <c r="I7" s="39">
@@ -6031,22 +5985,22 @@
     </row>
     <row r="8" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B8" s="37" t="s">
-        <v>546</v>
+        <v>496</v>
       </c>
       <c r="C8" s="38" t="s">
-        <v>462</v>
+        <v>443</v>
       </c>
       <c r="D8" s="52" t="s">
-        <v>468</v>
+        <v>843</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>469</v>
+        <v>844</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>470</v>
+        <v>845</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>471</v>
+        <v>846</v>
       </c>
       <c r="H8" s="38"/>
       <c r="I8" s="39">
@@ -6058,22 +6012,22 @@
     </row>
     <row r="9" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B9" s="37" t="s">
-        <v>547</v>
+        <v>497</v>
       </c>
       <c r="C9" s="38" t="s">
-        <v>462</v>
+        <v>443</v>
       </c>
       <c r="D9" s="52" t="s">
-        <v>472</v>
+        <v>847</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>473</v>
+        <v>848</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>474</v>
+        <v>449</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>475</v>
+        <v>450</v>
       </c>
       <c r="H9" s="38"/>
       <c r="I9" s="39">
@@ -6085,22 +6039,22 @@
     </row>
     <row r="10" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B10" s="40" t="s">
-        <v>548</v>
+        <v>498</v>
       </c>
       <c r="C10" s="41" t="s">
-        <v>462</v>
+        <v>443</v>
       </c>
       <c r="D10" s="53" t="s">
-        <v>476</v>
+        <v>451</v>
       </c>
       <c r="E10" s="42" t="s">
-        <v>477</v>
+        <v>452</v>
       </c>
       <c r="F10" s="42" t="s">
-        <v>478</v>
+        <v>453</v>
       </c>
       <c r="G10" s="42" t="s">
-        <v>479</v>
+        <v>454</v>
       </c>
       <c r="H10" s="41"/>
       <c r="I10" s="43">
@@ -6112,7 +6066,7 @@
     </row>
     <row r="11" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B11" s="32" t="s">
-        <v>480</v>
+        <v>455</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" s="44"/>
@@ -6125,22 +6079,22 @@
     </row>
     <row r="12" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B12" s="46" t="s">
-        <v>544</v>
+        <v>494</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>480</v>
+        <v>455</v>
       </c>
       <c r="D12" s="54" t="s">
-        <v>481</v>
+        <v>456</v>
       </c>
       <c r="E12" s="47" t="s">
-        <v>482</v>
+        <v>457</v>
       </c>
       <c r="F12" s="47" t="s">
-        <v>483</v>
+        <v>458</v>
       </c>
       <c r="G12" s="47" t="s">
-        <v>484</v>
+        <v>459</v>
       </c>
       <c r="I12" s="48">
         <v>4613</v>
@@ -6151,22 +6105,22 @@
     </row>
     <row r="13" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B13" s="46" t="s">
-        <v>545</v>
+        <v>495</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>480</v>
+        <v>455</v>
       </c>
       <c r="D13" s="54" t="s">
-        <v>481</v>
+        <v>456</v>
       </c>
       <c r="E13" s="47" t="s">
-        <v>485</v>
+        <v>460</v>
       </c>
       <c r="F13" s="47" t="s">
-        <v>486</v>
+        <v>461</v>
       </c>
       <c r="G13" s="47" t="s">
-        <v>487</v>
+        <v>462</v>
       </c>
       <c r="I13" s="48">
         <v>4613</v>
@@ -6177,22 +6131,22 @@
     </row>
     <row r="14" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B14" s="46" t="s">
-        <v>546</v>
+        <v>496</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>480</v>
+        <v>455</v>
       </c>
       <c r="D14" s="54" t="s">
-        <v>488</v>
+        <v>849</v>
       </c>
       <c r="E14" s="47" t="s">
-        <v>489</v>
+        <v>850</v>
       </c>
       <c r="F14" s="47" t="s">
-        <v>490</v>
+        <v>851</v>
       </c>
       <c r="G14" s="47" t="s">
-        <v>491</v>
+        <v>852</v>
       </c>
       <c r="I14" s="48">
         <v>4613</v>
@@ -6203,22 +6157,22 @@
     </row>
     <row r="15" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B15" s="46" t="s">
-        <v>547</v>
+        <v>497</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>480</v>
+        <v>455</v>
       </c>
       <c r="D15" s="54" t="s">
-        <v>492</v>
+        <v>853</v>
       </c>
       <c r="E15" s="47" t="s">
-        <v>493</v>
+        <v>854</v>
       </c>
       <c r="F15" s="47" t="s">
-        <v>494</v>
+        <v>855</v>
       </c>
       <c r="G15" s="47" t="s">
-        <v>495</v>
+        <v>856</v>
       </c>
       <c r="I15" s="48">
         <v>4129</v>
@@ -6229,22 +6183,22 @@
     </row>
     <row r="16" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B16" s="49" t="s">
-        <v>548</v>
+        <v>498</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>480</v>
+        <v>455</v>
       </c>
       <c r="D16" s="55" t="s">
-        <v>496</v>
+        <v>857</v>
       </c>
       <c r="E16" s="44" t="s">
-        <v>497</v>
+        <v>858</v>
       </c>
       <c r="F16" s="44" t="s">
-        <v>498</v>
+        <v>859</v>
       </c>
       <c r="G16" s="44" t="s">
-        <v>499</v>
+        <v>860</v>
       </c>
       <c r="H16" s="2"/>
       <c r="I16" s="45">
@@ -6256,7 +6210,7 @@
     </row>
     <row r="17" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B17" s="50" t="s">
-        <v>500</v>
+        <v>463</v>
       </c>
       <c r="C17" s="41"/>
       <c r="D17" s="42"/>
@@ -6269,22 +6223,22 @@
     </row>
     <row r="18" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B18" s="37" t="s">
-        <v>544</v>
+        <v>494</v>
       </c>
       <c r="C18" s="38" t="s">
-        <v>501</v>
+        <v>464</v>
       </c>
       <c r="D18" s="52" t="s">
-        <v>502</v>
+        <v>465</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>503</v>
+        <v>466</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>504</v>
+        <v>467</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>505</v>
+        <v>468</v>
       </c>
       <c r="H18" s="38"/>
       <c r="I18" s="39">
@@ -6296,22 +6250,22 @@
     </row>
     <row r="19" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B19" s="37" t="s">
-        <v>545</v>
+        <v>495</v>
       </c>
       <c r="C19" s="38" t="s">
-        <v>501</v>
+        <v>464</v>
       </c>
       <c r="D19" s="52" t="s">
-        <v>506</v>
+        <v>469</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>507</v>
+        <v>470</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>508</v>
+        <v>471</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>509</v>
+        <v>472</v>
       </c>
       <c r="H19" s="38"/>
       <c r="I19" s="39">
@@ -6323,22 +6277,22 @@
     </row>
     <row r="20" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B20" s="37" t="s">
-        <v>546</v>
+        <v>496</v>
       </c>
       <c r="C20" s="38" t="s">
-        <v>501</v>
+        <v>464</v>
       </c>
       <c r="D20" s="52" t="s">
-        <v>510</v>
+        <v>473</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>511</v>
+        <v>861</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>512</v>
+        <v>474</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>513</v>
+        <v>475</v>
       </c>
       <c r="H20" s="38"/>
       <c r="I20" s="39">
@@ -6350,22 +6304,22 @@
     </row>
     <row r="21" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B21" s="37" t="s">
-        <v>547</v>
+        <v>497</v>
       </c>
       <c r="C21" s="38" t="s">
-        <v>501</v>
+        <v>464</v>
       </c>
       <c r="D21" s="52" t="s">
-        <v>514</v>
+        <v>862</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>515</v>
+        <v>863</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>516</v>
+        <v>864</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>517</v>
+        <v>476</v>
       </c>
       <c r="H21" s="38"/>
       <c r="I21" s="39">
@@ -6377,22 +6331,22 @@
     </row>
     <row r="22" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B22" s="40" t="s">
-        <v>548</v>
+        <v>498</v>
       </c>
       <c r="C22" s="41" t="s">
-        <v>501</v>
+        <v>464</v>
       </c>
       <c r="D22" s="53" t="s">
-        <v>518</v>
+        <v>865</v>
       </c>
       <c r="E22" s="42" t="s">
-        <v>519</v>
+        <v>866</v>
       </c>
       <c r="F22" s="42" t="s">
-        <v>520</v>
+        <v>867</v>
       </c>
       <c r="G22" s="42" t="s">
-        <v>521</v>
+        <v>868</v>
       </c>
       <c r="H22" s="41"/>
       <c r="I22" s="43">
@@ -6404,7 +6358,7 @@
     </row>
     <row r="23" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B23" s="32" t="s">
-        <v>522</v>
+        <v>477</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" s="44"/>
@@ -6417,22 +6371,22 @@
     </row>
     <row r="24" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B24" s="46" t="s">
-        <v>544</v>
+        <v>494</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>523</v>
+        <v>478</v>
       </c>
       <c r="D24" s="54" t="s">
-        <v>524</v>
+        <v>479</v>
       </c>
       <c r="E24" s="47" t="s">
-        <v>525</v>
+        <v>480</v>
       </c>
       <c r="F24" s="47" t="s">
-        <v>526</v>
+        <v>481</v>
       </c>
       <c r="G24" s="47" t="s">
-        <v>527</v>
+        <v>482</v>
       </c>
       <c r="I24" s="48">
         <v>267</v>
@@ -6443,22 +6397,22 @@
     </row>
     <row r="25" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B25" s="46" t="s">
-        <v>545</v>
+        <v>495</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>523</v>
+        <v>478</v>
       </c>
       <c r="D25" s="54" t="s">
-        <v>528</v>
+        <v>483</v>
       </c>
       <c r="E25" s="47" t="s">
-        <v>529</v>
+        <v>484</v>
       </c>
       <c r="F25" s="47" t="s">
-        <v>530</v>
+        <v>485</v>
       </c>
       <c r="G25" s="47" t="s">
-        <v>531</v>
+        <v>486</v>
       </c>
       <c r="I25" s="48">
         <v>267</v>
@@ -6469,22 +6423,22 @@
     </row>
     <row r="26" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B26" s="46" t="s">
-        <v>546</v>
+        <v>496</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>523</v>
+        <v>478</v>
       </c>
       <c r="D26" s="54" t="s">
-        <v>532</v>
+        <v>869</v>
       </c>
       <c r="E26" s="47" t="s">
-        <v>533</v>
+        <v>870</v>
       </c>
       <c r="F26" s="47" t="s">
-        <v>534</v>
+        <v>871</v>
       </c>
       <c r="G26" s="47" t="s">
-        <v>535</v>
+        <v>487</v>
       </c>
       <c r="I26" s="48">
         <v>267</v>
@@ -6495,22 +6449,22 @@
     </row>
     <row r="27" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B27" s="46" t="s">
-        <v>547</v>
+        <v>497</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>523</v>
+        <v>478</v>
       </c>
       <c r="D27" s="54" t="s">
-        <v>536</v>
+        <v>488</v>
       </c>
       <c r="E27" s="47" t="s">
-        <v>537</v>
+        <v>489</v>
       </c>
       <c r="F27" s="47" t="s">
-        <v>538</v>
+        <v>490</v>
       </c>
       <c r="G27" s="47" t="s">
-        <v>539</v>
+        <v>491</v>
       </c>
       <c r="I27" s="48">
         <v>238</v>
@@ -6521,22 +6475,22 @@
     </row>
     <row r="28" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B28" s="49" t="s">
-        <v>548</v>
+        <v>498</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>523</v>
+        <v>478</v>
       </c>
       <c r="D28" s="55" t="s">
-        <v>540</v>
+        <v>492</v>
       </c>
       <c r="E28" s="44" t="s">
-        <v>541</v>
+        <v>872</v>
       </c>
       <c r="F28" s="44" t="s">
-        <v>542</v>
+        <v>873</v>
       </c>
       <c r="G28" s="44" t="s">
-        <v>543</v>
+        <v>493</v>
       </c>
       <c r="H28" s="2"/>
       <c r="I28" s="45">
@@ -6548,7 +6502,7 @@
     </row>
     <row r="29" spans="2:10" ht="65" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B29" s="90" t="s">
-        <v>553</v>
+        <v>503</v>
       </c>
       <c r="C29" s="91"/>
       <c r="D29" s="91"/>
@@ -6587,7 +6541,7 @@
   <sheetData>
     <row r="3" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B3" s="89" t="s">
-        <v>656</v>
+        <v>579</v>
       </c>
       <c r="C3" s="89"/>
       <c r="D3" s="89"/>
@@ -6600,47 +6554,47 @@
     </row>
     <row r="4" spans="2:10" x14ac:dyDescent="0.2">
       <c r="D4" s="87" t="s">
-        <v>549</v>
+        <v>499</v>
       </c>
       <c r="E4" s="88"/>
       <c r="F4" s="88"/>
       <c r="G4" s="88"/>
       <c r="H4" s="31"/>
       <c r="I4" s="88" t="s">
-        <v>552</v>
+        <v>502</v>
       </c>
       <c r="J4" s="88"/>
     </row>
     <row r="5" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B5" s="32" t="s">
-        <v>550</v>
+        <v>500</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>461</v>
+        <v>442</v>
       </c>
       <c r="D5" s="51" t="s">
-        <v>437</v>
+        <v>418</v>
       </c>
       <c r="E5" s="33" t="s">
-        <v>439</v>
+        <v>420</v>
       </c>
       <c r="F5" s="33" t="s">
-        <v>441</v>
+        <v>422</v>
       </c>
       <c r="G5" s="33" t="s">
-        <v>443</v>
+        <v>424</v>
       </c>
       <c r="H5" s="32"/>
       <c r="I5" s="33" t="s">
-        <v>550</v>
+        <v>500</v>
       </c>
       <c r="J5" s="33" t="s">
-        <v>551</v>
+        <v>501</v>
       </c>
     </row>
     <row r="6" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B6" s="50" t="s">
-        <v>554</v>
+        <v>504</v>
       </c>
       <c r="C6" s="41"/>
       <c r="D6" s="41"/>
@@ -6653,22 +6607,22 @@
     </row>
     <row r="7" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B7" s="37" t="s">
-        <v>544</v>
+        <v>494</v>
       </c>
       <c r="C7" s="38" t="s">
-        <v>554</v>
+        <v>504</v>
       </c>
       <c r="D7" s="52" t="s">
-        <v>555</v>
+        <v>505</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>556</v>
+        <v>506</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>557</v>
+        <v>507</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>558</v>
+        <v>508</v>
       </c>
       <c r="H7" s="38"/>
       <c r="I7" s="39">
@@ -6680,22 +6634,22 @@
     </row>
     <row r="8" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B8" s="37" t="s">
-        <v>545</v>
+        <v>495</v>
       </c>
       <c r="C8" s="38" t="s">
-        <v>554</v>
+        <v>504</v>
       </c>
       <c r="D8" s="52" t="s">
-        <v>555</v>
+        <v>505</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>556</v>
+        <v>506</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>559</v>
+        <v>509</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>560</v>
+        <v>510</v>
       </c>
       <c r="H8" s="38"/>
       <c r="I8" s="39">
@@ -6707,22 +6661,22 @@
     </row>
     <row r="9" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B9" s="37" t="s">
-        <v>546</v>
+        <v>496</v>
       </c>
       <c r="C9" s="38" t="s">
-        <v>554</v>
+        <v>504</v>
       </c>
       <c r="D9" s="52" t="s">
-        <v>561</v>
+        <v>892</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>562</v>
+        <v>893</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>563</v>
+        <v>511</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>564</v>
+        <v>512</v>
       </c>
       <c r="H9" s="38"/>
       <c r="I9" s="39">
@@ -6734,22 +6688,22 @@
     </row>
     <row r="10" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B10" s="37" t="s">
-        <v>547</v>
+        <v>497</v>
       </c>
       <c r="C10" s="38" t="s">
-        <v>554</v>
+        <v>504</v>
       </c>
       <c r="D10" s="52" t="s">
-        <v>565</v>
+        <v>894</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>566</v>
+        <v>895</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>567</v>
+        <v>513</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>568</v>
+        <v>514</v>
       </c>
       <c r="H10" s="38"/>
       <c r="I10" s="39">
@@ -6761,22 +6715,22 @@
     </row>
     <row r="11" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B11" s="40" t="s">
-        <v>548</v>
+        <v>498</v>
       </c>
       <c r="C11" s="41" t="s">
-        <v>554</v>
+        <v>504</v>
       </c>
       <c r="D11" s="53" t="s">
-        <v>569</v>
+        <v>896</v>
       </c>
       <c r="E11" s="42" t="s">
-        <v>570</v>
+        <v>897</v>
       </c>
       <c r="F11" s="42" t="s">
-        <v>571</v>
+        <v>898</v>
       </c>
       <c r="G11" s="42" t="s">
-        <v>572</v>
+        <v>515</v>
       </c>
       <c r="H11" s="41"/>
       <c r="I11" s="43">
@@ -6788,7 +6742,7 @@
     </row>
     <row r="12" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B12" s="32" t="s">
-        <v>573</v>
+        <v>516</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" s="44"/>
@@ -6801,22 +6755,22 @@
     </row>
     <row r="13" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B13" s="46" t="s">
-        <v>544</v>
+        <v>494</v>
       </c>
       <c r="C13" s="56" t="s">
-        <v>573</v>
+        <v>516</v>
       </c>
       <c r="D13" s="59" t="s">
-        <v>574</v>
+        <v>517</v>
       </c>
       <c r="E13" s="60" t="s">
-        <v>575</v>
+        <v>518</v>
       </c>
       <c r="F13" s="60" t="s">
-        <v>576</v>
+        <v>519</v>
       </c>
       <c r="G13" s="60" t="s">
-        <v>577</v>
+        <v>520</v>
       </c>
       <c r="I13" s="48">
         <v>2410</v>
@@ -6827,22 +6781,22 @@
     </row>
     <row r="14" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B14" s="46" t="s">
-        <v>545</v>
+        <v>495</v>
       </c>
       <c r="C14" s="56" t="s">
-        <v>573</v>
+        <v>516</v>
       </c>
       <c r="D14" s="59" t="s">
-        <v>578</v>
+        <v>521</v>
       </c>
       <c r="E14" s="60" t="s">
-        <v>575</v>
+        <v>518</v>
       </c>
       <c r="F14" s="60" t="s">
-        <v>579</v>
+        <v>522</v>
       </c>
       <c r="G14" s="60" t="s">
-        <v>580</v>
+        <v>523</v>
       </c>
       <c r="I14" s="48">
         <v>2410</v>
@@ -6853,22 +6807,22 @@
     </row>
     <row r="15" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B15" s="46" t="s">
-        <v>546</v>
+        <v>496</v>
       </c>
       <c r="C15" s="56" t="s">
-        <v>573</v>
+        <v>516</v>
       </c>
       <c r="D15" s="59" t="s">
-        <v>581</v>
+        <v>877</v>
       </c>
       <c r="E15" s="60" t="s">
-        <v>582</v>
+        <v>878</v>
       </c>
       <c r="F15" s="60" t="s">
-        <v>583</v>
+        <v>879</v>
       </c>
       <c r="G15" s="60" t="s">
-        <v>584</v>
+        <v>880</v>
       </c>
       <c r="I15" s="48">
         <v>2410</v>
@@ -6879,22 +6833,22 @@
     </row>
     <row r="16" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B16" s="46" t="s">
-        <v>547</v>
+        <v>497</v>
       </c>
       <c r="C16" s="56" t="s">
-        <v>573</v>
+        <v>516</v>
       </c>
       <c r="D16" s="59" t="s">
-        <v>585</v>
+        <v>881</v>
       </c>
       <c r="E16" s="60" t="s">
-        <v>586</v>
+        <v>882</v>
       </c>
       <c r="F16" s="60" t="s">
-        <v>587</v>
+        <v>524</v>
       </c>
       <c r="G16" s="60" t="s">
-        <v>588</v>
+        <v>883</v>
       </c>
       <c r="I16" s="48">
         <v>2154</v>
@@ -6905,22 +6859,22 @@
     </row>
     <row r="17" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B17" s="49" t="s">
-        <v>548</v>
+        <v>498</v>
       </c>
       <c r="C17" s="57" t="s">
-        <v>573</v>
+        <v>516</v>
       </c>
       <c r="D17" s="61" t="s">
-        <v>589</v>
+        <v>525</v>
       </c>
       <c r="E17" s="62" t="s">
-        <v>590</v>
+        <v>526</v>
       </c>
       <c r="F17" s="62" t="s">
-        <v>591</v>
+        <v>527</v>
       </c>
       <c r="G17" s="62" t="s">
-        <v>592</v>
+        <v>528</v>
       </c>
       <c r="H17" s="2"/>
       <c r="I17" s="45">
@@ -6932,7 +6886,7 @@
     </row>
     <row r="18" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B18" s="63" t="s">
-        <v>593</v>
+        <v>529</v>
       </c>
       <c r="C18" s="41"/>
       <c r="D18" s="42"/>
@@ -6945,22 +6899,22 @@
     </row>
     <row r="19" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B19" s="37" t="s">
-        <v>544</v>
+        <v>494</v>
       </c>
       <c r="C19" s="64" t="s">
-        <v>593</v>
+        <v>529</v>
       </c>
       <c r="D19" s="65" t="s">
-        <v>594</v>
+        <v>530</v>
       </c>
       <c r="E19" s="66" t="s">
-        <v>595</v>
+        <v>531</v>
       </c>
       <c r="F19" s="66" t="s">
-        <v>596</v>
+        <v>532</v>
       </c>
       <c r="G19" s="66" t="s">
-        <v>597</v>
+        <v>533</v>
       </c>
       <c r="H19" s="38"/>
       <c r="I19" s="39">
@@ -6972,22 +6926,22 @@
     </row>
     <row r="20" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B20" s="37" t="s">
-        <v>545</v>
+        <v>495</v>
       </c>
       <c r="C20" s="64" t="s">
-        <v>593</v>
+        <v>529</v>
       </c>
       <c r="D20" s="65" t="s">
-        <v>598</v>
+        <v>534</v>
       </c>
       <c r="E20" s="66" t="s">
-        <v>599</v>
+        <v>535</v>
       </c>
       <c r="F20" s="66" t="s">
-        <v>600</v>
+        <v>536</v>
       </c>
       <c r="G20" s="66" t="s">
-        <v>601</v>
+        <v>537</v>
       </c>
       <c r="H20" s="38"/>
       <c r="I20" s="39">
@@ -6999,22 +6953,22 @@
     </row>
     <row r="21" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B21" s="37" t="s">
-        <v>546</v>
+        <v>496</v>
       </c>
       <c r="C21" s="64" t="s">
-        <v>593</v>
+        <v>529</v>
       </c>
       <c r="D21" s="65" t="s">
-        <v>602</v>
+        <v>538</v>
       </c>
       <c r="E21" s="66" t="s">
-        <v>603</v>
+        <v>539</v>
       </c>
       <c r="F21" s="66" t="s">
-        <v>604</v>
+        <v>540</v>
       </c>
       <c r="G21" s="66" t="s">
-        <v>605</v>
+        <v>541</v>
       </c>
       <c r="H21" s="38"/>
       <c r="I21" s="39">
@@ -7026,22 +6980,22 @@
     </row>
     <row r="22" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B22" s="37" t="s">
-        <v>547</v>
+        <v>497</v>
       </c>
       <c r="C22" s="64" t="s">
-        <v>593</v>
+        <v>529</v>
       </c>
       <c r="D22" s="65" t="s">
-        <v>606</v>
+        <v>874</v>
       </c>
       <c r="E22" s="66" t="s">
-        <v>607</v>
+        <v>542</v>
       </c>
       <c r="F22" s="66" t="s">
-        <v>608</v>
+        <v>543</v>
       </c>
       <c r="G22" s="66" t="s">
-        <v>609</v>
+        <v>544</v>
       </c>
       <c r="H22" s="38"/>
       <c r="I22" s="39">
@@ -7053,22 +7007,22 @@
     </row>
     <row r="23" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B23" s="40" t="s">
-        <v>548</v>
+        <v>498</v>
       </c>
       <c r="C23" s="67" t="s">
-        <v>593</v>
+        <v>529</v>
       </c>
       <c r="D23" s="68" t="s">
-        <v>610</v>
+        <v>875</v>
       </c>
       <c r="E23" s="69" t="s">
-        <v>611</v>
+        <v>545</v>
       </c>
       <c r="F23" s="69" t="s">
-        <v>612</v>
+        <v>876</v>
       </c>
       <c r="G23" s="69" t="s">
-        <v>613</v>
+        <v>546</v>
       </c>
       <c r="H23" s="41"/>
       <c r="I23" s="43">
@@ -7080,7 +7034,7 @@
     </row>
     <row r="24" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B24" s="58" t="s">
-        <v>614</v>
+        <v>547</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" s="44"/>
@@ -7093,22 +7047,22 @@
     </row>
     <row r="25" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B25" s="46" t="s">
-        <v>544</v>
+        <v>494</v>
       </c>
       <c r="C25" s="56" t="s">
-        <v>614</v>
+        <v>547</v>
       </c>
       <c r="D25" s="59" t="s">
-        <v>615</v>
+        <v>548</v>
       </c>
       <c r="E25" s="60" t="s">
-        <v>616</v>
+        <v>549</v>
       </c>
       <c r="F25" s="60" t="s">
-        <v>617</v>
+        <v>550</v>
       </c>
       <c r="G25" s="60" t="s">
-        <v>618</v>
+        <v>551</v>
       </c>
       <c r="I25" s="48">
         <v>1058</v>
@@ -7119,22 +7073,22 @@
     </row>
     <row r="26" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B26" s="46" t="s">
-        <v>545</v>
+        <v>495</v>
       </c>
       <c r="C26" s="56" t="s">
-        <v>614</v>
+        <v>547</v>
       </c>
       <c r="D26" s="59" t="s">
-        <v>619</v>
+        <v>552</v>
       </c>
       <c r="E26" s="60" t="s">
-        <v>620</v>
+        <v>553</v>
       </c>
       <c r="F26" s="60" t="s">
-        <v>621</v>
+        <v>554</v>
       </c>
       <c r="G26" s="60" t="s">
-        <v>622</v>
+        <v>555</v>
       </c>
       <c r="I26" s="48">
         <v>1058</v>
@@ -7145,22 +7099,22 @@
     </row>
     <row r="27" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B27" s="46" t="s">
-        <v>546</v>
+        <v>496</v>
       </c>
       <c r="C27" s="56" t="s">
-        <v>614</v>
+        <v>547</v>
       </c>
       <c r="D27" s="59" t="s">
-        <v>623</v>
+        <v>556</v>
       </c>
       <c r="E27" s="60" t="s">
-        <v>624</v>
+        <v>557</v>
       </c>
       <c r="F27" s="60" t="s">
-        <v>625</v>
+        <v>558</v>
       </c>
       <c r="G27" s="60" t="s">
-        <v>626</v>
+        <v>899</v>
       </c>
       <c r="I27" s="48">
         <v>1058</v>
@@ -7171,22 +7125,22 @@
     </row>
     <row r="28" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B28" s="46" t="s">
+        <v>497</v>
+      </c>
+      <c r="C28" s="56" t="s">
         <v>547</v>
       </c>
-      <c r="C28" s="56" t="s">
-        <v>614</v>
-      </c>
       <c r="D28" s="59" t="s">
-        <v>627</v>
+        <v>559</v>
       </c>
       <c r="E28" s="60" t="s">
-        <v>628</v>
+        <v>560</v>
       </c>
       <c r="F28" s="60" t="s">
-        <v>629</v>
+        <v>561</v>
       </c>
       <c r="G28" s="60" t="s">
-        <v>630</v>
+        <v>562</v>
       </c>
       <c r="I28" s="48">
         <v>908</v>
@@ -7197,22 +7151,22 @@
     </row>
     <row r="29" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B29" s="49" t="s">
-        <v>548</v>
+        <v>498</v>
       </c>
       <c r="C29" s="57" t="s">
-        <v>614</v>
+        <v>547</v>
       </c>
       <c r="D29" s="61" t="s">
-        <v>631</v>
+        <v>900</v>
       </c>
       <c r="E29" s="62" t="s">
-        <v>632</v>
+        <v>563</v>
       </c>
       <c r="F29" s="62" t="s">
-        <v>633</v>
+        <v>564</v>
       </c>
       <c r="G29" s="62" t="s">
-        <v>634</v>
+        <v>565</v>
       </c>
       <c r="H29" s="2"/>
       <c r="I29" s="45">
@@ -7224,7 +7178,7 @@
     </row>
     <row r="30" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B30" s="63" t="s">
-        <v>635</v>
+        <v>566</v>
       </c>
       <c r="C30" s="41"/>
       <c r="D30" s="42"/>
@@ -7237,22 +7191,22 @@
     </row>
     <row r="31" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B31" s="37" t="s">
-        <v>544</v>
+        <v>494</v>
       </c>
       <c r="C31" s="64" t="s">
-        <v>635</v>
+        <v>566</v>
       </c>
       <c r="D31" s="65" t="s">
-        <v>636</v>
+        <v>567</v>
       </c>
       <c r="E31" s="66" t="s">
-        <v>637</v>
+        <v>568</v>
       </c>
       <c r="F31" s="66" t="s">
-        <v>638</v>
+        <v>569</v>
       </c>
       <c r="G31" s="66" t="s">
-        <v>639</v>
+        <v>570</v>
       </c>
       <c r="H31" s="38"/>
       <c r="I31" s="39">
@@ -7264,22 +7218,22 @@
     </row>
     <row r="32" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B32" s="37" t="s">
-        <v>545</v>
+        <v>495</v>
       </c>
       <c r="C32" s="64" t="s">
-        <v>635</v>
+        <v>566</v>
       </c>
       <c r="D32" s="65" t="s">
-        <v>640</v>
+        <v>571</v>
       </c>
       <c r="E32" s="66" t="s">
-        <v>641</v>
+        <v>572</v>
       </c>
       <c r="F32" s="66" t="s">
-        <v>642</v>
+        <v>573</v>
       </c>
       <c r="G32" s="66" t="s">
-        <v>643</v>
+        <v>574</v>
       </c>
       <c r="H32" s="38"/>
       <c r="I32" s="39">
@@ -7291,22 +7245,22 @@
     </row>
     <row r="33" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B33" s="37" t="s">
-        <v>546</v>
+        <v>496</v>
       </c>
       <c r="C33" s="64" t="s">
-        <v>635</v>
+        <v>566</v>
       </c>
       <c r="D33" s="65" t="s">
-        <v>644</v>
+        <v>884</v>
       </c>
       <c r="E33" s="66" t="s">
-        <v>645</v>
+        <v>885</v>
       </c>
       <c r="F33" s="66" t="s">
-        <v>646</v>
+        <v>886</v>
       </c>
       <c r="G33" s="66" t="s">
-        <v>647</v>
+        <v>887</v>
       </c>
       <c r="H33" s="38"/>
       <c r="I33" s="39">
@@ -7318,22 +7272,22 @@
     </row>
     <row r="34" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B34" s="37" t="s">
-        <v>547</v>
+        <v>497</v>
       </c>
       <c r="C34" s="64" t="s">
-        <v>635</v>
+        <v>566</v>
       </c>
       <c r="D34" s="65" t="s">
-        <v>648</v>
+        <v>888</v>
       </c>
       <c r="E34" s="66" t="s">
-        <v>649</v>
+        <v>889</v>
       </c>
       <c r="F34" s="66" t="s">
-        <v>650</v>
+        <v>575</v>
       </c>
       <c r="G34" s="66" t="s">
-        <v>651</v>
+        <v>890</v>
       </c>
       <c r="H34" s="38"/>
       <c r="I34" s="39">
@@ -7345,22 +7299,22 @@
     </row>
     <row r="35" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B35" s="40" t="s">
-        <v>548</v>
+        <v>498</v>
       </c>
       <c r="C35" s="67" t="s">
-        <v>635</v>
+        <v>566</v>
       </c>
       <c r="D35" s="68" t="s">
-        <v>652</v>
+        <v>576</v>
       </c>
       <c r="E35" s="69" t="s">
-        <v>653</v>
+        <v>891</v>
       </c>
       <c r="F35" s="69" t="s">
-        <v>654</v>
+        <v>577</v>
       </c>
       <c r="G35" s="69" t="s">
-        <v>655</v>
+        <v>578</v>
       </c>
       <c r="H35" s="41"/>
       <c r="I35" s="43">
@@ -7372,7 +7326,7 @@
     </row>
     <row r="36" spans="2:10" ht="66" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B36" s="90" t="s">
-        <v>657</v>
+        <v>580</v>
       </c>
       <c r="C36" s="90"/>
       <c r="D36" s="90"/>
@@ -7414,7 +7368,7 @@
   <sheetData>
     <row r="2" spans="2:11" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B2" s="92" t="s">
-        <v>716</v>
+        <v>625</v>
       </c>
       <c r="C2" s="92"/>
       <c r="D2" s="92"/>
@@ -7429,7 +7383,7 @@
     <row r="3" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B3" s="31"/>
       <c r="C3" s="88" t="s">
-        <v>682</v>
+        <v>593</v>
       </c>
       <c r="D3" s="88"/>
       <c r="E3" s="72"/>
@@ -7440,53 +7394,53 @@
     <row r="4" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B4" s="31"/>
       <c r="C4" s="72" t="s">
-        <v>683</v>
+        <v>594</v>
       </c>
       <c r="D4" s="72" t="s">
-        <v>684</v>
+        <v>595</v>
       </c>
       <c r="E4" s="72"/>
       <c r="F4" s="88" t="s">
-        <v>686</v>
+        <v>597</v>
       </c>
       <c r="G4" s="88"/>
       <c r="H4" s="88"/>
       <c r="J4" s="88" t="s">
-        <v>552</v>
+        <v>502</v>
       </c>
       <c r="K4" s="88"/>
     </row>
     <row r="5" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B5" s="32" t="s">
-        <v>677</v>
+        <v>589</v>
       </c>
       <c r="C5" s="70" t="s">
-        <v>685</v>
+        <v>596</v>
       </c>
       <c r="D5" s="70" t="s">
-        <v>685</v>
+        <v>596</v>
       </c>
       <c r="E5" s="70"/>
       <c r="F5" s="70" t="s">
-        <v>683</v>
+        <v>594</v>
       </c>
       <c r="G5" s="70" t="s">
-        <v>684</v>
+        <v>595</v>
       </c>
       <c r="H5" s="70" t="s">
-        <v>687</v>
+        <v>598</v>
       </c>
       <c r="I5" s="2"/>
       <c r="J5" s="70" t="s">
-        <v>677</v>
+        <v>589</v>
       </c>
       <c r="K5" s="70" t="s">
-        <v>551</v>
+        <v>501</v>
       </c>
     </row>
     <row r="6" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B6" s="50" t="s">
-        <v>437</v>
+        <v>418</v>
       </c>
       <c r="C6" s="41"/>
       <c r="D6" s="41"/>
@@ -7500,23 +7454,23 @@
     </row>
     <row r="7" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B7" s="37" t="s">
-        <v>415</v>
+        <v>840</v>
       </c>
       <c r="C7" s="38" t="s">
-        <v>709</v>
+        <v>618</v>
       </c>
       <c r="D7" s="38" t="s">
-        <v>692</v>
+        <v>603</v>
       </c>
       <c r="E7" s="38"/>
       <c r="F7" s="3">
         <v>0.14000000000000001</v>
       </c>
       <c r="G7" s="76" t="s">
-        <v>700</v>
-      </c>
-      <c r="H7" s="3">
-        <v>0.28999999999999998</v>
+        <v>610</v>
+      </c>
+      <c r="H7" s="94" t="s">
+        <v>901</v>
       </c>
       <c r="I7" s="38"/>
       <c r="J7" s="3">
@@ -7528,20 +7482,20 @@
     </row>
     <row r="8" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B8" s="37" t="s">
-        <v>410</v>
+        <v>841</v>
       </c>
       <c r="C8" s="38" t="s">
-        <v>705</v>
+        <v>615</v>
       </c>
       <c r="D8" s="38" t="s">
-        <v>688</v>
+        <v>599</v>
       </c>
       <c r="E8" s="38"/>
       <c r="F8" s="3" t="s">
-        <v>700</v>
+        <v>610</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>700</v>
+        <v>610</v>
       </c>
       <c r="H8" s="3">
         <v>0.27</v>
@@ -7556,20 +7510,20 @@
     </row>
     <row r="9" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B9" s="40" t="s">
-        <v>678</v>
+        <v>842</v>
       </c>
       <c r="C9" s="41" t="s">
-        <v>701</v>
+        <v>611</v>
       </c>
       <c r="D9" s="41" t="s">
-        <v>696</v>
+        <v>606</v>
       </c>
       <c r="E9" s="41"/>
       <c r="F9" s="42" t="s">
-        <v>700</v>
+        <v>610</v>
       </c>
       <c r="G9" s="42" t="s">
-        <v>700</v>
+        <v>610</v>
       </c>
       <c r="H9" s="42">
         <v>0.55000000000000004</v>
@@ -7584,7 +7538,7 @@
     </row>
     <row r="10" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B10" s="73" t="s">
-        <v>679</v>
+        <v>590</v>
       </c>
       <c r="C10" s="2"/>
       <c r="D10" s="2"/>
@@ -7598,22 +7552,22 @@
     </row>
     <row r="11" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B11" s="46" t="s">
-        <v>415</v>
+        <v>840</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>710</v>
+        <v>619</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>693</v>
+        <v>902</v>
       </c>
       <c r="F11" s="47">
         <v>0.46</v>
       </c>
       <c r="G11" s="47" t="s">
-        <v>700</v>
+        <v>610</v>
       </c>
       <c r="H11" s="47">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="J11" s="47">
         <v>62</v>
@@ -7624,22 +7578,22 @@
     </row>
     <row r="12" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B12" s="46" t="s">
-        <v>410</v>
+        <v>841</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>706</v>
+        <v>616</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>689</v>
+        <v>600</v>
       </c>
       <c r="F12" s="77" t="s">
-        <v>714</v>
+        <v>623</v>
       </c>
       <c r="G12" s="47" t="s">
-        <v>700</v>
+        <v>610</v>
       </c>
       <c r="H12" s="47">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="J12" s="47">
         <v>94</v>
@@ -7650,23 +7604,23 @@
     </row>
     <row r="13" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B13" s="74" t="s">
-        <v>678</v>
+        <v>842</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>702</v>
+        <v>612</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>697</v>
+        <v>607</v>
       </c>
       <c r="E13" s="75"/>
       <c r="F13" s="78" t="s">
-        <v>700</v>
+        <v>610</v>
       </c>
       <c r="G13" s="78" t="s">
-        <v>700</v>
+        <v>610</v>
       </c>
       <c r="H13" s="79" t="s">
-        <v>713</v>
+        <v>622</v>
       </c>
       <c r="I13" s="2"/>
       <c r="J13" s="44">
@@ -7678,7 +7632,7 @@
     </row>
     <row r="14" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B14" s="50" t="s">
-        <v>680</v>
+        <v>591</v>
       </c>
       <c r="C14" s="41"/>
       <c r="D14" s="41"/>
@@ -7692,13 +7646,13 @@
     </row>
     <row r="15" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B15" s="37" t="s">
-        <v>415</v>
+        <v>840</v>
       </c>
       <c r="C15" s="38" t="s">
-        <v>711</v>
+        <v>620</v>
       </c>
       <c r="D15" s="38" t="s">
-        <v>694</v>
+        <v>604</v>
       </c>
       <c r="E15" s="38"/>
       <c r="F15" s="3">
@@ -7720,23 +7674,23 @@
     </row>
     <row r="16" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B16" s="37" t="s">
-        <v>410</v>
+        <v>841</v>
       </c>
       <c r="C16" s="38" t="s">
-        <v>707</v>
+        <v>903</v>
       </c>
       <c r="D16" s="38" t="s">
-        <v>690</v>
+        <v>601</v>
       </c>
       <c r="E16" s="38"/>
       <c r="F16" s="3">
         <v>0.02</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>700</v>
+        <v>610</v>
       </c>
       <c r="H16" s="3">
-        <v>0.52</v>
+        <v>0.05</v>
       </c>
       <c r="I16" s="38"/>
       <c r="J16" s="3">
@@ -7748,20 +7702,20 @@
     </row>
     <row r="17" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B17" s="40" t="s">
-        <v>678</v>
+        <v>842</v>
       </c>
       <c r="C17" s="41" t="s">
-        <v>703</v>
+        <v>613</v>
       </c>
       <c r="D17" s="41" t="s">
-        <v>698</v>
+        <v>608</v>
       </c>
       <c r="E17" s="41"/>
       <c r="F17" s="42" t="s">
-        <v>700</v>
+        <v>610</v>
       </c>
       <c r="G17" s="42" t="s">
-        <v>700</v>
+        <v>610</v>
       </c>
       <c r="H17" s="42">
         <v>0.73</v>
@@ -7776,7 +7730,7 @@
     </row>
     <row r="18" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B18" s="32" t="s">
-        <v>681</v>
+        <v>592</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" s="2"/>
@@ -7790,19 +7744,19 @@
     </row>
     <row r="19" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B19" s="46" t="s">
-        <v>415</v>
+        <v>840</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>712</v>
+        <v>621</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>695</v>
+        <v>605</v>
       </c>
       <c r="F19" s="47" t="s">
-        <v>700</v>
+        <v>610</v>
       </c>
       <c r="G19" s="47" t="s">
-        <v>700</v>
+        <v>610</v>
       </c>
       <c r="H19" s="47">
         <v>0.74</v>
@@ -7816,19 +7770,19 @@
     </row>
     <row r="20" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B20" s="46" t="s">
-        <v>410</v>
+        <v>841</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>708</v>
+        <v>617</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>691</v>
+        <v>602</v>
       </c>
       <c r="F20" s="47" t="s">
-        <v>700</v>
+        <v>610</v>
       </c>
       <c r="G20" s="47" t="s">
-        <v>700</v>
+        <v>610</v>
       </c>
       <c r="H20" s="47">
         <v>0.47</v>
@@ -7842,20 +7796,20 @@
     </row>
     <row r="21" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B21" s="49" t="s">
-        <v>678</v>
+        <v>842</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>704</v>
+        <v>614</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>699</v>
+        <v>609</v>
       </c>
       <c r="E21" s="2"/>
       <c r="F21" s="44" t="s">
-        <v>700</v>
+        <v>610</v>
       </c>
       <c r="G21" s="44" t="s">
-        <v>700</v>
+        <v>610</v>
       </c>
       <c r="H21" s="44">
         <v>0.08</v>
@@ -7870,7 +7824,7 @@
     </row>
     <row r="22" spans="2:11" ht="32" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B22" s="90" t="s">
-        <v>715</v>
+        <v>624</v>
       </c>
       <c r="C22" s="90"/>
       <c r="D22" s="90"/>
@@ -7907,7 +7861,7 @@
   <sheetData>
     <row r="2" spans="2:10" ht="32" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B2" s="89" t="s">
-        <v>717</v>
+        <v>626</v>
       </c>
       <c r="C2" s="89"/>
       <c r="D2" s="89"/>
@@ -7922,47 +7876,47 @@
       <c r="B3" s="1"/>
       <c r="C3" s="1"/>
       <c r="D3" s="87" t="s">
-        <v>549</v>
+        <v>499</v>
       </c>
       <c r="E3" s="88"/>
       <c r="F3" s="88"/>
       <c r="G3" s="88"/>
       <c r="H3" s="31"/>
       <c r="I3" s="88" t="s">
-        <v>552</v>
+        <v>502</v>
       </c>
       <c r="J3" s="88"/>
     </row>
     <row r="4" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B4" s="32" t="s">
-        <v>550</v>
+        <v>500</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>461</v>
+        <v>442</v>
       </c>
       <c r="D4" s="51" t="s">
-        <v>437</v>
+        <v>418</v>
       </c>
       <c r="E4" s="33" t="s">
-        <v>439</v>
+        <v>420</v>
       </c>
       <c r="F4" s="33" t="s">
-        <v>441</v>
+        <v>422</v>
       </c>
       <c r="G4" s="33" t="s">
-        <v>443</v>
+        <v>424</v>
       </c>
       <c r="H4" s="32"/>
       <c r="I4" s="33" t="s">
-        <v>550</v>
+        <v>500</v>
       </c>
       <c r="J4" s="33" t="s">
-        <v>551</v>
+        <v>501</v>
       </c>
     </row>
     <row r="5" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B5" s="34" t="s">
-        <v>378</v>
+        <v>363</v>
       </c>
       <c r="C5" s="35"/>
       <c r="D5" s="36"/>
@@ -7975,22 +7929,22 @@
     </row>
     <row r="6" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B6" s="37" t="s">
-        <v>544</v>
+        <v>494</v>
       </c>
       <c r="C6" s="38" t="s">
-        <v>462</v>
+        <v>443</v>
       </c>
       <c r="D6" s="52" t="s">
-        <v>658</v>
+        <v>581</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>659</v>
+        <v>582</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>660</v>
+        <v>583</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>661</v>
+        <v>584</v>
       </c>
       <c r="H6" s="38"/>
       <c r="I6" s="39">
@@ -8002,22 +7956,22 @@
     </row>
     <row r="7" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B7" s="37" t="s">
-        <v>545</v>
+        <v>495</v>
       </c>
       <c r="C7" s="38" t="s">
-        <v>462</v>
+        <v>443</v>
       </c>
       <c r="D7" s="52" t="s">
-        <v>658</v>
+        <v>581</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>659</v>
+        <v>582</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>662</v>
+        <v>585</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>663</v>
+        <v>586</v>
       </c>
       <c r="H7" s="38"/>
       <c r="I7" s="39">
@@ -8029,22 +7983,22 @@
     </row>
     <row r="8" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B8" s="37" t="s">
-        <v>546</v>
+        <v>496</v>
       </c>
       <c r="C8" s="38" t="s">
-        <v>462</v>
+        <v>443</v>
       </c>
       <c r="D8" s="52" t="s">
-        <v>664</v>
+        <v>904</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>665</v>
+        <v>905</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>666</v>
+        <v>906</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>667</v>
+        <v>907</v>
       </c>
       <c r="H8" s="38"/>
       <c r="I8" s="39">
@@ -8056,22 +8010,22 @@
     </row>
     <row r="9" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B9" s="37" t="s">
-        <v>547</v>
+        <v>497</v>
       </c>
       <c r="C9" s="38" t="s">
-        <v>462</v>
+        <v>443</v>
       </c>
       <c r="D9" s="52" t="s">
-        <v>668</v>
+        <v>908</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>669</v>
+        <v>909</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>670</v>
+        <v>910</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>671</v>
+        <v>911</v>
       </c>
       <c r="H9" s="38"/>
       <c r="I9" s="39">
@@ -8083,22 +8037,22 @@
     </row>
     <row r="10" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B10" s="40" t="s">
-        <v>548</v>
+        <v>498</v>
       </c>
       <c r="C10" s="41" t="s">
-        <v>462</v>
+        <v>443</v>
       </c>
       <c r="D10" s="53" t="s">
-        <v>672</v>
+        <v>912</v>
       </c>
       <c r="E10" s="42" t="s">
-        <v>673</v>
+        <v>913</v>
       </c>
       <c r="F10" s="42" t="s">
-        <v>674</v>
+        <v>914</v>
       </c>
       <c r="G10" s="42" t="s">
-        <v>675</v>
+        <v>587</v>
       </c>
       <c r="H10" s="41"/>
       <c r="I10" s="43">
@@ -8110,7 +8064,7 @@
     </row>
     <row r="11" spans="2:10" ht="66" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B11" s="90" t="s">
-        <v>553</v>
+        <v>503</v>
       </c>
       <c r="C11" s="91"/>
       <c r="D11" s="91"/>
@@ -8154,7 +8108,7 @@
   <sheetData>
     <row r="3" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B3" s="93" t="s">
-        <v>922</v>
+        <v>831</v>
       </c>
       <c r="C3" s="93"/>
       <c r="D3" s="93"/>
@@ -8169,59 +8123,59 @@
     </row>
     <row r="4" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B4" s="32" t="s">
-        <v>919</v>
+        <v>828</v>
       </c>
       <c r="C4" s="32" t="s">
-        <v>920</v>
+        <v>829</v>
       </c>
       <c r="D4" s="71" t="s">
-        <v>921</v>
+        <v>830</v>
       </c>
       <c r="E4" s="32"/>
       <c r="F4" s="32" t="s">
-        <v>919</v>
+        <v>828</v>
       </c>
       <c r="G4" s="32" t="s">
-        <v>920</v>
+        <v>829</v>
       </c>
       <c r="H4" s="71" t="s">
-        <v>921</v>
+        <v>830</v>
       </c>
       <c r="I4" s="32"/>
       <c r="J4" s="32" t="s">
-        <v>919</v>
+        <v>828</v>
       </c>
       <c r="K4" s="32" t="s">
-        <v>920</v>
+        <v>829</v>
       </c>
       <c r="L4" s="71" t="s">
-        <v>921</v>
+        <v>830</v>
       </c>
     </row>
     <row r="5" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B5" s="38" t="s">
-        <v>719</v>
+        <v>628</v>
       </c>
       <c r="C5" s="38" t="s">
-        <v>720</v>
+        <v>629</v>
       </c>
       <c r="D5" s="39">
         <v>284</v>
       </c>
       <c r="F5" s="38" t="s">
-        <v>787</v>
+        <v>696</v>
       </c>
       <c r="G5" s="38" t="s">
-        <v>593</v>
+        <v>529</v>
       </c>
       <c r="H5" s="39">
         <v>1247</v>
       </c>
       <c r="J5" s="38" t="s">
-        <v>854</v>
+        <v>763</v>
       </c>
       <c r="K5" s="38" t="s">
-        <v>855</v>
+        <v>764</v>
       </c>
       <c r="L5" s="39">
         <v>205</v>
@@ -8229,28 +8183,28 @@
     </row>
     <row r="6" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
-        <v>721</v>
+        <v>630</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>722</v>
+        <v>631</v>
       </c>
       <c r="D6" s="48">
         <v>18</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>788</v>
+        <v>697</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>789</v>
+        <v>698</v>
       </c>
       <c r="H6" s="48">
         <v>1177</v>
       </c>
       <c r="J6" s="1" t="s">
-        <v>856</v>
+        <v>765</v>
       </c>
       <c r="K6" s="1" t="s">
-        <v>857</v>
+        <v>766</v>
       </c>
       <c r="L6" s="48">
         <v>787</v>
@@ -8258,28 +8212,28 @@
     </row>
     <row r="7" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B7" s="38" t="s">
-        <v>723</v>
+        <v>632</v>
       </c>
       <c r="C7" s="38" t="s">
-        <v>724</v>
+        <v>633</v>
       </c>
       <c r="D7" s="39">
         <v>92</v>
       </c>
       <c r="F7" s="38" t="s">
-        <v>790</v>
+        <v>699</v>
       </c>
       <c r="G7" s="38" t="s">
-        <v>791</v>
+        <v>700</v>
       </c>
       <c r="H7" s="39">
         <v>1144</v>
       </c>
       <c r="J7" s="38" t="s">
-        <v>858</v>
+        <v>767</v>
       </c>
       <c r="K7" s="38" t="s">
-        <v>480</v>
+        <v>455</v>
       </c>
       <c r="L7" s="39">
         <v>2105</v>
@@ -8287,28 +8241,28 @@
     </row>
     <row r="8" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B8" s="1" t="s">
-        <v>725</v>
+        <v>634</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>726</v>
+        <v>635</v>
       </c>
       <c r="D8" s="48">
         <v>76</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>792</v>
+        <v>701</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>793</v>
+        <v>702</v>
       </c>
       <c r="H8" s="48">
         <v>9</v>
       </c>
       <c r="J8" s="1" t="s">
-        <v>859</v>
+        <v>768</v>
       </c>
       <c r="K8" s="1" t="s">
-        <v>860</v>
+        <v>769</v>
       </c>
       <c r="L8" s="48">
         <v>1594</v>
@@ -8316,28 +8270,28 @@
     </row>
     <row r="9" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B9" s="38" t="s">
-        <v>727</v>
+        <v>636</v>
       </c>
       <c r="C9" s="38" t="s">
-        <v>728</v>
+        <v>637</v>
       </c>
       <c r="D9" s="39">
         <v>23</v>
       </c>
       <c r="F9" s="38" t="s">
-        <v>794</v>
+        <v>703</v>
       </c>
       <c r="G9" s="38" t="s">
-        <v>795</v>
+        <v>704</v>
       </c>
       <c r="H9" s="39">
         <v>89</v>
       </c>
       <c r="J9" s="38" t="s">
-        <v>861</v>
+        <v>770</v>
       </c>
       <c r="K9" s="38" t="s">
-        <v>862</v>
+        <v>771</v>
       </c>
       <c r="L9" s="39">
         <v>907</v>
@@ -8345,28 +8299,28 @@
     </row>
     <row r="10" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B10" s="1" t="s">
-        <v>729</v>
+        <v>638</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>730</v>
+        <v>639</v>
       </c>
       <c r="D10" s="48">
         <v>18</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>796</v>
+        <v>705</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>797</v>
+        <v>706</v>
       </c>
       <c r="H10" s="48">
         <v>328</v>
       </c>
       <c r="J10" s="1" t="s">
-        <v>863</v>
+        <v>772</v>
       </c>
       <c r="K10" s="1" t="s">
-        <v>864</v>
+        <v>773</v>
       </c>
       <c r="L10" s="48">
         <v>329</v>
@@ -8374,28 +8328,28 @@
     </row>
     <row r="11" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B11" s="38" t="s">
-        <v>731</v>
+        <v>640</v>
       </c>
       <c r="C11" s="38" t="s">
-        <v>732</v>
+        <v>641</v>
       </c>
       <c r="D11" s="39">
         <v>253</v>
       </c>
       <c r="F11" s="38" t="s">
-        <v>798</v>
+        <v>707</v>
       </c>
       <c r="G11" s="38" t="s">
-        <v>799</v>
+        <v>708</v>
       </c>
       <c r="H11" s="39">
         <v>1281</v>
       </c>
       <c r="J11" s="38" t="s">
-        <v>865</v>
+        <v>774</v>
       </c>
       <c r="K11" s="38" t="s">
-        <v>866</v>
+        <v>775</v>
       </c>
       <c r="L11" s="39">
         <v>241</v>
@@ -8403,28 +8357,28 @@
     </row>
     <row r="12" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B12" s="1" t="s">
-        <v>733</v>
+        <v>642</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>734</v>
+        <v>643</v>
       </c>
       <c r="D12" s="48">
         <v>84</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>800</v>
+        <v>709</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>801</v>
+        <v>710</v>
       </c>
       <c r="H12" s="48">
         <v>193</v>
       </c>
       <c r="J12" s="1" t="s">
-        <v>867</v>
+        <v>776</v>
       </c>
       <c r="K12" s="1" t="s">
-        <v>868</v>
+        <v>777</v>
       </c>
       <c r="L12" s="48">
         <v>251</v>
@@ -8432,28 +8386,28 @@
     </row>
     <row r="13" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B13" s="38" t="s">
-        <v>735</v>
+        <v>644</v>
       </c>
       <c r="C13" s="38" t="s">
-        <v>736</v>
+        <v>645</v>
       </c>
       <c r="D13" s="39">
         <v>30</v>
       </c>
       <c r="F13" s="38" t="s">
-        <v>802</v>
+        <v>711</v>
       </c>
       <c r="G13" s="38" t="s">
-        <v>803</v>
+        <v>712</v>
       </c>
       <c r="H13" s="39">
         <v>1139</v>
       </c>
       <c r="J13" s="38" t="s">
-        <v>869</v>
+        <v>778</v>
       </c>
       <c r="K13" s="38" t="s">
-        <v>870</v>
+        <v>779</v>
       </c>
       <c r="L13" s="39">
         <v>153</v>
@@ -8461,28 +8415,28 @@
     </row>
     <row r="14" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B14" s="1" t="s">
-        <v>737</v>
+        <v>646</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>738</v>
+        <v>647</v>
       </c>
       <c r="D14" s="48">
         <v>19</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>804</v>
+        <v>713</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>805</v>
+        <v>714</v>
       </c>
       <c r="H14" s="48">
         <v>262</v>
       </c>
       <c r="J14" s="1" t="s">
-        <v>871</v>
+        <v>780</v>
       </c>
       <c r="K14" s="1" t="s">
-        <v>872</v>
+        <v>781</v>
       </c>
       <c r="L14" s="48">
         <v>320</v>
@@ -8490,28 +8444,28 @@
     </row>
     <row r="15" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B15" s="38" t="s">
-        <v>739</v>
+        <v>648</v>
       </c>
       <c r="C15" s="38" t="s">
-        <v>740</v>
+        <v>649</v>
       </c>
       <c r="D15" s="39">
         <v>78</v>
       </c>
       <c r="F15" s="38" t="s">
-        <v>806</v>
+        <v>715</v>
       </c>
       <c r="G15" s="38" t="s">
-        <v>807</v>
+        <v>716</v>
       </c>
       <c r="H15" s="39">
         <v>466</v>
       </c>
       <c r="J15" s="38" t="s">
-        <v>873</v>
+        <v>782</v>
       </c>
       <c r="K15" s="38" t="s">
-        <v>874</v>
+        <v>783</v>
       </c>
       <c r="L15" s="39">
         <v>68</v>
@@ -8519,28 +8473,28 @@
     </row>
     <row r="16" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B16" s="1" t="s">
-        <v>741</v>
+        <v>650</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>742</v>
+        <v>651</v>
       </c>
       <c r="D16" s="48">
         <v>69</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>808</v>
+        <v>717</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>809</v>
+        <v>718</v>
       </c>
       <c r="H16" s="48">
         <v>207</v>
       </c>
       <c r="J16" s="1" t="s">
-        <v>875</v>
+        <v>784</v>
       </c>
       <c r="K16" s="1" t="s">
-        <v>876</v>
+        <v>785</v>
       </c>
       <c r="L16" s="48">
         <v>2595</v>
@@ -8548,28 +8502,28 @@
     </row>
     <row r="17" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B17" s="38" t="s">
-        <v>743</v>
+        <v>652</v>
       </c>
       <c r="C17" s="38" t="s">
-        <v>744</v>
+        <v>653</v>
       </c>
       <c r="D17" s="39">
         <v>38</v>
       </c>
       <c r="F17" s="38" t="s">
-        <v>810</v>
+        <v>719</v>
       </c>
       <c r="G17" s="38" t="s">
-        <v>811</v>
+        <v>720</v>
       </c>
       <c r="H17" s="39">
         <v>159</v>
       </c>
       <c r="J17" s="38" t="s">
-        <v>877</v>
+        <v>786</v>
       </c>
       <c r="K17" s="38" t="s">
-        <v>878</v>
+        <v>787</v>
       </c>
       <c r="L17" s="39">
         <v>71</v>
@@ -8577,28 +8531,28 @@
     </row>
     <row r="18" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B18" s="1" t="s">
-        <v>745</v>
+        <v>654</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>746</v>
+        <v>655</v>
       </c>
       <c r="D18" s="48">
         <v>112</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>812</v>
+        <v>721</v>
       </c>
       <c r="G18" s="1" t="s">
-        <v>813</v>
+        <v>722</v>
       </c>
       <c r="H18" s="48">
         <v>229</v>
       </c>
       <c r="J18" s="1" t="s">
-        <v>879</v>
+        <v>788</v>
       </c>
       <c r="K18" s="1" t="s">
-        <v>880</v>
+        <v>789</v>
       </c>
       <c r="L18" s="48">
         <v>1215</v>
@@ -8606,28 +8560,28 @@
     </row>
     <row r="19" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B19" s="38" t="s">
-        <v>747</v>
+        <v>656</v>
       </c>
       <c r="C19" s="38" t="s">
-        <v>748</v>
+        <v>657</v>
       </c>
       <c r="D19" s="39">
         <v>154</v>
       </c>
       <c r="F19" s="38" t="s">
-        <v>814</v>
+        <v>723</v>
       </c>
       <c r="G19" s="38" t="s">
-        <v>815</v>
+        <v>724</v>
       </c>
       <c r="H19" s="39">
         <v>1058</v>
       </c>
       <c r="J19" s="38" t="s">
-        <v>881</v>
+        <v>790</v>
       </c>
       <c r="K19" s="38" t="s">
-        <v>882</v>
+        <v>791</v>
       </c>
       <c r="L19" s="39">
         <v>264</v>
@@ -8635,28 +8589,28 @@
     </row>
     <row r="20" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B20" s="1" t="s">
-        <v>749</v>
+        <v>658</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>750</v>
+        <v>659</v>
       </c>
       <c r="D20" s="48">
         <v>637</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>816</v>
+        <v>725</v>
       </c>
       <c r="G20" s="1" t="s">
-        <v>817</v>
+        <v>726</v>
       </c>
       <c r="H20" s="48">
         <v>158</v>
       </c>
       <c r="J20" s="1" t="s">
-        <v>883</v>
+        <v>792</v>
       </c>
       <c r="K20" s="1" t="s">
-        <v>884</v>
+        <v>793</v>
       </c>
       <c r="L20" s="48">
         <v>133</v>
@@ -8664,28 +8618,28 @@
     </row>
     <row r="21" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B21" s="38" t="s">
-        <v>751</v>
+        <v>660</v>
       </c>
       <c r="C21" s="38" t="s">
-        <v>752</v>
+        <v>661</v>
       </c>
       <c r="D21" s="39">
         <v>499</v>
       </c>
       <c r="F21" s="38" t="s">
-        <v>818</v>
+        <v>727</v>
       </c>
       <c r="G21" s="38" t="s">
-        <v>819</v>
+        <v>728</v>
       </c>
       <c r="H21" s="39">
         <v>29</v>
       </c>
       <c r="J21" s="38" t="s">
-        <v>885</v>
+        <v>794</v>
       </c>
       <c r="K21" s="38" t="s">
-        <v>886</v>
+        <v>795</v>
       </c>
       <c r="L21" s="39">
         <v>984</v>
@@ -8693,28 +8647,28 @@
     </row>
     <row r="22" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B22" s="1" t="s">
-        <v>753</v>
+        <v>662</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>754</v>
+        <v>663</v>
       </c>
       <c r="D22" s="48">
         <v>335</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>820</v>
+        <v>729</v>
       </c>
       <c r="G22" s="1" t="s">
-        <v>821</v>
+        <v>730</v>
       </c>
       <c r="H22" s="48">
         <v>101</v>
       </c>
       <c r="J22" s="1" t="s">
-        <v>887</v>
+        <v>796</v>
       </c>
       <c r="K22" s="1" t="s">
-        <v>888</v>
+        <v>797</v>
       </c>
       <c r="L22" s="48">
         <v>864</v>
@@ -8722,28 +8676,28 @@
     </row>
     <row r="23" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B23" s="38" t="s">
-        <v>755</v>
+        <v>664</v>
       </c>
       <c r="C23" s="38" t="s">
-        <v>756</v>
+        <v>665</v>
       </c>
       <c r="D23" s="39">
         <v>219</v>
       </c>
       <c r="F23" s="38" t="s">
-        <v>822</v>
+        <v>731</v>
       </c>
       <c r="G23" s="38" t="s">
-        <v>823</v>
+        <v>732</v>
       </c>
       <c r="H23" s="39">
         <v>40</v>
       </c>
       <c r="J23" s="38" t="s">
-        <v>889</v>
+        <v>798</v>
       </c>
       <c r="K23" s="38" t="s">
-        <v>890</v>
+        <v>799</v>
       </c>
       <c r="L23" s="39">
         <v>322</v>
@@ -8751,28 +8705,28 @@
     </row>
     <row r="24" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B24" s="1" t="s">
-        <v>757</v>
+        <v>666</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>758</v>
+        <v>667</v>
       </c>
       <c r="D24" s="48">
         <v>172</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>824</v>
+        <v>733</v>
       </c>
       <c r="G24" s="1" t="s">
-        <v>825</v>
+        <v>734</v>
       </c>
       <c r="H24" s="48">
         <v>852</v>
       </c>
       <c r="J24" s="1" t="s">
-        <v>891</v>
+        <v>800</v>
       </c>
       <c r="K24" s="1" t="s">
-        <v>892</v>
+        <v>801</v>
       </c>
       <c r="L24" s="48">
         <v>158</v>
@@ -8780,28 +8734,28 @@
     </row>
     <row r="25" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B25" s="38" t="s">
-        <v>759</v>
+        <v>668</v>
       </c>
       <c r="C25" s="38" t="s">
-        <v>760</v>
+        <v>669</v>
       </c>
       <c r="D25" s="39">
         <v>133</v>
       </c>
       <c r="F25" s="38" t="s">
-        <v>826</v>
+        <v>735</v>
       </c>
       <c r="G25" s="38" t="s">
-        <v>827</v>
+        <v>736</v>
       </c>
       <c r="H25" s="39">
         <v>449</v>
       </c>
       <c r="J25" s="38" t="s">
-        <v>893</v>
+        <v>802</v>
       </c>
       <c r="K25" s="38" t="s">
-        <v>894</v>
+        <v>803</v>
       </c>
       <c r="L25" s="39">
         <v>33</v>
@@ -8809,28 +8763,28 @@
     </row>
     <row r="26" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B26" s="1" t="s">
-        <v>761</v>
+        <v>670</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>762</v>
+        <v>671</v>
       </c>
       <c r="D26" s="48">
         <v>645</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>828</v>
+        <v>737</v>
       </c>
       <c r="G26" s="1" t="s">
-        <v>829</v>
+        <v>738</v>
       </c>
       <c r="H26" s="48">
         <v>383</v>
       </c>
       <c r="J26" s="1" t="s">
-        <v>895</v>
+        <v>804</v>
       </c>
       <c r="K26" s="1" t="s">
-        <v>896</v>
+        <v>805</v>
       </c>
       <c r="L26" s="48">
         <v>162</v>
@@ -8838,28 +8792,28 @@
     </row>
     <row r="27" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B27" s="38" t="s">
-        <v>763</v>
+        <v>672</v>
       </c>
       <c r="C27" s="38" t="s">
-        <v>764</v>
+        <v>673</v>
       </c>
       <c r="D27" s="39">
         <v>669</v>
       </c>
       <c r="F27" s="38" t="s">
-        <v>830</v>
+        <v>739</v>
       </c>
       <c r="G27" s="38" t="s">
-        <v>831</v>
+        <v>740</v>
       </c>
       <c r="H27" s="39">
         <v>50</v>
       </c>
       <c r="J27" s="38" t="s">
-        <v>897</v>
+        <v>806</v>
       </c>
       <c r="K27" s="38" t="s">
-        <v>898</v>
+        <v>807</v>
       </c>
       <c r="L27" s="39">
         <v>802</v>
@@ -8867,28 +8821,28 @@
     </row>
     <row r="28" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B28" s="1" t="s">
-        <v>765</v>
+        <v>674</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>766</v>
+        <v>675</v>
       </c>
       <c r="D28" s="48">
         <v>57</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>832</v>
+        <v>741</v>
       </c>
       <c r="G28" s="1" t="s">
-        <v>833</v>
+        <v>742</v>
       </c>
       <c r="H28" s="48">
         <v>444</v>
       </c>
       <c r="J28" s="1" t="s">
-        <v>899</v>
+        <v>808</v>
       </c>
       <c r="K28" s="1" t="s">
-        <v>900</v>
+        <v>809</v>
       </c>
       <c r="L28" s="48">
         <v>310</v>
@@ -8896,28 +8850,28 @@
     </row>
     <row r="29" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B29" s="38" t="s">
-        <v>767</v>
+        <v>676</v>
       </c>
       <c r="C29" s="38" t="s">
-        <v>768</v>
+        <v>677</v>
       </c>
       <c r="D29" s="39">
         <v>37</v>
       </c>
       <c r="F29" s="38" t="s">
-        <v>834</v>
+        <v>743</v>
       </c>
       <c r="G29" s="38" t="s">
-        <v>835</v>
+        <v>744</v>
       </c>
       <c r="H29" s="39">
         <v>397</v>
       </c>
       <c r="J29" s="38" t="s">
-        <v>901</v>
+        <v>810</v>
       </c>
       <c r="K29" s="38" t="s">
-        <v>902</v>
+        <v>811</v>
       </c>
       <c r="L29" s="39">
         <v>155</v>
@@ -8925,28 +8879,28 @@
     </row>
     <row r="30" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B30" s="1" t="s">
-        <v>769</v>
+        <v>678</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>770</v>
+        <v>679</v>
       </c>
       <c r="D30" s="48">
         <v>81</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>836</v>
+        <v>745</v>
       </c>
       <c r="G30" s="1" t="s">
-        <v>837</v>
+        <v>746</v>
       </c>
       <c r="H30" s="48">
         <v>111</v>
       </c>
       <c r="J30" s="1" t="s">
-        <v>903</v>
+        <v>812</v>
       </c>
       <c r="K30" s="1" t="s">
-        <v>904</v>
+        <v>813</v>
       </c>
       <c r="L30" s="48">
         <v>169</v>
@@ -8954,28 +8908,28 @@
     </row>
     <row r="31" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B31" s="38" t="s">
-        <v>771</v>
+        <v>680</v>
       </c>
       <c r="C31" s="38" t="s">
-        <v>772</v>
+        <v>681</v>
       </c>
       <c r="D31" s="39">
         <v>61</v>
       </c>
       <c r="F31" s="38" t="s">
-        <v>838</v>
+        <v>747</v>
       </c>
       <c r="G31" s="38" t="s">
-        <v>839</v>
+        <v>748</v>
       </c>
       <c r="H31" s="39">
         <v>81</v>
       </c>
       <c r="J31" s="38" t="s">
-        <v>905</v>
+        <v>814</v>
       </c>
       <c r="K31" s="38" t="s">
-        <v>906</v>
+        <v>815</v>
       </c>
       <c r="L31" s="39">
         <v>310</v>
@@ -8983,28 +8937,28 @@
     </row>
     <row r="32" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B32" s="1" t="s">
-        <v>773</v>
+        <v>682</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>774</v>
+        <v>683</v>
       </c>
       <c r="D32" s="48">
         <v>459</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>840</v>
+        <v>749</v>
       </c>
       <c r="G32" s="1" t="s">
-        <v>841</v>
+        <v>750</v>
       </c>
       <c r="H32" s="48">
         <v>370</v>
       </c>
       <c r="J32" s="1" t="s">
-        <v>907</v>
+        <v>816</v>
       </c>
       <c r="K32" s="1" t="s">
-        <v>908</v>
+        <v>817</v>
       </c>
       <c r="L32" s="48">
         <v>168</v>
@@ -9012,28 +8966,28 @@
     </row>
     <row r="33" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B33" s="38" t="s">
-        <v>775</v>
+        <v>684</v>
       </c>
       <c r="C33" s="38" t="s">
-        <v>776</v>
+        <v>685</v>
       </c>
       <c r="D33" s="39">
         <v>397</v>
       </c>
       <c r="F33" s="38" t="s">
-        <v>842</v>
+        <v>751</v>
       </c>
       <c r="G33" s="38" t="s">
-        <v>843</v>
+        <v>752</v>
       </c>
       <c r="H33" s="39">
         <v>229</v>
       </c>
       <c r="J33" s="38" t="s">
-        <v>909</v>
+        <v>818</v>
       </c>
       <c r="K33" s="38" t="s">
-        <v>910</v>
+        <v>819</v>
       </c>
       <c r="L33" s="39">
         <v>87</v>
@@ -9041,28 +8995,28 @@
     </row>
     <row r="34" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B34" s="1" t="s">
-        <v>777</v>
+        <v>686</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>778</v>
+        <v>687</v>
       </c>
       <c r="D34" s="48">
         <v>525</v>
       </c>
       <c r="F34" s="1" t="s">
-        <v>844</v>
+        <v>753</v>
       </c>
       <c r="G34" s="1" t="s">
-        <v>845</v>
+        <v>754</v>
       </c>
       <c r="H34" s="48">
         <v>199</v>
       </c>
       <c r="J34" s="1" t="s">
-        <v>911</v>
+        <v>820</v>
       </c>
       <c r="K34" s="1" t="s">
-        <v>912</v>
+        <v>821</v>
       </c>
       <c r="L34" s="48">
         <v>40</v>
@@ -9070,28 +9024,28 @@
     </row>
     <row r="35" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B35" s="38" t="s">
-        <v>779</v>
+        <v>688</v>
       </c>
       <c r="C35" s="38" t="s">
-        <v>780</v>
+        <v>689</v>
       </c>
       <c r="D35" s="39">
         <v>203</v>
       </c>
       <c r="F35" s="38" t="s">
-        <v>846</v>
+        <v>755</v>
       </c>
       <c r="G35" s="38" t="s">
-        <v>847</v>
+        <v>756</v>
       </c>
       <c r="H35" s="39">
         <v>371</v>
       </c>
       <c r="J35" s="38" t="s">
-        <v>913</v>
+        <v>822</v>
       </c>
       <c r="K35" s="38" t="s">
-        <v>914</v>
+        <v>823</v>
       </c>
       <c r="L35" s="39">
         <v>248</v>
@@ -9099,28 +9053,28 @@
     </row>
     <row r="36" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B36" s="1" t="s">
-        <v>781</v>
+        <v>690</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>782</v>
+        <v>691</v>
       </c>
       <c r="D36" s="48">
         <v>392</v>
       </c>
       <c r="F36" s="1" t="s">
-        <v>848</v>
+        <v>757</v>
       </c>
       <c r="G36" s="1" t="s">
-        <v>849</v>
+        <v>758</v>
       </c>
       <c r="H36" s="48">
         <v>274</v>
       </c>
       <c r="J36" s="1" t="s">
-        <v>915</v>
+        <v>824</v>
       </c>
       <c r="K36" s="1" t="s">
-        <v>916</v>
+        <v>825</v>
       </c>
       <c r="L36" s="48">
         <v>117</v>
@@ -9128,28 +9082,28 @@
     </row>
     <row r="37" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B37" s="38" t="s">
-        <v>783</v>
+        <v>692</v>
       </c>
       <c r="C37" s="38" t="s">
-        <v>784</v>
+        <v>693</v>
       </c>
       <c r="D37" s="39">
         <v>1958</v>
       </c>
       <c r="F37" s="38" t="s">
-        <v>850</v>
+        <v>759</v>
       </c>
       <c r="G37" s="38" t="s">
-        <v>851</v>
+        <v>760</v>
       </c>
       <c r="H37" s="39">
         <v>7030</v>
       </c>
       <c r="J37" s="38" t="s">
-        <v>917</v>
+        <v>826</v>
       </c>
       <c r="K37" s="38" t="s">
-        <v>918</v>
+        <v>827</v>
       </c>
       <c r="L37" s="39">
         <v>279</v>
@@ -9157,20 +9111,20 @@
     </row>
     <row r="38" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B38" s="2" t="s">
-        <v>785</v>
+        <v>694</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>786</v>
+        <v>695</v>
       </c>
       <c r="D38" s="45">
         <v>834</v>
       </c>
       <c r="E38" s="2"/>
       <c r="F38" s="2" t="s">
-        <v>852</v>
+        <v>761</v>
       </c>
       <c r="G38" s="2" t="s">
-        <v>853</v>
+        <v>762</v>
       </c>
       <c r="H38" s="45">
         <v>6897</v>
@@ -9186,4 +9140,35 @@
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D0568018-B914-CD4D-B7DD-E06AE67D7DE9}">
+  <dimension ref="B5:C7"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="2" max="2" width="21.6640625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="5" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B5" t="s">
+        <v>504</v>
+      </c>
+      <c r="C5">
+        <v>172.1</v>
+      </c>
+    </row>
+    <row r="6" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="C6">
+        <v>172.11</v>
+      </c>
+    </row>
+    <row r="7" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B7" t="s">
+        <v>516</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/new_tables.xlsx
+++ b/new_tables.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/maxsalvatore/Documents/projects/covid/new_cancer/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A45EAF35-7E4D-5140-A729-B72E0E41157A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{77822E2E-3122-E240-9B01-D003EB1929E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="15940" windowHeight="18000" activeTab="4" xr2:uid="{23B5B348-4D99-B540-995F-50D24F235ACD}"/>
+    <workbookView xWindow="28800" yWindow="500" windowWidth="23600" windowHeight="15900" activeTab="7" xr2:uid="{23B5B348-4D99-B540-995F-50D24F235ACD}"/>
   </bookViews>
   <sheets>
     <sheet name="table 1" sheetId="1" r:id="rId1"/>
@@ -20,6 +20,8 @@
     <sheet name="table 5" sheetId="4" r:id="rId5"/>
     <sheet name="cancer_counts" sheetId="6" r:id="rId6"/>
     <sheet name="Sheet1" sheetId="7" r:id="rId7"/>
+    <sheet name="recent table 2" sheetId="8" r:id="rId8"/>
+    <sheet name="recent table 3" sheetId="10" r:id="rId9"/>
   </sheets>
   <calcPr calcId="181029"/>
   <extLst>
@@ -41,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1176" uniqueCount="915">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1473" uniqueCount="1089">
   <si>
     <t>Age</t>
   </si>
@@ -2016,79 +2018,16 @@
     <t>Interaction</t>
   </si>
   <si>
-    <t>0.48 (0.34, 0.65)</t>
-  </si>
-  <si>
-    <t>0.54 (0.38, 0.74)</t>
-  </si>
-  <si>
     <t>0.14 (0.03, 0.40)</t>
   </si>
   <si>
-    <t>0.04 (0.00, 0.26)</t>
-  </si>
-  <si>
-    <t>0.57 (0.39, 0.80)</t>
-  </si>
-  <si>
     <t>0.37 (0.12, 0.83)</t>
   </si>
   <si>
-    <t>0.17 (0.02, 0.62)</t>
-  </si>
-  <si>
-    <t>0.31 (0.21, 0.43)</t>
-  </si>
-  <si>
-    <t>0.35 (0.24, 0.49)</t>
-  </si>
-  <si>
-    <t>0.29 (0.12, 0.58)</t>
-  </si>
-  <si>
-    <t>0.09 (0.01, 0.32)</t>
-  </si>
-  <si>
     <t>&lt;0.01</t>
   </si>
   <si>
-    <t>0.35 (0.26, 0.46)</t>
-  </si>
-  <si>
-    <t>0.37 (0.27, 0.49)</t>
-  </si>
-  <si>
-    <t>0.35 (0.17, 0.62)</t>
-  </si>
-  <si>
-    <t>0.33 (0.17, 0.58)</t>
-  </si>
-  <si>
-    <t>0.61 (0.45, 0.80)</t>
-  </si>
-  <si>
-    <t>0.70 (0.52, 0.93)</t>
-  </si>
-  <si>
-    <t>0.11 (0.02, 0.30)</t>
-  </si>
-  <si>
-    <t>0.76 (0.51, 1.09)</t>
-  </si>
-  <si>
-    <t>0.87 (0.58, 1.26)</t>
-  </si>
-  <si>
     <t>0.27 (0.06, 0.77)</t>
-  </si>
-  <si>
-    <t>0.24 (0.05, 0.70)</t>
-  </si>
-  <si>
-    <t>0.80</t>
-  </si>
-  <si>
-    <t>0.01</t>
   </si>
   <si>
     <t>Models were adjusted for age, race/ethnicity, sex, Disadvantage Index (quartile) and comorbidity score (i.e., adjustment set 3)</t>
@@ -2987,12 +2926,6 @@
     <t>0.89 (0.71, 1.10)</t>
   </si>
   <si>
-    <t>0.30</t>
-  </si>
-  <si>
-    <t>0.63 (0.43, 0.89)</t>
-  </si>
-  <si>
     <t>0.50 (0.24, 0.92)</t>
   </si>
   <si>
@@ -3027,6 +2960,634 @@
   </si>
   <si>
     <t>1.63 (1.26, 2.10)</t>
+  </si>
+  <si>
+    <t>0.49 (0.33, 0.69)</t>
+  </si>
+  <si>
+    <t>0.43 (0.31, 0.59)</t>
+  </si>
+  <si>
+    <t>0.34 (0.23, 0.47)</t>
+  </si>
+  <si>
+    <t>0.51 (0.37, 0.76)</t>
+  </si>
+  <si>
+    <t>0.49 (0.35, 0.67)</t>
+  </si>
+  <si>
+    <t>0.38 (0.26, 0.54)</t>
+  </si>
+  <si>
+    <t>0.29 (0.12, 0.59)</t>
+  </si>
+  <si>
+    <t>0.16 (0.02, 0.56)</t>
+  </si>
+  <si>
+    <t>0.04 (0.00, 0.24)</t>
+  </si>
+  <si>
+    <t>0.09 (0.01, 0.33)</t>
+  </si>
+  <si>
+    <t>0.54 (0.40, 0.71)</t>
+  </si>
+  <si>
+    <t>0.65 (0.44, 0.95)</t>
+  </si>
+  <si>
+    <t>0.37 (0.28, 0.49)</t>
+  </si>
+  <si>
+    <t>0.75 (0.50, 1.09)</t>
+  </si>
+  <si>
+    <t>0.63 (0.46, 0.83)</t>
+  </si>
+  <si>
+    <t>0.40 (0.29, 0.53)</t>
+  </si>
+  <si>
+    <t>0.35 (0.18, 0.62)</t>
+  </si>
+  <si>
+    <t>0.22 (0.05, 0.63)</t>
+  </si>
+  <si>
+    <t>0.10 (0.02, 0.28)</t>
+  </si>
+  <si>
+    <t>0.35 (0.18, 0.60)</t>
+  </si>
+  <si>
+    <t>2.50 (2.30, 2.72)</t>
+  </si>
+  <si>
+    <t>2.31 (2.12, 2.52)</t>
+  </si>
+  <si>
+    <t>1.93 (1.64, 2.27)</t>
+  </si>
+  <si>
+    <t>3.96 (3.34, 4.69)</t>
+  </si>
+  <si>
+    <t>3.96 (3.34, 4.68)</t>
+  </si>
+  <si>
+    <t>1.56 (1.43, 1.70)</t>
+  </si>
+  <si>
+    <t>1.49 (1.36, 1.64)</t>
+  </si>
+  <si>
+    <t>1.23 (1.04, 1.46)</t>
+  </si>
+  <si>
+    <t>1.82 (1.53, 2.17)</t>
+  </si>
+  <si>
+    <t>1.54 (1.40, 1.69)</t>
+  </si>
+  <si>
+    <t>1.50 (1.36, 1.66)</t>
+  </si>
+  <si>
+    <t>1.22 (1.01, 1.47)</t>
+  </si>
+  <si>
+    <t>1.66 (1.37, 2.01)</t>
+  </si>
+  <si>
+    <t>1.63 (1.47, 1.80)</t>
+  </si>
+  <si>
+    <t>1.60 (1.44, 1.78)</t>
+  </si>
+  <si>
+    <t>1.58 (1.29, 1.92)</t>
+  </si>
+  <si>
+    <t>1.77 (1.44, 2.17)</t>
+  </si>
+  <si>
+    <t>4.48 (3.96, 5.06)</t>
+  </si>
+  <si>
+    <t>4.17 (3.67, 4.73)</t>
+  </si>
+  <si>
+    <t>3.09 (2.44, 3.90)</t>
+  </si>
+  <si>
+    <t>5.62 (4.40, 7.18)</t>
+  </si>
+  <si>
+    <t>3.10 (2.44, 3.89)</t>
+  </si>
+  <si>
+    <t>5.65 (4.40, 7.17)</t>
+  </si>
+  <si>
+    <t>2.98 (2.62, 3.39)</t>
+  </si>
+  <si>
+    <t>2.85 (2.49, 3.25)</t>
+  </si>
+  <si>
+    <t>2.05 (1.61, 2.59)</t>
+  </si>
+  <si>
+    <t>2.84 (2.19, 3.63)</t>
+  </si>
+  <si>
+    <t>3.00 (2.61, 3.44)</t>
+  </si>
+  <si>
+    <t>2.96 (2.56, 3.41)</t>
+  </si>
+  <si>
+    <t>2.11 (1.62, 2.71)</t>
+  </si>
+  <si>
+    <t>2.47 (1.85, 3.25)</t>
+  </si>
+  <si>
+    <t>3.00 (2.60, 3.46)</t>
+  </si>
+  <si>
+    <t>2.99 (2.57, 3.46)</t>
+  </si>
+  <si>
+    <t>2.67 (2.03, 3.47)</t>
+  </si>
+  <si>
+    <t>2.57 (1.91, 3.41)</t>
+  </si>
+  <si>
+    <t>3.38 (2.51, 4.54)</t>
+  </si>
+  <si>
+    <t>3.19 (2.34, 4.34)</t>
+  </si>
+  <si>
+    <t>2.89 (1.68, 4.96)</t>
+  </si>
+  <si>
+    <t>6.63 (4.02, 10.92)</t>
+  </si>
+  <si>
+    <t>3.40 (2.51, 4.53)</t>
+  </si>
+  <si>
+    <t>3.21 (2.33, 4.33)</t>
+  </si>
+  <si>
+    <t>2.98 (1.67, 4.89)</t>
+  </si>
+  <si>
+    <t>6.80 (4.01, 10.80)</t>
+  </si>
+  <si>
+    <t>1.81 (1.33, 2.44)</t>
+  </si>
+  <si>
+    <t>1.79 (1.29, 2.44)</t>
+  </si>
+  <si>
+    <t>1.61 (0.90, 2.67)</t>
+  </si>
+  <si>
+    <t>2.61 (1.52, 4.20)</t>
+  </si>
+  <si>
+    <t>1.73 (1.23, 2.40)</t>
+  </si>
+  <si>
+    <t>1.72 (1.20, 2.41)</t>
+  </si>
+  <si>
+    <t>1.49 (0.77, 2.60)</t>
+  </si>
+  <si>
+    <t>2.49 (1.37, 4.18)</t>
+  </si>
+  <si>
+    <t>1.75 (1.22, 2.46)</t>
+  </si>
+  <si>
+    <t>1.81 (1.24, 2.57)</t>
+  </si>
+  <si>
+    <t>1.84 (0.91, 3.31)</t>
+  </si>
+  <si>
+    <t>2.21 (1.15, 3.86)</t>
+  </si>
+  <si>
+    <t>2.40 (0.93, 6.21)</t>
+  </si>
+  <si>
+    <t>2.61 (1.01, 6.75)</t>
+  </si>
+  <si>
+    <t>1.67 (0.23, 12.25)</t>
+  </si>
+  <si>
+    <t>2.60 (0.93, 5.98)</t>
+  </si>
+  <si>
+    <t>2.82 (1.01, 6.50)</t>
+  </si>
+  <si>
+    <t>2.47 (0.28, 9.30)</t>
+  </si>
+  <si>
+    <t>1.50 (0.01, 10.56)</t>
+  </si>
+  <si>
+    <t>1.59 (0.56, 3.73)</t>
+  </si>
+  <si>
+    <t>1.80 (0.64, 4.22)</t>
+  </si>
+  <si>
+    <t>1.59 (0.18, 6.13)</t>
+  </si>
+  <si>
+    <t>0.68 (0.01, 4.98)</t>
+  </si>
+  <si>
+    <t>1.66 (0.58, 3.96)</t>
+  </si>
+  <si>
+    <t>1.90 (0.66, 4.53)</t>
+  </si>
+  <si>
+    <t>1.55 (0.17, 6.10)</t>
+  </si>
+  <si>
+    <t>0.63 (0.00, 4.76)</t>
+  </si>
+  <si>
+    <t>1.42 (0.49, 3.49)</t>
+  </si>
+  <si>
+    <t>1.66 (0.57, 4.07)</t>
+  </si>
+  <si>
+    <t>1.70 (0.19, 6.78)</t>
+  </si>
+  <si>
+    <t>0.50 (0.00, 3.90)</t>
+  </si>
+  <si>
+    <t>Cancer/
+treatment group</t>
+  </si>
+  <si>
+    <t>Cancer type</t>
+  </si>
+  <si>
+    <t>2.70 (2.18, 3.34)</t>
+  </si>
+  <si>
+    <t>2.57 (2.06, 3.21)</t>
+  </si>
+  <si>
+    <t>1.87 (1.20, 2.91)</t>
+  </si>
+  <si>
+    <t>5.07 (3.48, 7.40)</t>
+  </si>
+  <si>
+    <t>2.71 (2.18, 3.34)</t>
+  </si>
+  <si>
+    <t>2.58 (2.06, 3.21)</t>
+  </si>
+  <si>
+    <t>1.91 (1.20, 2.88)</t>
+  </si>
+  <si>
+    <t>5.15 (3.47, 7.36)</t>
+  </si>
+  <si>
+    <t>1.55 (1.24, 1.92)</t>
+  </si>
+  <si>
+    <t>1.56 (1.23, 1.94)</t>
+  </si>
+  <si>
+    <t>1.19 (0.74, 1.80)</t>
+  </si>
+  <si>
+    <t>2.04 (1.36, 2.94)</t>
+  </si>
+  <si>
+    <t>1.64 (1.29, 2.06)</t>
+  </si>
+  <si>
+    <t>1.62 (1.26, 2.06)</t>
+  </si>
+  <si>
+    <t>1.23 (0.74, 1.92)</t>
+  </si>
+  <si>
+    <t>2.32 (1.53, 3.38)</t>
+  </si>
+  <si>
+    <t>1.77 (1.38, 2.24)</t>
+  </si>
+  <si>
+    <t>1.77 (1.36, 2.26)</t>
+  </si>
+  <si>
+    <t>1.62 (0.97, 2.55)</t>
+  </si>
+  <si>
+    <t>2.50 (1.64, 3.68)</t>
+  </si>
+  <si>
+    <t>3.65 (3.10, 4.31)</t>
+  </si>
+  <si>
+    <t>3.35 (2.81, 3.98)</t>
+  </si>
+  <si>
+    <t>2.84 (2.08, 3.87)</t>
+  </si>
+  <si>
+    <t>5.05 (3.66, 6.98)</t>
+  </si>
+  <si>
+    <t>3.66 (3.09, 4.30)</t>
+  </si>
+  <si>
+    <t>2.86 (2.07, 3.85)</t>
+  </si>
+  <si>
+    <t>5.10 (3.65, 6.95)</t>
+  </si>
+  <si>
+    <t>2.67 (2.24, 3.17)</t>
+  </si>
+  <si>
+    <t>2.48 (2.07, 2.96)</t>
+  </si>
+  <si>
+    <t>2.03 (1.46, 2.75)</t>
+  </si>
+  <si>
+    <t>2.94 (2.08, 4.06)</t>
+  </si>
+  <si>
+    <t>2.65 (2.19, 3.19)</t>
+  </si>
+  <si>
+    <t>2.49 (2.04, 3.02)</t>
+  </si>
+  <si>
+    <t>1.97 (1.38, 2.74)</t>
+  </si>
+  <si>
+    <t>2.62 (1.78, 3.73)</t>
+  </si>
+  <si>
+    <t>2.56 (2.09, 3.10)</t>
+  </si>
+  <si>
+    <t>2.40 (1.95, 2.94)</t>
+  </si>
+  <si>
+    <t>2.37 (1.61, 3.36)</t>
+  </si>
+  <si>
+    <t>2.33 (1.52, 3.44)</t>
+  </si>
+  <si>
+    <t>1.77 (1.30, 2.39)</t>
+  </si>
+  <si>
+    <t>1.65 (1.20, 2.28)</t>
+  </si>
+  <si>
+    <t>2.01 (1.20, 3.38)</t>
+  </si>
+  <si>
+    <t>3.76 (2.23, 6.35)</t>
+  </si>
+  <si>
+    <t>1.78 (1.30, 2.38)</t>
+  </si>
+  <si>
+    <t>1.67 (1.20, 2.27)</t>
+  </si>
+  <si>
+    <t>2.07 (1.19, 3.34)</t>
+  </si>
+  <si>
+    <t>3.88 (2.22, 6.27)</t>
+  </si>
+  <si>
+    <t>1.35 (0.98, 1.83)</t>
+  </si>
+  <si>
+    <t>1.32 (0.94, 1.81)</t>
+  </si>
+  <si>
+    <t>1.96 (1.12, 3.20)</t>
+  </si>
+  <si>
+    <t>2.44 (1.37, 4.02)</t>
+  </si>
+  <si>
+    <t>1.34 (0.94, 1.86)</t>
+  </si>
+  <si>
+    <t>1.36 (0.94, 1.91)</t>
+  </si>
+  <si>
+    <t>2.13 (1.18, 3.55)</t>
+  </si>
+  <si>
+    <t>2.32 (1.22, 4.03)</t>
+  </si>
+  <si>
+    <t>1.42 (0.97, 2.01)</t>
+  </si>
+  <si>
+    <t>1.43 (0.96, 2.06)</t>
+  </si>
+  <si>
+    <t>2.76 (1.46, 4.77)</t>
+  </si>
+  <si>
+    <t>2.71 (1.38, 4.82)</t>
+  </si>
+  <si>
+    <t>2.33 (1.78, 3.05)</t>
+  </si>
+  <si>
+    <t>1.94 (1.44, 2.61)</t>
+  </si>
+  <si>
+    <t>1.42 (0.78, 2.59)</t>
+  </si>
+  <si>
+    <t>4.66 (2.92, 7.45)</t>
+  </si>
+  <si>
+    <t>2.34 (1.78, 3.04)</t>
+  </si>
+  <si>
+    <t>1.96 (1.44, 2.61)</t>
+  </si>
+  <si>
+    <t>1.48 (0.77, 2.54)</t>
+  </si>
+  <si>
+    <t>4.77 (2.91, 7.38)</t>
+  </si>
+  <si>
+    <t>0.84 (0.63, 1.09)</t>
+  </si>
+  <si>
+    <t>0.74 (0.54, 0.99)</t>
+  </si>
+  <si>
+    <t>0.50 (0.26, 0.86)</t>
+  </si>
+  <si>
+    <t>1.09 (0.66, 1.71)</t>
+  </si>
+  <si>
+    <t>0.83 (0.60, 1.11)</t>
+  </si>
+  <si>
+    <t>0.71 (0.50, 0.98)</t>
+  </si>
+  <si>
+    <t>0.56 (0.28, 0.99)</t>
+  </si>
+  <si>
+    <t>1.15 (0.67, 1.85)</t>
+  </si>
+  <si>
+    <t>0.97 (0.69, 1.33)</t>
+  </si>
+  <si>
+    <t>0.80 (0.54, 1.15)</t>
+  </si>
+  <si>
+    <t>0.66 (0.29, 1.29)</t>
+  </si>
+  <si>
+    <t>1.44 (0.82, 2.37)</t>
+  </si>
+  <si>
+    <t>4.34 (3.17, 5.94)</t>
+  </si>
+  <si>
+    <t>3.49 (2.48, 4.91)</t>
+  </si>
+  <si>
+    <t>2.92 (1.59, 5.38)</t>
+  </si>
+  <si>
+    <t>9.81 (6.08, 15.85)</t>
+  </si>
+  <si>
+    <t>4.37 (3.17, 5.92)</t>
+  </si>
+  <si>
+    <t>3.52 (2.48, 4.89)</t>
+  </si>
+  <si>
+    <t>3.04 (1.58, 5.28)</t>
+  </si>
+  <si>
+    <t>10.04 (6.06, 15.71)</t>
+  </si>
+  <si>
+    <t>2.17 (1.56, 2.97)</t>
+  </si>
+  <si>
+    <t>1.83 (1.27, 2.56)</t>
+  </si>
+  <si>
+    <t>1.54 (0.79, 2.69)</t>
+  </si>
+  <si>
+    <t>3.56 (2.12, 5.65)</t>
+  </si>
+  <si>
+    <t>1.90 (1.30, 2.71)</t>
+  </si>
+  <si>
+    <t>1.77 (1.19, 2.58)</t>
+  </si>
+  <si>
+    <t>1.49 (0.71, 2.76)</t>
+  </si>
+  <si>
+    <t>2.50 (1.31, 4.37)</t>
+  </si>
+  <si>
+    <t>2.04 (1.38, 2.94)</t>
+  </si>
+  <si>
+    <t>1.91 (1.26, 2.81)</t>
+  </si>
+  <si>
+    <t>1.89 (0.87, 3.61)</t>
+  </si>
+  <si>
+    <t>2.70 (1.37, 4.84)</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Helvetica Neue"/>
+        <family val="2"/>
+      </rPr>
+      <t>Table 3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Helvetica Neue"/>
+        <family val="2"/>
+      </rPr>
+      <t>. Logistic regression odds ratios (95% CI) for COVID-19 outcomes by cancer type using restricted electronic health record for cancer recency analysis.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Helvetica Neue"/>
+        <family val="2"/>
+      </rPr>
+      <t>Table 2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Helvetica Neue"/>
+        <family val="2"/>
+      </rPr>
+      <t>. Logistic regression odds ratios (95% CI) for COVID-19 outcomes by cancer and by cancer treatment type using restricted electronic health record for cancer recency analysis.</t>
+    </r>
   </si>
 </sst>
 </file>
@@ -3229,7 +3790,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="95">
+  <cellXfs count="98">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
@@ -3424,14 +3985,14 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -3444,6 +4005,15 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -3466,8 +4036,8 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -3794,16 +4364,16 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:9" x14ac:dyDescent="0.15">
-      <c r="B2" s="80" t="s">
+      <c r="B2" s="87" t="s">
         <v>430</v>
       </c>
-      <c r="C2" s="80"/>
-      <c r="D2" s="80"/>
-      <c r="E2" s="80"/>
-      <c r="F2" s="80"/>
-      <c r="G2" s="80"/>
-      <c r="H2" s="80"/>
-      <c r="I2" s="80"/>
+      <c r="C2" s="87"/>
+      <c r="D2" s="87"/>
+      <c r="E2" s="87"/>
+      <c r="F2" s="87"/>
+      <c r="G2" s="87"/>
+      <c r="H2" s="87"/>
+      <c r="I2" s="87"/>
     </row>
     <row r="3" spans="2:9" x14ac:dyDescent="0.15">
       <c r="B3" s="4"/>
@@ -4656,25 +5226,25 @@
         <v>205</v>
       </c>
       <c r="C41" s="11" t="s">
-        <v>832</v>
+        <v>811</v>
       </c>
       <c r="D41" s="11" t="s">
-        <v>833</v>
+        <v>812</v>
       </c>
       <c r="E41" s="11" t="s">
-        <v>834</v>
+        <v>813</v>
       </c>
       <c r="F41" s="28" t="s">
-        <v>838</v>
+        <v>817</v>
       </c>
       <c r="G41" s="23" t="s">
-        <v>835</v>
+        <v>814</v>
       </c>
       <c r="H41" s="23" t="s">
-        <v>836</v>
+        <v>815</v>
       </c>
       <c r="I41" s="23" t="s">
-        <v>837</v>
+        <v>816</v>
       </c>
     </row>
     <row r="42" spans="2:9" ht="13" x14ac:dyDescent="0.15">
@@ -5645,7 +6215,7 @@
     </row>
     <row r="84" spans="2:9" x14ac:dyDescent="0.15">
       <c r="B84" s="14" t="s">
-        <v>842</v>
+        <v>821</v>
       </c>
       <c r="C84" s="13" t="s">
         <v>588</v>
@@ -5671,7 +6241,7 @@
     </row>
     <row r="85" spans="2:9" x14ac:dyDescent="0.15">
       <c r="B85" s="14" t="s">
-        <v>841</v>
+        <v>820</v>
       </c>
       <c r="C85" s="13" t="s">
         <v>588</v>
@@ -5697,7 +6267,7 @@
     </row>
     <row r="86" spans="2:9" x14ac:dyDescent="0.15">
       <c r="B86" s="14" t="s">
-        <v>840</v>
+        <v>819</v>
       </c>
       <c r="C86" s="13" t="s">
         <v>588</v>
@@ -5723,7 +6293,7 @@
     </row>
     <row r="87" spans="2:9" x14ac:dyDescent="0.15">
       <c r="B87" s="14" t="s">
-        <v>839</v>
+        <v>818</v>
       </c>
       <c r="C87" s="13" t="s">
         <v>588</v>
@@ -5774,28 +6344,28 @@
       </c>
     </row>
     <row r="89" spans="2:9" x14ac:dyDescent="0.15">
-      <c r="B89" s="81" t="s">
+      <c r="B89" s="88" t="s">
         <v>431</v>
       </c>
-      <c r="C89" s="81"/>
-      <c r="D89" s="81"/>
-      <c r="E89" s="81"/>
-      <c r="F89" s="81"/>
-      <c r="G89" s="81"/>
-      <c r="H89" s="81"/>
-      <c r="I89" s="81"/>
+      <c r="C89" s="88"/>
+      <c r="D89" s="88"/>
+      <c r="E89" s="88"/>
+      <c r="F89" s="88"/>
+      <c r="G89" s="88"/>
+      <c r="H89" s="88"/>
+      <c r="I89" s="88"/>
     </row>
     <row r="90" spans="2:9" ht="13" x14ac:dyDescent="0.15">
-      <c r="B90" s="82" t="s">
+      <c r="B90" s="89" t="s">
         <v>432</v>
       </c>
-      <c r="C90" s="82"/>
-      <c r="D90" s="82"/>
-      <c r="E90" s="82"/>
-      <c r="F90" s="82"/>
-      <c r="G90" s="82"/>
-      <c r="H90" s="82"/>
-      <c r="I90" s="82"/>
+      <c r="C90" s="89"/>
+      <c r="D90" s="89"/>
+      <c r="E90" s="89"/>
+      <c r="F90" s="89"/>
+      <c r="G90" s="89"/>
+      <c r="H90" s="89"/>
+      <c r="I90" s="89"/>
     </row>
     <row r="91" spans="2:9" ht="37" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B91" s="83" t="s">
@@ -5858,41 +6428,39 @@
     <col min="3" max="3" width="14.33203125" style="1" hidden="1" customWidth="1"/>
     <col min="4" max="7" width="15.6640625" style="1" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="1.83203125" style="1" customWidth="1"/>
-    <col min="9" max="9" width="10" style="47" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="16.6640625" style="47" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="7.5" style="47" bestFit="1" customWidth="1"/>
     <col min="11" max="16384" width="10.83203125" style="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:10" ht="32" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B2" s="89" t="s">
-        <v>627</v>
-      </c>
-      <c r="C2" s="89"/>
-      <c r="D2" s="89"/>
-      <c r="E2" s="89"/>
-      <c r="F2" s="89"/>
-      <c r="G2" s="89"/>
-      <c r="H2" s="89"/>
-      <c r="I2" s="89"/>
-      <c r="J2" s="89"/>
+      <c r="B2" s="92" t="s">
+        <v>606</v>
+      </c>
+      <c r="C2" s="92"/>
+      <c r="D2" s="92"/>
+      <c r="E2" s="92"/>
+      <c r="F2" s="92"/>
+      <c r="G2" s="92"/>
+      <c r="H2" s="92"/>
+      <c r="I2" s="92"/>
+      <c r="J2" s="92"/>
     </row>
     <row r="3" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="D3" s="87" t="s">
+      <c r="D3" s="90" t="s">
         <v>499</v>
       </c>
-      <c r="E3" s="88"/>
-      <c r="F3" s="88"/>
-      <c r="G3" s="88"/>
+      <c r="E3" s="91"/>
+      <c r="F3" s="91"/>
+      <c r="G3" s="91"/>
       <c r="H3" s="31"/>
-      <c r="I3" s="88" t="s">
+      <c r="I3" s="91" t="s">
         <v>502</v>
       </c>
-      <c r="J3" s="88"/>
-    </row>
-    <row r="4" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="B4" s="32" t="s">
-        <v>500</v>
-      </c>
+      <c r="J3" s="91"/>
+    </row>
+    <row r="4" spans="2:10" ht="34" x14ac:dyDescent="0.2">
+      <c r="B4" s="32"/>
       <c r="C4" s="2" t="s">
         <v>442</v>
       </c>
@@ -5909,8 +6477,8 @@
         <v>424</v>
       </c>
       <c r="H4" s="32"/>
-      <c r="I4" s="33" t="s">
-        <v>500</v>
+      <c r="I4" s="97" t="s">
+        <v>986</v>
       </c>
       <c r="J4" s="33" t="s">
         <v>501</v>
@@ -5991,16 +6559,16 @@
         <v>443</v>
       </c>
       <c r="D8" s="52" t="s">
-        <v>843</v>
+        <v>822</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>844</v>
+        <v>823</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>845</v>
+        <v>824</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>846</v>
+        <v>825</v>
       </c>
       <c r="H8" s="38"/>
       <c r="I8" s="39">
@@ -6018,10 +6586,10 @@
         <v>443</v>
       </c>
       <c r="D9" s="52" t="s">
-        <v>847</v>
+        <v>826</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>848</v>
+        <v>827</v>
       </c>
       <c r="F9" s="3" t="s">
         <v>449</v>
@@ -6137,16 +6705,16 @@
         <v>455</v>
       </c>
       <c r="D14" s="54" t="s">
-        <v>849</v>
+        <v>828</v>
       </c>
       <c r="E14" s="47" t="s">
-        <v>850</v>
+        <v>829</v>
       </c>
       <c r="F14" s="47" t="s">
-        <v>851</v>
+        <v>830</v>
       </c>
       <c r="G14" s="47" t="s">
-        <v>852</v>
+        <v>831</v>
       </c>
       <c r="I14" s="48">
         <v>4613</v>
@@ -6163,16 +6731,16 @@
         <v>455</v>
       </c>
       <c r="D15" s="54" t="s">
-        <v>853</v>
+        <v>832</v>
       </c>
       <c r="E15" s="47" t="s">
-        <v>854</v>
+        <v>833</v>
       </c>
       <c r="F15" s="47" t="s">
-        <v>855</v>
+        <v>834</v>
       </c>
       <c r="G15" s="47" t="s">
-        <v>856</v>
+        <v>835</v>
       </c>
       <c r="I15" s="48">
         <v>4129</v>
@@ -6189,16 +6757,16 @@
         <v>455</v>
       </c>
       <c r="D16" s="55" t="s">
-        <v>857</v>
+        <v>836</v>
       </c>
       <c r="E16" s="44" t="s">
-        <v>858</v>
+        <v>837</v>
       </c>
       <c r="F16" s="44" t="s">
-        <v>859</v>
+        <v>838</v>
       </c>
       <c r="G16" s="44" t="s">
-        <v>860</v>
+        <v>839</v>
       </c>
       <c r="H16" s="2"/>
       <c r="I16" s="45">
@@ -6286,7 +6854,7 @@
         <v>473</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>861</v>
+        <v>840</v>
       </c>
       <c r="F20" s="3" t="s">
         <v>474</v>
@@ -6310,13 +6878,13 @@
         <v>464</v>
       </c>
       <c r="D21" s="52" t="s">
-        <v>862</v>
+        <v>841</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>863</v>
+        <v>842</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>864</v>
+        <v>843</v>
       </c>
       <c r="G21" s="3" t="s">
         <v>476</v>
@@ -6337,16 +6905,16 @@
         <v>464</v>
       </c>
       <c r="D22" s="53" t="s">
-        <v>865</v>
+        <v>844</v>
       </c>
       <c r="E22" s="42" t="s">
-        <v>866</v>
+        <v>845</v>
       </c>
       <c r="F22" s="42" t="s">
-        <v>867</v>
+        <v>846</v>
       </c>
       <c r="G22" s="42" t="s">
-        <v>868</v>
+        <v>847</v>
       </c>
       <c r="H22" s="41"/>
       <c r="I22" s="43">
@@ -6429,13 +6997,13 @@
         <v>478</v>
       </c>
       <c r="D26" s="54" t="s">
-        <v>869</v>
+        <v>848</v>
       </c>
       <c r="E26" s="47" t="s">
-        <v>870</v>
+        <v>849</v>
       </c>
       <c r="F26" s="47" t="s">
-        <v>871</v>
+        <v>850</v>
       </c>
       <c r="G26" s="47" t="s">
         <v>487</v>
@@ -6484,10 +7052,10 @@
         <v>492</v>
       </c>
       <c r="E28" s="44" t="s">
-        <v>872</v>
+        <v>851</v>
       </c>
       <c r="F28" s="44" t="s">
-        <v>873</v>
+        <v>852</v>
       </c>
       <c r="G28" s="44" t="s">
         <v>493</v>
@@ -6501,17 +7069,17 @@
       </c>
     </row>
     <row r="29" spans="2:10" ht="65" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B29" s="90" t="s">
+      <c r="B29" s="93" t="s">
         <v>503</v>
       </c>
-      <c r="C29" s="91"/>
-      <c r="D29" s="91"/>
-      <c r="E29" s="91"/>
-      <c r="F29" s="91"/>
-      <c r="G29" s="91"/>
-      <c r="H29" s="91"/>
-      <c r="I29" s="91"/>
-      <c r="J29" s="91"/>
+      <c r="C29" s="94"/>
+      <c r="D29" s="94"/>
+      <c r="E29" s="94"/>
+      <c r="F29" s="94"/>
+      <c r="G29" s="94"/>
+      <c r="H29" s="94"/>
+      <c r="I29" s="94"/>
+      <c r="J29" s="94"/>
     </row>
   </sheetData>
   <mergeCells count="4">
@@ -6535,40 +7103,39 @@
     <col min="4" max="6" width="15.6640625" style="1" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="17" style="1" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="1.83203125" style="1" customWidth="1"/>
-    <col min="9" max="10" width="10.83203125" style="47"/>
+    <col min="9" max="9" width="12.6640625" style="47" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="10.83203125" style="47"/>
     <col min="11" max="16384" width="10.83203125" style="1"/>
   </cols>
   <sheetData>
     <row r="3" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="B3" s="89" t="s">
+      <c r="B3" s="92" t="s">
         <v>579</v>
       </c>
-      <c r="C3" s="89"/>
-      <c r="D3" s="89"/>
-      <c r="E3" s="89"/>
-      <c r="F3" s="89"/>
-      <c r="G3" s="89"/>
-      <c r="H3" s="89"/>
-      <c r="I3" s="89"/>
-      <c r="J3" s="89"/>
+      <c r="C3" s="92"/>
+      <c r="D3" s="92"/>
+      <c r="E3" s="92"/>
+      <c r="F3" s="92"/>
+      <c r="G3" s="92"/>
+      <c r="H3" s="92"/>
+      <c r="I3" s="92"/>
+      <c r="J3" s="92"/>
     </row>
     <row r="4" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="D4" s="87" t="s">
+      <c r="D4" s="90" t="s">
         <v>499</v>
       </c>
-      <c r="E4" s="88"/>
-      <c r="F4" s="88"/>
-      <c r="G4" s="88"/>
+      <c r="E4" s="91"/>
+      <c r="F4" s="91"/>
+      <c r="G4" s="91"/>
       <c r="H4" s="31"/>
-      <c r="I4" s="88" t="s">
+      <c r="I4" s="91" t="s">
         <v>502</v>
       </c>
-      <c r="J4" s="88"/>
+      <c r="J4" s="91"/>
     </row>
     <row r="5" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="B5" s="32" t="s">
-        <v>500</v>
-      </c>
+      <c r="B5" s="32"/>
       <c r="C5" s="2" t="s">
         <v>442</v>
       </c>
@@ -6586,7 +7153,7 @@
       </c>
       <c r="H5" s="32"/>
       <c r="I5" s="33" t="s">
-        <v>500</v>
+        <v>987</v>
       </c>
       <c r="J5" s="33" t="s">
         <v>501</v>
@@ -6667,10 +7234,10 @@
         <v>504</v>
       </c>
       <c r="D9" s="52" t="s">
-        <v>892</v>
+        <v>871</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>893</v>
+        <v>872</v>
       </c>
       <c r="F9" s="3" t="s">
         <v>511</v>
@@ -6694,10 +7261,10 @@
         <v>504</v>
       </c>
       <c r="D10" s="52" t="s">
-        <v>894</v>
+        <v>873</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>895</v>
+        <v>874</v>
       </c>
       <c r="F10" s="3" t="s">
         <v>513</v>
@@ -6721,13 +7288,13 @@
         <v>504</v>
       </c>
       <c r="D11" s="53" t="s">
-        <v>896</v>
+        <v>875</v>
       </c>
       <c r="E11" s="42" t="s">
-        <v>897</v>
+        <v>876</v>
       </c>
       <c r="F11" s="42" t="s">
-        <v>898</v>
+        <v>877</v>
       </c>
       <c r="G11" s="42" t="s">
         <v>515</v>
@@ -6813,16 +7380,16 @@
         <v>516</v>
       </c>
       <c r="D15" s="59" t="s">
-        <v>877</v>
+        <v>856</v>
       </c>
       <c r="E15" s="60" t="s">
-        <v>878</v>
+        <v>857</v>
       </c>
       <c r="F15" s="60" t="s">
-        <v>879</v>
+        <v>858</v>
       </c>
       <c r="G15" s="60" t="s">
-        <v>880</v>
+        <v>859</v>
       </c>
       <c r="I15" s="48">
         <v>2410</v>
@@ -6839,16 +7406,16 @@
         <v>516</v>
       </c>
       <c r="D16" s="59" t="s">
-        <v>881</v>
+        <v>860</v>
       </c>
       <c r="E16" s="60" t="s">
-        <v>882</v>
+        <v>861</v>
       </c>
       <c r="F16" s="60" t="s">
         <v>524</v>
       </c>
       <c r="G16" s="60" t="s">
-        <v>883</v>
+        <v>862</v>
       </c>
       <c r="I16" s="48">
         <v>2154</v>
@@ -6986,7 +7553,7 @@
         <v>529</v>
       </c>
       <c r="D22" s="65" t="s">
-        <v>874</v>
+        <v>853</v>
       </c>
       <c r="E22" s="66" t="s">
         <v>542</v>
@@ -7013,13 +7580,13 @@
         <v>529</v>
       </c>
       <c r="D23" s="68" t="s">
-        <v>875</v>
+        <v>854</v>
       </c>
       <c r="E23" s="69" t="s">
         <v>545</v>
       </c>
       <c r="F23" s="69" t="s">
-        <v>876</v>
+        <v>855</v>
       </c>
       <c r="G23" s="69" t="s">
         <v>546</v>
@@ -7114,7 +7681,7 @@
         <v>558</v>
       </c>
       <c r="G27" s="60" t="s">
-        <v>899</v>
+        <v>878</v>
       </c>
       <c r="I27" s="48">
         <v>1058</v>
@@ -7157,7 +7724,7 @@
         <v>547</v>
       </c>
       <c r="D29" s="61" t="s">
-        <v>900</v>
+        <v>879</v>
       </c>
       <c r="E29" s="62" t="s">
         <v>563</v>
@@ -7251,16 +7818,16 @@
         <v>566</v>
       </c>
       <c r="D33" s="65" t="s">
-        <v>884</v>
+        <v>863</v>
       </c>
       <c r="E33" s="66" t="s">
-        <v>885</v>
+        <v>864</v>
       </c>
       <c r="F33" s="66" t="s">
-        <v>886</v>
+        <v>865</v>
       </c>
       <c r="G33" s="66" t="s">
-        <v>887</v>
+        <v>866</v>
       </c>
       <c r="H33" s="38"/>
       <c r="I33" s="39">
@@ -7278,16 +7845,16 @@
         <v>566</v>
       </c>
       <c r="D34" s="65" t="s">
-        <v>888</v>
+        <v>867</v>
       </c>
       <c r="E34" s="66" t="s">
-        <v>889</v>
+        <v>868</v>
       </c>
       <c r="F34" s="66" t="s">
         <v>575</v>
       </c>
       <c r="G34" s="66" t="s">
-        <v>890</v>
+        <v>869</v>
       </c>
       <c r="H34" s="38"/>
       <c r="I34" s="39">
@@ -7308,7 +7875,7 @@
         <v>576</v>
       </c>
       <c r="E35" s="69" t="s">
-        <v>891</v>
+        <v>870</v>
       </c>
       <c r="F35" s="69" t="s">
         <v>577</v>
@@ -7325,17 +7892,17 @@
       </c>
     </row>
     <row r="36" spans="2:10" ht="66" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B36" s="90" t="s">
+      <c r="B36" s="93" t="s">
         <v>580</v>
       </c>
-      <c r="C36" s="90"/>
-      <c r="D36" s="90"/>
-      <c r="E36" s="90"/>
-      <c r="F36" s="90"/>
-      <c r="G36" s="90"/>
-      <c r="H36" s="90"/>
-      <c r="I36" s="90"/>
-      <c r="J36" s="90"/>
+      <c r="C36" s="93"/>
+      <c r="D36" s="93"/>
+      <c r="E36" s="93"/>
+      <c r="F36" s="93"/>
+      <c r="G36" s="93"/>
+      <c r="H36" s="93"/>
+      <c r="I36" s="93"/>
+      <c r="J36" s="93"/>
     </row>
   </sheetData>
   <mergeCells count="4">
@@ -7367,25 +7934,25 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:11" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B2" s="92" t="s">
-        <v>625</v>
-      </c>
-      <c r="C2" s="92"/>
-      <c r="D2" s="92"/>
-      <c r="E2" s="92"/>
-      <c r="F2" s="92"/>
-      <c r="G2" s="92"/>
-      <c r="H2" s="92"/>
-      <c r="I2" s="92"/>
-      <c r="J2" s="92"/>
-      <c r="K2" s="92"/>
+      <c r="B2" s="95" t="s">
+        <v>604</v>
+      </c>
+      <c r="C2" s="95"/>
+      <c r="D2" s="95"/>
+      <c r="E2" s="95"/>
+      <c r="F2" s="95"/>
+      <c r="G2" s="95"/>
+      <c r="H2" s="95"/>
+      <c r="I2" s="95"/>
+      <c r="J2" s="95"/>
+      <c r="K2" s="95"/>
     </row>
     <row r="3" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B3" s="31"/>
-      <c r="C3" s="88" t="s">
+      <c r="C3" s="91" t="s">
         <v>593</v>
       </c>
-      <c r="D3" s="88"/>
+      <c r="D3" s="91"/>
       <c r="E3" s="72"/>
       <c r="F3" s="72"/>
       <c r="G3" s="72"/>
@@ -7400,15 +7967,15 @@
         <v>595</v>
       </c>
       <c r="E4" s="72"/>
-      <c r="F4" s="88" t="s">
+      <c r="F4" s="91" t="s">
         <v>597</v>
       </c>
-      <c r="G4" s="88"/>
-      <c r="H4" s="88"/>
-      <c r="J4" s="88" t="s">
+      <c r="G4" s="91"/>
+      <c r="H4" s="91"/>
+      <c r="J4" s="91" t="s">
         <v>502</v>
       </c>
-      <c r="K4" s="88"/>
+      <c r="K4" s="91"/>
     </row>
     <row r="5" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B5" s="32" t="s">
@@ -7454,23 +8021,23 @@
     </row>
     <row r="7" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B7" s="37" t="s">
-        <v>840</v>
+        <v>819</v>
       </c>
       <c r="C7" s="38" t="s">
-        <v>618</v>
+        <v>903</v>
       </c>
       <c r="D7" s="38" t="s">
-        <v>603</v>
+        <v>892</v>
       </c>
       <c r="E7" s="38"/>
       <c r="F7" s="3">
-        <v>0.14000000000000001</v>
+        <v>0.02</v>
       </c>
       <c r="G7" s="76" t="s">
-        <v>610</v>
-      </c>
-      <c r="H7" s="94" t="s">
-        <v>901</v>
+        <v>601</v>
+      </c>
+      <c r="H7" s="82">
+        <v>0.28999999999999998</v>
       </c>
       <c r="I7" s="38"/>
       <c r="J7" s="3">
@@ -7482,23 +8049,23 @@
     </row>
     <row r="8" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B8" s="37" t="s">
-        <v>841</v>
+        <v>820</v>
       </c>
       <c r="C8" s="38" t="s">
-        <v>615</v>
+        <v>902</v>
       </c>
       <c r="D8" s="38" t="s">
-        <v>599</v>
+        <v>893</v>
       </c>
       <c r="E8" s="38"/>
       <c r="F8" s="3" t="s">
-        <v>610</v>
+        <v>601</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>610</v>
+        <v>601</v>
       </c>
       <c r="H8" s="3">
-        <v>0.27</v>
+        <v>0.31</v>
       </c>
       <c r="I8" s="38"/>
       <c r="J8" s="3">
@@ -7510,23 +8077,23 @@
     </row>
     <row r="9" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B9" s="40" t="s">
-        <v>842</v>
+        <v>821</v>
       </c>
       <c r="C9" s="41" t="s">
-        <v>611</v>
+        <v>904</v>
       </c>
       <c r="D9" s="41" t="s">
-        <v>606</v>
+        <v>894</v>
       </c>
       <c r="E9" s="41"/>
       <c r="F9" s="42" t="s">
-        <v>610</v>
+        <v>601</v>
       </c>
       <c r="G9" s="42" t="s">
-        <v>610</v>
+        <v>601</v>
       </c>
       <c r="H9" s="42">
-        <v>0.55000000000000004</v>
+        <v>0.63</v>
       </c>
       <c r="I9" s="41"/>
       <c r="J9" s="42">
@@ -7552,22 +8119,22 @@
     </row>
     <row r="11" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B11" s="46" t="s">
-        <v>840</v>
+        <v>819</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>619</v>
+        <v>905</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>902</v>
+        <v>895</v>
       </c>
       <c r="F11" s="47">
-        <v>0.46</v>
+        <v>0.14000000000000001</v>
       </c>
       <c r="G11" s="47" t="s">
-        <v>610</v>
+        <v>601</v>
       </c>
       <c r="H11" s="47">
-        <v>0.23</v>
+        <v>0.22</v>
       </c>
       <c r="J11" s="47">
         <v>62</v>
@@ -7578,22 +8145,22 @@
     </row>
     <row r="12" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B12" s="46" t="s">
-        <v>841</v>
+        <v>820</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>616</v>
+        <v>906</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>600</v>
+        <v>896</v>
       </c>
       <c r="F12" s="77" t="s">
-        <v>623</v>
+        <v>601</v>
       </c>
       <c r="G12" s="47" t="s">
-        <v>610</v>
+        <v>601</v>
       </c>
       <c r="H12" s="47">
-        <v>0.25</v>
+        <v>0.28000000000000003</v>
       </c>
       <c r="J12" s="47">
         <v>94</v>
@@ -7604,23 +8171,23 @@
     </row>
     <row r="13" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B13" s="74" t="s">
-        <v>842</v>
+        <v>821</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>612</v>
+        <v>907</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>607</v>
+        <v>897</v>
       </c>
       <c r="E13" s="75"/>
       <c r="F13" s="78" t="s">
-        <v>610</v>
+        <v>601</v>
       </c>
       <c r="G13" s="78" t="s">
-        <v>610</v>
-      </c>
-      <c r="H13" s="79" t="s">
-        <v>622</v>
+        <v>601</v>
+      </c>
+      <c r="H13" s="79">
+        <v>0.89</v>
       </c>
       <c r="I13" s="2"/>
       <c r="J13" s="44">
@@ -7646,13 +8213,13 @@
     </row>
     <row r="15" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B15" s="37" t="s">
-        <v>840</v>
+        <v>819</v>
       </c>
       <c r="C15" s="38" t="s">
-        <v>620</v>
+        <v>602</v>
       </c>
       <c r="D15" s="38" t="s">
-        <v>604</v>
+        <v>600</v>
       </c>
       <c r="E15" s="38"/>
       <c r="F15" s="3">
@@ -7674,20 +8241,20 @@
     </row>
     <row r="16" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B16" s="37" t="s">
-        <v>841</v>
+        <v>820</v>
       </c>
       <c r="C16" s="38" t="s">
-        <v>903</v>
+        <v>880</v>
       </c>
       <c r="D16" s="38" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
       <c r="E16" s="38"/>
       <c r="F16" s="3">
         <v>0.02</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>610</v>
+        <v>601</v>
       </c>
       <c r="H16" s="3">
         <v>0.05</v>
@@ -7702,20 +8269,20 @@
     </row>
     <row r="17" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B17" s="40" t="s">
-        <v>842</v>
+        <v>821</v>
       </c>
       <c r="C17" s="41" t="s">
-        <v>613</v>
+        <v>908</v>
       </c>
       <c r="D17" s="41" t="s">
-        <v>608</v>
+        <v>898</v>
       </c>
       <c r="E17" s="41"/>
       <c r="F17" s="42" t="s">
-        <v>610</v>
+        <v>601</v>
       </c>
       <c r="G17" s="42" t="s">
-        <v>610</v>
+        <v>601</v>
       </c>
       <c r="H17" s="42">
         <v>0.73</v>
@@ -7744,19 +8311,19 @@
     </row>
     <row r="19" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B19" s="46" t="s">
-        <v>840</v>
+        <v>819</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>621</v>
+        <v>909</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>605</v>
+        <v>899</v>
       </c>
       <c r="F19" s="47" t="s">
-        <v>610</v>
+        <v>601</v>
       </c>
       <c r="G19" s="47" t="s">
-        <v>610</v>
+        <v>601</v>
       </c>
       <c r="H19" s="47">
         <v>0.74</v>
@@ -7770,22 +8337,22 @@
     </row>
     <row r="20" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B20" s="46" t="s">
-        <v>841</v>
+        <v>820</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>617</v>
+        <v>910</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>602</v>
+        <v>900</v>
       </c>
       <c r="F20" s="47" t="s">
-        <v>610</v>
+        <v>601</v>
       </c>
       <c r="G20" s="47" t="s">
-        <v>610</v>
+        <v>601</v>
       </c>
       <c r="H20" s="47">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="J20" s="47">
         <v>2</v>
@@ -7796,20 +8363,20 @@
     </row>
     <row r="21" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B21" s="49" t="s">
-        <v>842</v>
+        <v>821</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>614</v>
+        <v>911</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>609</v>
+        <v>901</v>
       </c>
       <c r="E21" s="2"/>
       <c r="F21" s="44" t="s">
-        <v>610</v>
+        <v>601</v>
       </c>
       <c r="G21" s="44" t="s">
-        <v>610</v>
+        <v>601</v>
       </c>
       <c r="H21" s="44">
         <v>0.08</v>
@@ -7823,18 +8390,18 @@
       </c>
     </row>
     <row r="22" spans="2:11" ht="32" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B22" s="90" t="s">
-        <v>624</v>
-      </c>
-      <c r="C22" s="90"/>
-      <c r="D22" s="90"/>
-      <c r="E22" s="90"/>
-      <c r="F22" s="90"/>
-      <c r="G22" s="90"/>
-      <c r="H22" s="90"/>
-      <c r="I22" s="90"/>
-      <c r="J22" s="90"/>
-      <c r="K22" s="90"/>
+      <c r="B22" s="93" t="s">
+        <v>603</v>
+      </c>
+      <c r="C22" s="93"/>
+      <c r="D22" s="93"/>
+      <c r="E22" s="93"/>
+      <c r="F22" s="93"/>
+      <c r="G22" s="93"/>
+      <c r="H22" s="93"/>
+      <c r="I22" s="93"/>
+      <c r="J22" s="93"/>
+      <c r="K22" s="93"/>
     </row>
   </sheetData>
   <mergeCells count="5">
@@ -7860,32 +8427,32 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:10" ht="32" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B2" s="89" t="s">
-        <v>626</v>
-      </c>
-      <c r="C2" s="89"/>
-      <c r="D2" s="89"/>
-      <c r="E2" s="89"/>
-      <c r="F2" s="89"/>
-      <c r="G2" s="89"/>
-      <c r="H2" s="89"/>
-      <c r="I2" s="89"/>
-      <c r="J2" s="89"/>
+      <c r="B2" s="92" t="s">
+        <v>605</v>
+      </c>
+      <c r="C2" s="92"/>
+      <c r="D2" s="92"/>
+      <c r="E2" s="92"/>
+      <c r="F2" s="92"/>
+      <c r="G2" s="92"/>
+      <c r="H2" s="92"/>
+      <c r="I2" s="92"/>
+      <c r="J2" s="92"/>
     </row>
     <row r="3" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B3" s="1"/>
       <c r="C3" s="1"/>
-      <c r="D3" s="87" t="s">
+      <c r="D3" s="90" t="s">
         <v>499</v>
       </c>
-      <c r="E3" s="88"/>
-      <c r="F3" s="88"/>
-      <c r="G3" s="88"/>
+      <c r="E3" s="91"/>
+      <c r="F3" s="91"/>
+      <c r="G3" s="91"/>
       <c r="H3" s="31"/>
-      <c r="I3" s="88" t="s">
+      <c r="I3" s="91" t="s">
         <v>502</v>
       </c>
-      <c r="J3" s="88"/>
+      <c r="J3" s="91"/>
     </row>
     <row r="4" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B4" s="32" t="s">
@@ -7989,16 +8556,16 @@
         <v>443</v>
       </c>
       <c r="D8" s="52" t="s">
-        <v>904</v>
+        <v>881</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>905</v>
+        <v>882</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>906</v>
+        <v>883</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>907</v>
+        <v>884</v>
       </c>
       <c r="H8" s="38"/>
       <c r="I8" s="39">
@@ -8016,16 +8583,16 @@
         <v>443</v>
       </c>
       <c r="D9" s="52" t="s">
-        <v>908</v>
+        <v>885</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>909</v>
+        <v>886</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>910</v>
+        <v>887</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>911</v>
+        <v>888</v>
       </c>
       <c r="H9" s="38"/>
       <c r="I9" s="39">
@@ -8043,13 +8610,13 @@
         <v>443</v>
       </c>
       <c r="D10" s="53" t="s">
-        <v>912</v>
+        <v>889</v>
       </c>
       <c r="E10" s="42" t="s">
-        <v>913</v>
+        <v>890</v>
       </c>
       <c r="F10" s="42" t="s">
-        <v>914</v>
+        <v>891</v>
       </c>
       <c r="G10" s="42" t="s">
         <v>587</v>
@@ -8063,17 +8630,17 @@
       </c>
     </row>
     <row r="11" spans="2:10" ht="66" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B11" s="90" t="s">
+      <c r="B11" s="93" t="s">
         <v>503</v>
       </c>
-      <c r="C11" s="91"/>
-      <c r="D11" s="91"/>
-      <c r="E11" s="91"/>
-      <c r="F11" s="91"/>
-      <c r="G11" s="91"/>
-      <c r="H11" s="91"/>
-      <c r="I11" s="91"/>
-      <c r="J11" s="91"/>
+      <c r="C11" s="94"/>
+      <c r="D11" s="94"/>
+      <c r="E11" s="94"/>
+      <c r="F11" s="94"/>
+      <c r="G11" s="94"/>
+      <c r="H11" s="94"/>
+      <c r="I11" s="94"/>
+      <c r="J11" s="94"/>
     </row>
   </sheetData>
   <mergeCells count="4">
@@ -8107,63 +8674,63 @@
   </cols>
   <sheetData>
     <row r="3" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B3" s="93" t="s">
-        <v>831</v>
-      </c>
-      <c r="C3" s="93"/>
-      <c r="D3" s="93"/>
-      <c r="E3" s="93"/>
-      <c r="F3" s="93"/>
-      <c r="G3" s="93"/>
-      <c r="H3" s="93"/>
-      <c r="I3" s="93"/>
-      <c r="J3" s="93"/>
-      <c r="K3" s="93"/>
-      <c r="L3" s="93"/>
+      <c r="B3" s="96" t="s">
+        <v>810</v>
+      </c>
+      <c r="C3" s="96"/>
+      <c r="D3" s="96"/>
+      <c r="E3" s="96"/>
+      <c r="F3" s="96"/>
+      <c r="G3" s="96"/>
+      <c r="H3" s="96"/>
+      <c r="I3" s="96"/>
+      <c r="J3" s="96"/>
+      <c r="K3" s="96"/>
+      <c r="L3" s="96"/>
     </row>
     <row r="4" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B4" s="32" t="s">
-        <v>828</v>
+        <v>807</v>
       </c>
       <c r="C4" s="32" t="s">
-        <v>829</v>
+        <v>808</v>
       </c>
       <c r="D4" s="71" t="s">
-        <v>830</v>
+        <v>809</v>
       </c>
       <c r="E4" s="32"/>
       <c r="F4" s="32" t="s">
-        <v>828</v>
+        <v>807</v>
       </c>
       <c r="G4" s="32" t="s">
-        <v>829</v>
+        <v>808</v>
       </c>
       <c r="H4" s="71" t="s">
-        <v>830</v>
+        <v>809</v>
       </c>
       <c r="I4" s="32"/>
       <c r="J4" s="32" t="s">
-        <v>828</v>
+        <v>807</v>
       </c>
       <c r="K4" s="32" t="s">
-        <v>829</v>
+        <v>808</v>
       </c>
       <c r="L4" s="71" t="s">
-        <v>830</v>
+        <v>809</v>
       </c>
     </row>
     <row r="5" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B5" s="38" t="s">
-        <v>628</v>
+        <v>607</v>
       </c>
       <c r="C5" s="38" t="s">
-        <v>629</v>
+        <v>608</v>
       </c>
       <c r="D5" s="39">
         <v>284</v>
       </c>
       <c r="F5" s="38" t="s">
-        <v>696</v>
+        <v>675</v>
       </c>
       <c r="G5" s="38" t="s">
         <v>529</v>
@@ -8172,10 +8739,10 @@
         <v>1247</v>
       </c>
       <c r="J5" s="38" t="s">
-        <v>763</v>
+        <v>742</v>
       </c>
       <c r="K5" s="38" t="s">
-        <v>764</v>
+        <v>743</v>
       </c>
       <c r="L5" s="39">
         <v>205</v>
@@ -8183,28 +8750,28 @@
     </row>
     <row r="6" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
-        <v>630</v>
+        <v>609</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>631</v>
+        <v>610</v>
       </c>
       <c r="D6" s="48">
         <v>18</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>697</v>
+        <v>676</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>698</v>
+        <v>677</v>
       </c>
       <c r="H6" s="48">
         <v>1177</v>
       </c>
       <c r="J6" s="1" t="s">
-        <v>765</v>
+        <v>744</v>
       </c>
       <c r="K6" s="1" t="s">
-        <v>766</v>
+        <v>745</v>
       </c>
       <c r="L6" s="48">
         <v>787</v>
@@ -8212,25 +8779,25 @@
     </row>
     <row r="7" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B7" s="38" t="s">
-        <v>632</v>
+        <v>611</v>
       </c>
       <c r="C7" s="38" t="s">
-        <v>633</v>
+        <v>612</v>
       </c>
       <c r="D7" s="39">
         <v>92</v>
       </c>
       <c r="F7" s="38" t="s">
-        <v>699</v>
+        <v>678</v>
       </c>
       <c r="G7" s="38" t="s">
-        <v>700</v>
+        <v>679</v>
       </c>
       <c r="H7" s="39">
         <v>1144</v>
       </c>
       <c r="J7" s="38" t="s">
-        <v>767</v>
+        <v>746</v>
       </c>
       <c r="K7" s="38" t="s">
         <v>455</v>
@@ -8241,28 +8808,28 @@
     </row>
     <row r="8" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B8" s="1" t="s">
-        <v>634</v>
+        <v>613</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>635</v>
+        <v>614</v>
       </c>
       <c r="D8" s="48">
         <v>76</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>701</v>
+        <v>680</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>702</v>
+        <v>681</v>
       </c>
       <c r="H8" s="48">
         <v>9</v>
       </c>
       <c r="J8" s="1" t="s">
-        <v>768</v>
+        <v>747</v>
       </c>
       <c r="K8" s="1" t="s">
-        <v>769</v>
+        <v>748</v>
       </c>
       <c r="L8" s="48">
         <v>1594</v>
@@ -8270,28 +8837,28 @@
     </row>
     <row r="9" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B9" s="38" t="s">
-        <v>636</v>
+        <v>615</v>
       </c>
       <c r="C9" s="38" t="s">
-        <v>637</v>
+        <v>616</v>
       </c>
       <c r="D9" s="39">
         <v>23</v>
       </c>
       <c r="F9" s="38" t="s">
-        <v>703</v>
+        <v>682</v>
       </c>
       <c r="G9" s="38" t="s">
-        <v>704</v>
+        <v>683</v>
       </c>
       <c r="H9" s="39">
         <v>89</v>
       </c>
       <c r="J9" s="38" t="s">
-        <v>770</v>
+        <v>749</v>
       </c>
       <c r="K9" s="38" t="s">
-        <v>771</v>
+        <v>750</v>
       </c>
       <c r="L9" s="39">
         <v>907</v>
@@ -8299,28 +8866,28 @@
     </row>
     <row r="10" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B10" s="1" t="s">
-        <v>638</v>
+        <v>617</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>639</v>
+        <v>618</v>
       </c>
       <c r="D10" s="48">
         <v>18</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>705</v>
+        <v>684</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>706</v>
+        <v>685</v>
       </c>
       <c r="H10" s="48">
         <v>328</v>
       </c>
       <c r="J10" s="1" t="s">
-        <v>772</v>
+        <v>751</v>
       </c>
       <c r="K10" s="1" t="s">
-        <v>773</v>
+        <v>752</v>
       </c>
       <c r="L10" s="48">
         <v>329</v>
@@ -8328,28 +8895,28 @@
     </row>
     <row r="11" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B11" s="38" t="s">
-        <v>640</v>
+        <v>619</v>
       </c>
       <c r="C11" s="38" t="s">
-        <v>641</v>
+        <v>620</v>
       </c>
       <c r="D11" s="39">
         <v>253</v>
       </c>
       <c r="F11" s="38" t="s">
-        <v>707</v>
+        <v>686</v>
       </c>
       <c r="G11" s="38" t="s">
-        <v>708</v>
+        <v>687</v>
       </c>
       <c r="H11" s="39">
         <v>1281</v>
       </c>
       <c r="J11" s="38" t="s">
-        <v>774</v>
+        <v>753</v>
       </c>
       <c r="K11" s="38" t="s">
-        <v>775</v>
+        <v>754</v>
       </c>
       <c r="L11" s="39">
         <v>241</v>
@@ -8357,28 +8924,28 @@
     </row>
     <row r="12" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B12" s="1" t="s">
-        <v>642</v>
+        <v>621</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>643</v>
+        <v>622</v>
       </c>
       <c r="D12" s="48">
         <v>84</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>709</v>
+        <v>688</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>710</v>
+        <v>689</v>
       </c>
       <c r="H12" s="48">
         <v>193</v>
       </c>
       <c r="J12" s="1" t="s">
-        <v>776</v>
+        <v>755</v>
       </c>
       <c r="K12" s="1" t="s">
-        <v>777</v>
+        <v>756</v>
       </c>
       <c r="L12" s="48">
         <v>251</v>
@@ -8386,28 +8953,28 @@
     </row>
     <row r="13" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B13" s="38" t="s">
-        <v>644</v>
+        <v>623</v>
       </c>
       <c r="C13" s="38" t="s">
-        <v>645</v>
+        <v>624</v>
       </c>
       <c r="D13" s="39">
         <v>30</v>
       </c>
       <c r="F13" s="38" t="s">
-        <v>711</v>
+        <v>690</v>
       </c>
       <c r="G13" s="38" t="s">
-        <v>712</v>
+        <v>691</v>
       </c>
       <c r="H13" s="39">
         <v>1139</v>
       </c>
       <c r="J13" s="38" t="s">
-        <v>778</v>
+        <v>757</v>
       </c>
       <c r="K13" s="38" t="s">
-        <v>779</v>
+        <v>758</v>
       </c>
       <c r="L13" s="39">
         <v>153</v>
@@ -8415,28 +8982,28 @@
     </row>
     <row r="14" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B14" s="1" t="s">
-        <v>646</v>
+        <v>625</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>647</v>
+        <v>626</v>
       </c>
       <c r="D14" s="48">
         <v>19</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>713</v>
+        <v>692</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>714</v>
+        <v>693</v>
       </c>
       <c r="H14" s="48">
         <v>262</v>
       </c>
       <c r="J14" s="1" t="s">
-        <v>780</v>
+        <v>759</v>
       </c>
       <c r="K14" s="1" t="s">
-        <v>781</v>
+        <v>760</v>
       </c>
       <c r="L14" s="48">
         <v>320</v>
@@ -8444,28 +9011,28 @@
     </row>
     <row r="15" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B15" s="38" t="s">
-        <v>648</v>
+        <v>627</v>
       </c>
       <c r="C15" s="38" t="s">
-        <v>649</v>
+        <v>628</v>
       </c>
       <c r="D15" s="39">
         <v>78</v>
       </c>
       <c r="F15" s="38" t="s">
-        <v>715</v>
+        <v>694</v>
       </c>
       <c r="G15" s="38" t="s">
-        <v>716</v>
+        <v>695</v>
       </c>
       <c r="H15" s="39">
         <v>466</v>
       </c>
       <c r="J15" s="38" t="s">
-        <v>782</v>
+        <v>761</v>
       </c>
       <c r="K15" s="38" t="s">
-        <v>783</v>
+        <v>762</v>
       </c>
       <c r="L15" s="39">
         <v>68</v>
@@ -8473,28 +9040,28 @@
     </row>
     <row r="16" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B16" s="1" t="s">
-        <v>650</v>
+        <v>629</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>651</v>
+        <v>630</v>
       </c>
       <c r="D16" s="48">
         <v>69</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>717</v>
+        <v>696</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>718</v>
+        <v>697</v>
       </c>
       <c r="H16" s="48">
         <v>207</v>
       </c>
       <c r="J16" s="1" t="s">
-        <v>784</v>
+        <v>763</v>
       </c>
       <c r="K16" s="1" t="s">
-        <v>785</v>
+        <v>764</v>
       </c>
       <c r="L16" s="48">
         <v>2595</v>
@@ -8502,28 +9069,28 @@
     </row>
     <row r="17" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B17" s="38" t="s">
-        <v>652</v>
+        <v>631</v>
       </c>
       <c r="C17" s="38" t="s">
-        <v>653</v>
+        <v>632</v>
       </c>
       <c r="D17" s="39">
         <v>38</v>
       </c>
       <c r="F17" s="38" t="s">
-        <v>719</v>
+        <v>698</v>
       </c>
       <c r="G17" s="38" t="s">
-        <v>720</v>
+        <v>699</v>
       </c>
       <c r="H17" s="39">
         <v>159</v>
       </c>
       <c r="J17" s="38" t="s">
-        <v>786</v>
+        <v>765</v>
       </c>
       <c r="K17" s="38" t="s">
-        <v>787</v>
+        <v>766</v>
       </c>
       <c r="L17" s="39">
         <v>71</v>
@@ -8531,28 +9098,28 @@
     </row>
     <row r="18" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B18" s="1" t="s">
-        <v>654</v>
+        <v>633</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>655</v>
+        <v>634</v>
       </c>
       <c r="D18" s="48">
         <v>112</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>721</v>
+        <v>700</v>
       </c>
       <c r="G18" s="1" t="s">
-        <v>722</v>
+        <v>701</v>
       </c>
       <c r="H18" s="48">
         <v>229</v>
       </c>
       <c r="J18" s="1" t="s">
-        <v>788</v>
+        <v>767</v>
       </c>
       <c r="K18" s="1" t="s">
-        <v>789</v>
+        <v>768</v>
       </c>
       <c r="L18" s="48">
         <v>1215</v>
@@ -8560,28 +9127,28 @@
     </row>
     <row r="19" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B19" s="38" t="s">
-        <v>656</v>
+        <v>635</v>
       </c>
       <c r="C19" s="38" t="s">
-        <v>657</v>
+        <v>636</v>
       </c>
       <c r="D19" s="39">
         <v>154</v>
       </c>
       <c r="F19" s="38" t="s">
-        <v>723</v>
+        <v>702</v>
       </c>
       <c r="G19" s="38" t="s">
-        <v>724</v>
+        <v>703</v>
       </c>
       <c r="H19" s="39">
         <v>1058</v>
       </c>
       <c r="J19" s="38" t="s">
-        <v>790</v>
+        <v>769</v>
       </c>
       <c r="K19" s="38" t="s">
-        <v>791</v>
+        <v>770</v>
       </c>
       <c r="L19" s="39">
         <v>264</v>
@@ -8589,28 +9156,28 @@
     </row>
     <row r="20" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B20" s="1" t="s">
-        <v>658</v>
+        <v>637</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>659</v>
+        <v>638</v>
       </c>
       <c r="D20" s="48">
         <v>637</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>725</v>
+        <v>704</v>
       </c>
       <c r="G20" s="1" t="s">
-        <v>726</v>
+        <v>705</v>
       </c>
       <c r="H20" s="48">
         <v>158</v>
       </c>
       <c r="J20" s="1" t="s">
-        <v>792</v>
+        <v>771</v>
       </c>
       <c r="K20" s="1" t="s">
-        <v>793</v>
+        <v>772</v>
       </c>
       <c r="L20" s="48">
         <v>133</v>
@@ -8618,28 +9185,28 @@
     </row>
     <row r="21" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B21" s="38" t="s">
-        <v>660</v>
+        <v>639</v>
       </c>
       <c r="C21" s="38" t="s">
-        <v>661</v>
+        <v>640</v>
       </c>
       <c r="D21" s="39">
         <v>499</v>
       </c>
       <c r="F21" s="38" t="s">
-        <v>727</v>
+        <v>706</v>
       </c>
       <c r="G21" s="38" t="s">
-        <v>728</v>
+        <v>707</v>
       </c>
       <c r="H21" s="39">
         <v>29</v>
       </c>
       <c r="J21" s="38" t="s">
-        <v>794</v>
+        <v>773</v>
       </c>
       <c r="K21" s="38" t="s">
-        <v>795</v>
+        <v>774</v>
       </c>
       <c r="L21" s="39">
         <v>984</v>
@@ -8647,28 +9214,28 @@
     </row>
     <row r="22" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B22" s="1" t="s">
-        <v>662</v>
+        <v>641</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>663</v>
+        <v>642</v>
       </c>
       <c r="D22" s="48">
         <v>335</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>729</v>
+        <v>708</v>
       </c>
       <c r="G22" s="1" t="s">
-        <v>730</v>
+        <v>709</v>
       </c>
       <c r="H22" s="48">
         <v>101</v>
       </c>
       <c r="J22" s="1" t="s">
-        <v>796</v>
+        <v>775</v>
       </c>
       <c r="K22" s="1" t="s">
-        <v>797</v>
+        <v>776</v>
       </c>
       <c r="L22" s="48">
         <v>864</v>
@@ -8676,28 +9243,28 @@
     </row>
     <row r="23" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B23" s="38" t="s">
-        <v>664</v>
+        <v>643</v>
       </c>
       <c r="C23" s="38" t="s">
-        <v>665</v>
+        <v>644</v>
       </c>
       <c r="D23" s="39">
         <v>219</v>
       </c>
       <c r="F23" s="38" t="s">
-        <v>731</v>
+        <v>710</v>
       </c>
       <c r="G23" s="38" t="s">
-        <v>732</v>
+        <v>711</v>
       </c>
       <c r="H23" s="39">
         <v>40</v>
       </c>
       <c r="J23" s="38" t="s">
-        <v>798</v>
+        <v>777</v>
       </c>
       <c r="K23" s="38" t="s">
-        <v>799</v>
+        <v>778</v>
       </c>
       <c r="L23" s="39">
         <v>322</v>
@@ -8705,28 +9272,28 @@
     </row>
     <row r="24" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B24" s="1" t="s">
-        <v>666</v>
+        <v>645</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>667</v>
+        <v>646</v>
       </c>
       <c r="D24" s="48">
         <v>172</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>733</v>
+        <v>712</v>
       </c>
       <c r="G24" s="1" t="s">
-        <v>734</v>
+        <v>713</v>
       </c>
       <c r="H24" s="48">
         <v>852</v>
       </c>
       <c r="J24" s="1" t="s">
-        <v>800</v>
+        <v>779</v>
       </c>
       <c r="K24" s="1" t="s">
-        <v>801</v>
+        <v>780</v>
       </c>
       <c r="L24" s="48">
         <v>158</v>
@@ -8734,28 +9301,28 @@
     </row>
     <row r="25" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B25" s="38" t="s">
-        <v>668</v>
+        <v>647</v>
       </c>
       <c r="C25" s="38" t="s">
-        <v>669</v>
+        <v>648</v>
       </c>
       <c r="D25" s="39">
         <v>133</v>
       </c>
       <c r="F25" s="38" t="s">
-        <v>735</v>
+        <v>714</v>
       </c>
       <c r="G25" s="38" t="s">
-        <v>736</v>
+        <v>715</v>
       </c>
       <c r="H25" s="39">
         <v>449</v>
       </c>
       <c r="J25" s="38" t="s">
-        <v>802</v>
+        <v>781</v>
       </c>
       <c r="K25" s="38" t="s">
-        <v>803</v>
+        <v>782</v>
       </c>
       <c r="L25" s="39">
         <v>33</v>
@@ -8763,28 +9330,28 @@
     </row>
     <row r="26" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B26" s="1" t="s">
-        <v>670</v>
+        <v>649</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>671</v>
+        <v>650</v>
       </c>
       <c r="D26" s="48">
         <v>645</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>737</v>
+        <v>716</v>
       </c>
       <c r="G26" s="1" t="s">
-        <v>738</v>
+        <v>717</v>
       </c>
       <c r="H26" s="48">
         <v>383</v>
       </c>
       <c r="J26" s="1" t="s">
-        <v>804</v>
+        <v>783</v>
       </c>
       <c r="K26" s="1" t="s">
-        <v>805</v>
+        <v>784</v>
       </c>
       <c r="L26" s="48">
         <v>162</v>
@@ -8792,28 +9359,28 @@
     </row>
     <row r="27" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B27" s="38" t="s">
-        <v>672</v>
+        <v>651</v>
       </c>
       <c r="C27" s="38" t="s">
-        <v>673</v>
+        <v>652</v>
       </c>
       <c r="D27" s="39">
         <v>669</v>
       </c>
       <c r="F27" s="38" t="s">
-        <v>739</v>
+        <v>718</v>
       </c>
       <c r="G27" s="38" t="s">
-        <v>740</v>
+        <v>719</v>
       </c>
       <c r="H27" s="39">
         <v>50</v>
       </c>
       <c r="J27" s="38" t="s">
-        <v>806</v>
+        <v>785</v>
       </c>
       <c r="K27" s="38" t="s">
-        <v>807</v>
+        <v>786</v>
       </c>
       <c r="L27" s="39">
         <v>802</v>
@@ -8821,28 +9388,28 @@
     </row>
     <row r="28" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B28" s="1" t="s">
-        <v>674</v>
+        <v>653</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>675</v>
+        <v>654</v>
       </c>
       <c r="D28" s="48">
         <v>57</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>741</v>
+        <v>720</v>
       </c>
       <c r="G28" s="1" t="s">
-        <v>742</v>
+        <v>721</v>
       </c>
       <c r="H28" s="48">
         <v>444</v>
       </c>
       <c r="J28" s="1" t="s">
-        <v>808</v>
+        <v>787</v>
       </c>
       <c r="K28" s="1" t="s">
-        <v>809</v>
+        <v>788</v>
       </c>
       <c r="L28" s="48">
         <v>310</v>
@@ -8850,28 +9417,28 @@
     </row>
     <row r="29" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B29" s="38" t="s">
-        <v>676</v>
+        <v>655</v>
       </c>
       <c r="C29" s="38" t="s">
-        <v>677</v>
+        <v>656</v>
       </c>
       <c r="D29" s="39">
         <v>37</v>
       </c>
       <c r="F29" s="38" t="s">
-        <v>743</v>
+        <v>722</v>
       </c>
       <c r="G29" s="38" t="s">
-        <v>744</v>
+        <v>723</v>
       </c>
       <c r="H29" s="39">
         <v>397</v>
       </c>
       <c r="J29" s="38" t="s">
-        <v>810</v>
+        <v>789</v>
       </c>
       <c r="K29" s="38" t="s">
-        <v>811</v>
+        <v>790</v>
       </c>
       <c r="L29" s="39">
         <v>155</v>
@@ -8879,28 +9446,28 @@
     </row>
     <row r="30" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B30" s="1" t="s">
-        <v>678</v>
+        <v>657</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>679</v>
+        <v>658</v>
       </c>
       <c r="D30" s="48">
         <v>81</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>745</v>
+        <v>724</v>
       </c>
       <c r="G30" s="1" t="s">
-        <v>746</v>
+        <v>725</v>
       </c>
       <c r="H30" s="48">
         <v>111</v>
       </c>
       <c r="J30" s="1" t="s">
-        <v>812</v>
+        <v>791</v>
       </c>
       <c r="K30" s="1" t="s">
-        <v>813</v>
+        <v>792</v>
       </c>
       <c r="L30" s="48">
         <v>169</v>
@@ -8908,28 +9475,28 @@
     </row>
     <row r="31" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B31" s="38" t="s">
-        <v>680</v>
+        <v>659</v>
       </c>
       <c r="C31" s="38" t="s">
-        <v>681</v>
+        <v>660</v>
       </c>
       <c r="D31" s="39">
         <v>61</v>
       </c>
       <c r="F31" s="38" t="s">
-        <v>747</v>
+        <v>726</v>
       </c>
       <c r="G31" s="38" t="s">
-        <v>748</v>
+        <v>727</v>
       </c>
       <c r="H31" s="39">
         <v>81</v>
       </c>
       <c r="J31" s="38" t="s">
-        <v>814</v>
+        <v>793</v>
       </c>
       <c r="K31" s="38" t="s">
-        <v>815</v>
+        <v>794</v>
       </c>
       <c r="L31" s="39">
         <v>310</v>
@@ -8937,28 +9504,28 @@
     </row>
     <row r="32" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B32" s="1" t="s">
-        <v>682</v>
+        <v>661</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>683</v>
+        <v>662</v>
       </c>
       <c r="D32" s="48">
         <v>459</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>749</v>
+        <v>728</v>
       </c>
       <c r="G32" s="1" t="s">
-        <v>750</v>
+        <v>729</v>
       </c>
       <c r="H32" s="48">
         <v>370</v>
       </c>
       <c r="J32" s="1" t="s">
-        <v>816</v>
+        <v>795</v>
       </c>
       <c r="K32" s="1" t="s">
-        <v>817</v>
+        <v>796</v>
       </c>
       <c r="L32" s="48">
         <v>168</v>
@@ -8966,28 +9533,28 @@
     </row>
     <row r="33" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B33" s="38" t="s">
-        <v>684</v>
+        <v>663</v>
       </c>
       <c r="C33" s="38" t="s">
-        <v>685</v>
+        <v>664</v>
       </c>
       <c r="D33" s="39">
         <v>397</v>
       </c>
       <c r="F33" s="38" t="s">
-        <v>751</v>
+        <v>730</v>
       </c>
       <c r="G33" s="38" t="s">
-        <v>752</v>
+        <v>731</v>
       </c>
       <c r="H33" s="39">
         <v>229</v>
       </c>
       <c r="J33" s="38" t="s">
-        <v>818</v>
+        <v>797</v>
       </c>
       <c r="K33" s="38" t="s">
-        <v>819</v>
+        <v>798</v>
       </c>
       <c r="L33" s="39">
         <v>87</v>
@@ -8995,28 +9562,28 @@
     </row>
     <row r="34" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B34" s="1" t="s">
-        <v>686</v>
+        <v>665</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>687</v>
+        <v>666</v>
       </c>
       <c r="D34" s="48">
         <v>525</v>
       </c>
       <c r="F34" s="1" t="s">
-        <v>753</v>
+        <v>732</v>
       </c>
       <c r="G34" s="1" t="s">
-        <v>754</v>
+        <v>733</v>
       </c>
       <c r="H34" s="48">
         <v>199</v>
       </c>
       <c r="J34" s="1" t="s">
-        <v>820</v>
+        <v>799</v>
       </c>
       <c r="K34" s="1" t="s">
-        <v>821</v>
+        <v>800</v>
       </c>
       <c r="L34" s="48">
         <v>40</v>
@@ -9024,28 +9591,28 @@
     </row>
     <row r="35" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B35" s="38" t="s">
-        <v>688</v>
+        <v>667</v>
       </c>
       <c r="C35" s="38" t="s">
-        <v>689</v>
+        <v>668</v>
       </c>
       <c r="D35" s="39">
         <v>203</v>
       </c>
       <c r="F35" s="38" t="s">
-        <v>755</v>
+        <v>734</v>
       </c>
       <c r="G35" s="38" t="s">
-        <v>756</v>
+        <v>735</v>
       </c>
       <c r="H35" s="39">
         <v>371</v>
       </c>
       <c r="J35" s="38" t="s">
-        <v>822</v>
+        <v>801</v>
       </c>
       <c r="K35" s="38" t="s">
-        <v>823</v>
+        <v>802</v>
       </c>
       <c r="L35" s="39">
         <v>248</v>
@@ -9053,28 +9620,28 @@
     </row>
     <row r="36" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B36" s="1" t="s">
-        <v>690</v>
+        <v>669</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>691</v>
+        <v>670</v>
       </c>
       <c r="D36" s="48">
         <v>392</v>
       </c>
       <c r="F36" s="1" t="s">
-        <v>757</v>
+        <v>736</v>
       </c>
       <c r="G36" s="1" t="s">
-        <v>758</v>
+        <v>737</v>
       </c>
       <c r="H36" s="48">
         <v>274</v>
       </c>
       <c r="J36" s="1" t="s">
-        <v>824</v>
+        <v>803</v>
       </c>
       <c r="K36" s="1" t="s">
-        <v>825</v>
+        <v>804</v>
       </c>
       <c r="L36" s="48">
         <v>117</v>
@@ -9082,28 +9649,28 @@
     </row>
     <row r="37" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B37" s="38" t="s">
-        <v>692</v>
+        <v>671</v>
       </c>
       <c r="C37" s="38" t="s">
-        <v>693</v>
+        <v>672</v>
       </c>
       <c r="D37" s="39">
         <v>1958</v>
       </c>
       <c r="F37" s="38" t="s">
-        <v>759</v>
+        <v>738</v>
       </c>
       <c r="G37" s="38" t="s">
-        <v>760</v>
+        <v>739</v>
       </c>
       <c r="H37" s="39">
         <v>7030</v>
       </c>
       <c r="J37" s="38" t="s">
-        <v>826</v>
+        <v>805</v>
       </c>
       <c r="K37" s="38" t="s">
-        <v>827</v>
+        <v>806</v>
       </c>
       <c r="L37" s="39">
         <v>279</v>
@@ -9111,20 +9678,20 @@
     </row>
     <row r="38" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B38" s="2" t="s">
-        <v>694</v>
+        <v>673</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>695</v>
+        <v>674</v>
       </c>
       <c r="D38" s="45">
         <v>834</v>
       </c>
       <c r="E38" s="2"/>
       <c r="F38" s="2" t="s">
-        <v>761</v>
+        <v>740</v>
       </c>
       <c r="G38" s="2" t="s">
-        <v>762</v>
+        <v>741</v>
       </c>
       <c r="H38" s="45">
         <v>6897</v>
@@ -9171,4 +9738,1517 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{116F4F12-F5E3-A94E-ACE3-238CE86EAC3E}">
+  <dimension ref="B2:J29"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="2" max="2" width="18.83203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14.33203125" hidden="1" customWidth="1"/>
+    <col min="4" max="7" width="15.6640625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="1.83203125" customWidth="1"/>
+    <col min="9" max="9" width="16.6640625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="7.5" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:10" ht="32" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B2" s="92" t="s">
+        <v>1088</v>
+      </c>
+      <c r="C2" s="92"/>
+      <c r="D2" s="92"/>
+      <c r="E2" s="92"/>
+      <c r="F2" s="92"/>
+      <c r="G2" s="92"/>
+      <c r="H2" s="92"/>
+      <c r="I2" s="92"/>
+      <c r="J2" s="92"/>
+    </row>
+    <row r="3" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="B3" s="1"/>
+      <c r="C3" s="1"/>
+      <c r="D3" s="90" t="s">
+        <v>499</v>
+      </c>
+      <c r="E3" s="91"/>
+      <c r="F3" s="91"/>
+      <c r="G3" s="91"/>
+      <c r="H3" s="31"/>
+      <c r="I3" s="91" t="s">
+        <v>502</v>
+      </c>
+      <c r="J3" s="91"/>
+    </row>
+    <row r="4" spans="2:10" ht="34" x14ac:dyDescent="0.2">
+      <c r="B4" s="32"/>
+      <c r="C4" s="2" t="s">
+        <v>442</v>
+      </c>
+      <c r="D4" s="80" t="s">
+        <v>418</v>
+      </c>
+      <c r="E4" s="81" t="s">
+        <v>420</v>
+      </c>
+      <c r="F4" s="81" t="s">
+        <v>422</v>
+      </c>
+      <c r="G4" s="81" t="s">
+        <v>424</v>
+      </c>
+      <c r="H4" s="32"/>
+      <c r="I4" s="97" t="s">
+        <v>986</v>
+      </c>
+      <c r="J4" s="81" t="s">
+        <v>501</v>
+      </c>
+    </row>
+    <row r="5" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="B5" s="34" t="s">
+        <v>363</v>
+      </c>
+      <c r="C5" s="35"/>
+      <c r="D5" s="36"/>
+      <c r="E5" s="36"/>
+      <c r="F5" s="36"/>
+      <c r="G5" s="36"/>
+      <c r="H5" s="35"/>
+      <c r="I5" s="36"/>
+      <c r="J5" s="36"/>
+    </row>
+    <row r="6" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="B6" s="37" t="s">
+        <v>494</v>
+      </c>
+      <c r="C6" s="38" t="s">
+        <v>443</v>
+      </c>
+      <c r="D6" s="52" t="s">
+        <v>912</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>913</v>
+      </c>
+      <c r="F6" s="3" t="s">
+        <v>914</v>
+      </c>
+      <c r="G6" s="3" t="s">
+        <v>915</v>
+      </c>
+      <c r="H6" s="38"/>
+      <c r="I6" s="39">
+        <v>5369</v>
+      </c>
+      <c r="J6" s="39">
+        <v>52837</v>
+      </c>
+    </row>
+    <row r="7" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="B7" s="37" t="s">
+        <v>495</v>
+      </c>
+      <c r="C7" s="38" t="s">
+        <v>443</v>
+      </c>
+      <c r="D7" s="52" t="s">
+        <v>912</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>913</v>
+      </c>
+      <c r="F7" s="3" t="s">
+        <v>914</v>
+      </c>
+      <c r="G7" s="3" t="s">
+        <v>916</v>
+      </c>
+      <c r="H7" s="38"/>
+      <c r="I7" s="39">
+        <v>5369</v>
+      </c>
+      <c r="J7" s="39">
+        <v>52837</v>
+      </c>
+    </row>
+    <row r="8" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="B8" s="37" t="s">
+        <v>496</v>
+      </c>
+      <c r="C8" s="38" t="s">
+        <v>443</v>
+      </c>
+      <c r="D8" s="52" t="s">
+        <v>917</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>918</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>919</v>
+      </c>
+      <c r="G8" s="3" t="s">
+        <v>920</v>
+      </c>
+      <c r="H8" s="38"/>
+      <c r="I8" s="39">
+        <v>5369</v>
+      </c>
+      <c r="J8" s="39">
+        <v>52837</v>
+      </c>
+    </row>
+    <row r="9" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="B9" s="37" t="s">
+        <v>497</v>
+      </c>
+      <c r="C9" s="38" t="s">
+        <v>443</v>
+      </c>
+      <c r="D9" s="52" t="s">
+        <v>921</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>922</v>
+      </c>
+      <c r="F9" s="3" t="s">
+        <v>923</v>
+      </c>
+      <c r="G9" s="3" t="s">
+        <v>924</v>
+      </c>
+      <c r="H9" s="38"/>
+      <c r="I9" s="39">
+        <v>4640</v>
+      </c>
+      <c r="J9" s="39">
+        <v>43979</v>
+      </c>
+    </row>
+    <row r="10" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="B10" s="40" t="s">
+        <v>498</v>
+      </c>
+      <c r="C10" s="41" t="s">
+        <v>443</v>
+      </c>
+      <c r="D10" s="53" t="s">
+        <v>925</v>
+      </c>
+      <c r="E10" s="42" t="s">
+        <v>926</v>
+      </c>
+      <c r="F10" s="42" t="s">
+        <v>927</v>
+      </c>
+      <c r="G10" s="42" t="s">
+        <v>928</v>
+      </c>
+      <c r="H10" s="41"/>
+      <c r="I10" s="43">
+        <v>4497</v>
+      </c>
+      <c r="J10" s="43">
+        <v>41481</v>
+      </c>
+    </row>
+    <row r="11" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="B11" s="32" t="s">
+        <v>455</v>
+      </c>
+      <c r="C11" s="2"/>
+      <c r="D11" s="44"/>
+      <c r="E11" s="44"/>
+      <c r="F11" s="44"/>
+      <c r="G11" s="44"/>
+      <c r="H11" s="2"/>
+      <c r="I11" s="45"/>
+      <c r="J11" s="45"/>
+    </row>
+    <row r="12" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="B12" s="46" t="s">
+        <v>494</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>455</v>
+      </c>
+      <c r="D12" s="54" t="s">
+        <v>929</v>
+      </c>
+      <c r="E12" s="47" t="s">
+        <v>930</v>
+      </c>
+      <c r="F12" s="47" t="s">
+        <v>931</v>
+      </c>
+      <c r="G12" s="47" t="s">
+        <v>932</v>
+      </c>
+      <c r="H12" s="1"/>
+      <c r="I12" s="48">
+        <v>2653</v>
+      </c>
+      <c r="J12" s="48">
+        <v>52837</v>
+      </c>
+    </row>
+    <row r="13" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="B13" s="46" t="s">
+        <v>495</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>455</v>
+      </c>
+      <c r="D13" s="54" t="s">
+        <v>929</v>
+      </c>
+      <c r="E13" s="47" t="s">
+        <v>930</v>
+      </c>
+      <c r="F13" s="47" t="s">
+        <v>933</v>
+      </c>
+      <c r="G13" s="47" t="s">
+        <v>934</v>
+      </c>
+      <c r="H13" s="1"/>
+      <c r="I13" s="48">
+        <v>2653</v>
+      </c>
+      <c r="J13" s="48">
+        <v>52837</v>
+      </c>
+    </row>
+    <row r="14" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="B14" s="46" t="s">
+        <v>496</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>455</v>
+      </c>
+      <c r="D14" s="54" t="s">
+        <v>935</v>
+      </c>
+      <c r="E14" s="47" t="s">
+        <v>936</v>
+      </c>
+      <c r="F14" s="47" t="s">
+        <v>937</v>
+      </c>
+      <c r="G14" s="47" t="s">
+        <v>938</v>
+      </c>
+      <c r="H14" s="1"/>
+      <c r="I14" s="48">
+        <v>2653</v>
+      </c>
+      <c r="J14" s="48">
+        <v>52837</v>
+      </c>
+    </row>
+    <row r="15" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="B15" s="46" t="s">
+        <v>497</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>455</v>
+      </c>
+      <c r="D15" s="54" t="s">
+        <v>939</v>
+      </c>
+      <c r="E15" s="47" t="s">
+        <v>940</v>
+      </c>
+      <c r="F15" s="47" t="s">
+        <v>941</v>
+      </c>
+      <c r="G15" s="47" t="s">
+        <v>942</v>
+      </c>
+      <c r="H15" s="1"/>
+      <c r="I15" s="48">
+        <v>2340</v>
+      </c>
+      <c r="J15" s="48">
+        <v>43979</v>
+      </c>
+    </row>
+    <row r="16" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="B16" s="49" t="s">
+        <v>498</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>455</v>
+      </c>
+      <c r="D16" s="55" t="s">
+        <v>943</v>
+      </c>
+      <c r="E16" s="44" t="s">
+        <v>944</v>
+      </c>
+      <c r="F16" s="44" t="s">
+        <v>945</v>
+      </c>
+      <c r="G16" s="44" t="s">
+        <v>946</v>
+      </c>
+      <c r="H16" s="2"/>
+      <c r="I16" s="45">
+        <v>2284</v>
+      </c>
+      <c r="J16" s="45">
+        <v>41481</v>
+      </c>
+    </row>
+    <row r="17" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="B17" s="50" t="s">
+        <v>463</v>
+      </c>
+      <c r="C17" s="41"/>
+      <c r="D17" s="42"/>
+      <c r="E17" s="42"/>
+      <c r="F17" s="42"/>
+      <c r="G17" s="42"/>
+      <c r="H17" s="41"/>
+      <c r="I17" s="43"/>
+      <c r="J17" s="43"/>
+    </row>
+    <row r="18" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="B18" s="37" t="s">
+        <v>494</v>
+      </c>
+      <c r="C18" s="38" t="s">
+        <v>464</v>
+      </c>
+      <c r="D18" s="52" t="s">
+        <v>947</v>
+      </c>
+      <c r="E18" s="3" t="s">
+        <v>948</v>
+      </c>
+      <c r="F18" s="3" t="s">
+        <v>949</v>
+      </c>
+      <c r="G18" s="3" t="s">
+        <v>950</v>
+      </c>
+      <c r="H18" s="38"/>
+      <c r="I18" s="39">
+        <v>534</v>
+      </c>
+      <c r="J18" s="39">
+        <v>52837</v>
+      </c>
+    </row>
+    <row r="19" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="B19" s="37" t="s">
+        <v>495</v>
+      </c>
+      <c r="C19" s="38" t="s">
+        <v>464</v>
+      </c>
+      <c r="D19" s="52" t="s">
+        <v>951</v>
+      </c>
+      <c r="E19" s="3" t="s">
+        <v>952</v>
+      </c>
+      <c r="F19" s="3" t="s">
+        <v>953</v>
+      </c>
+      <c r="G19" s="3" t="s">
+        <v>954</v>
+      </c>
+      <c r="H19" s="38"/>
+      <c r="I19" s="39">
+        <v>534</v>
+      </c>
+      <c r="J19" s="39">
+        <v>52837</v>
+      </c>
+    </row>
+    <row r="20" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="B20" s="37" t="s">
+        <v>496</v>
+      </c>
+      <c r="C20" s="38" t="s">
+        <v>464</v>
+      </c>
+      <c r="D20" s="52" t="s">
+        <v>955</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>956</v>
+      </c>
+      <c r="F20" s="3" t="s">
+        <v>957</v>
+      </c>
+      <c r="G20" s="3" t="s">
+        <v>958</v>
+      </c>
+      <c r="H20" s="38"/>
+      <c r="I20" s="39">
+        <v>534</v>
+      </c>
+      <c r="J20" s="39">
+        <v>52837</v>
+      </c>
+    </row>
+    <row r="21" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="B21" s="37" t="s">
+        <v>497</v>
+      </c>
+      <c r="C21" s="38" t="s">
+        <v>464</v>
+      </c>
+      <c r="D21" s="52" t="s">
+        <v>959</v>
+      </c>
+      <c r="E21" s="3" t="s">
+        <v>960</v>
+      </c>
+      <c r="F21" s="3" t="s">
+        <v>961</v>
+      </c>
+      <c r="G21" s="3" t="s">
+        <v>962</v>
+      </c>
+      <c r="H21" s="38"/>
+      <c r="I21" s="39">
+        <v>475</v>
+      </c>
+      <c r="J21" s="39">
+        <v>43979</v>
+      </c>
+    </row>
+    <row r="22" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="B22" s="40" t="s">
+        <v>498</v>
+      </c>
+      <c r="C22" s="41" t="s">
+        <v>464</v>
+      </c>
+      <c r="D22" s="53" t="s">
+        <v>963</v>
+      </c>
+      <c r="E22" s="42" t="s">
+        <v>964</v>
+      </c>
+      <c r="F22" s="42" t="s">
+        <v>965</v>
+      </c>
+      <c r="G22" s="42" t="s">
+        <v>966</v>
+      </c>
+      <c r="H22" s="41"/>
+      <c r="I22" s="43">
+        <v>469</v>
+      </c>
+      <c r="J22" s="43">
+        <v>41481</v>
+      </c>
+    </row>
+    <row r="23" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="B23" s="32" t="s">
+        <v>477</v>
+      </c>
+      <c r="C23" s="2"/>
+      <c r="D23" s="44"/>
+      <c r="E23" s="44"/>
+      <c r="F23" s="44"/>
+      <c r="G23" s="44"/>
+      <c r="H23" s="2"/>
+      <c r="I23" s="45"/>
+      <c r="J23" s="45"/>
+    </row>
+    <row r="24" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="B24" s="46" t="s">
+        <v>494</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>478</v>
+      </c>
+      <c r="D24" s="54" t="s">
+        <v>967</v>
+      </c>
+      <c r="E24" s="47" t="s">
+        <v>968</v>
+      </c>
+      <c r="F24" s="47" t="s">
+        <v>969</v>
+      </c>
+      <c r="G24" s="47" t="s">
+        <v>588</v>
+      </c>
+      <c r="H24" s="1"/>
+      <c r="I24" s="48">
+        <v>34</v>
+      </c>
+      <c r="J24" s="48">
+        <v>52837</v>
+      </c>
+    </row>
+    <row r="25" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="B25" s="46" t="s">
+        <v>495</v>
+      </c>
+      <c r="C25" s="1" t="s">
+        <v>478</v>
+      </c>
+      <c r="D25" s="54" t="s">
+        <v>970</v>
+      </c>
+      <c r="E25" s="47" t="s">
+        <v>971</v>
+      </c>
+      <c r="F25" s="47" t="s">
+        <v>972</v>
+      </c>
+      <c r="G25" s="47" t="s">
+        <v>973</v>
+      </c>
+      <c r="H25" s="1"/>
+      <c r="I25" s="48">
+        <v>34</v>
+      </c>
+      <c r="J25" s="48">
+        <v>52837</v>
+      </c>
+    </row>
+    <row r="26" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="B26" s="46" t="s">
+        <v>496</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>478</v>
+      </c>
+      <c r="D26" s="54" t="s">
+        <v>974</v>
+      </c>
+      <c r="E26" s="47" t="s">
+        <v>975</v>
+      </c>
+      <c r="F26" s="47" t="s">
+        <v>976</v>
+      </c>
+      <c r="G26" s="47" t="s">
+        <v>977</v>
+      </c>
+      <c r="H26" s="1"/>
+      <c r="I26" s="48">
+        <v>34</v>
+      </c>
+      <c r="J26" s="48">
+        <v>52837</v>
+      </c>
+    </row>
+    <row r="27" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="B27" s="46" t="s">
+        <v>497</v>
+      </c>
+      <c r="C27" s="1" t="s">
+        <v>478</v>
+      </c>
+      <c r="D27" s="54" t="s">
+        <v>978</v>
+      </c>
+      <c r="E27" s="47" t="s">
+        <v>979</v>
+      </c>
+      <c r="F27" s="47" t="s">
+        <v>980</v>
+      </c>
+      <c r="G27" s="47" t="s">
+        <v>981</v>
+      </c>
+      <c r="H27" s="1"/>
+      <c r="I27" s="48">
+        <v>32</v>
+      </c>
+      <c r="J27" s="48">
+        <v>43979</v>
+      </c>
+    </row>
+    <row r="28" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="B28" s="49" t="s">
+        <v>498</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>478</v>
+      </c>
+      <c r="D28" s="55" t="s">
+        <v>982</v>
+      </c>
+      <c r="E28" s="44" t="s">
+        <v>983</v>
+      </c>
+      <c r="F28" s="44" t="s">
+        <v>984</v>
+      </c>
+      <c r="G28" s="44" t="s">
+        <v>985</v>
+      </c>
+      <c r="H28" s="2"/>
+      <c r="I28" s="45">
+        <v>32</v>
+      </c>
+      <c r="J28" s="45">
+        <v>41481</v>
+      </c>
+    </row>
+    <row r="29" spans="2:10" ht="65" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B29" s="93" t="s">
+        <v>503</v>
+      </c>
+      <c r="C29" s="94"/>
+      <c r="D29" s="94"/>
+      <c r="E29" s="94"/>
+      <c r="F29" s="94"/>
+      <c r="G29" s="94"/>
+      <c r="H29" s="94"/>
+      <c r="I29" s="94"/>
+      <c r="J29" s="94"/>
+    </row>
+  </sheetData>
+  <mergeCells count="4">
+    <mergeCell ref="B2:J2"/>
+    <mergeCell ref="D3:G3"/>
+    <mergeCell ref="I3:J3"/>
+    <mergeCell ref="B29:J29"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DA6FCB3D-348D-E040-8F00-94D0B555D207}">
+  <dimension ref="B3:J36"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="2" max="2" width="24.83203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="23.5" hidden="1" customWidth="1"/>
+    <col min="4" max="6" width="15.6640625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="17" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="1.83203125" customWidth="1"/>
+    <col min="9" max="9" width="12.6640625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="7.5" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="3" spans="2:10" ht="32" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B3" s="92" t="s">
+        <v>1087</v>
+      </c>
+      <c r="C3" s="92"/>
+      <c r="D3" s="92"/>
+      <c r="E3" s="92"/>
+      <c r="F3" s="92"/>
+      <c r="G3" s="92"/>
+      <c r="H3" s="92"/>
+      <c r="I3" s="92"/>
+      <c r="J3" s="92"/>
+    </row>
+    <row r="4" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="B4" s="1"/>
+      <c r="C4" s="1"/>
+      <c r="D4" s="90" t="s">
+        <v>499</v>
+      </c>
+      <c r="E4" s="91"/>
+      <c r="F4" s="91"/>
+      <c r="G4" s="91"/>
+      <c r="H4" s="31"/>
+      <c r="I4" s="91" t="s">
+        <v>502</v>
+      </c>
+      <c r="J4" s="91"/>
+    </row>
+    <row r="5" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="B5" s="32"/>
+      <c r="C5" s="2" t="s">
+        <v>442</v>
+      </c>
+      <c r="D5" s="80" t="s">
+        <v>418</v>
+      </c>
+      <c r="E5" s="81" t="s">
+        <v>420</v>
+      </c>
+      <c r="F5" s="81" t="s">
+        <v>422</v>
+      </c>
+      <c r="G5" s="81" t="s">
+        <v>424</v>
+      </c>
+      <c r="H5" s="32"/>
+      <c r="I5" s="81" t="s">
+        <v>987</v>
+      </c>
+      <c r="J5" s="81" t="s">
+        <v>501</v>
+      </c>
+    </row>
+    <row r="6" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="B6" s="50" t="s">
+        <v>504</v>
+      </c>
+      <c r="C6" s="41"/>
+      <c r="D6" s="41"/>
+      <c r="E6" s="41"/>
+      <c r="F6" s="41"/>
+      <c r="G6" s="41"/>
+      <c r="H6" s="41"/>
+      <c r="I6" s="42"/>
+      <c r="J6" s="42"/>
+    </row>
+    <row r="7" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="B7" s="37" t="s">
+        <v>494</v>
+      </c>
+      <c r="C7" s="38" t="s">
+        <v>504</v>
+      </c>
+      <c r="D7" s="52" t="s">
+        <v>988</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>989</v>
+      </c>
+      <c r="F7" s="3" t="s">
+        <v>990</v>
+      </c>
+      <c r="G7" s="3" t="s">
+        <v>991</v>
+      </c>
+      <c r="H7" s="38"/>
+      <c r="I7" s="39">
+        <v>729</v>
+      </c>
+      <c r="J7" s="39">
+        <v>52837</v>
+      </c>
+    </row>
+    <row r="8" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="B8" s="37" t="s">
+        <v>495</v>
+      </c>
+      <c r="C8" s="38" t="s">
+        <v>504</v>
+      </c>
+      <c r="D8" s="52" t="s">
+        <v>992</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>993</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>994</v>
+      </c>
+      <c r="G8" s="3" t="s">
+        <v>995</v>
+      </c>
+      <c r="H8" s="38"/>
+      <c r="I8" s="39">
+        <v>729</v>
+      </c>
+      <c r="J8" s="39">
+        <v>52837</v>
+      </c>
+    </row>
+    <row r="9" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="B9" s="37" t="s">
+        <v>496</v>
+      </c>
+      <c r="C9" s="38" t="s">
+        <v>504</v>
+      </c>
+      <c r="D9" s="52" t="s">
+        <v>996</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>997</v>
+      </c>
+      <c r="F9" s="3" t="s">
+        <v>998</v>
+      </c>
+      <c r="G9" s="3" t="s">
+        <v>999</v>
+      </c>
+      <c r="H9" s="38"/>
+      <c r="I9" s="39">
+        <v>729</v>
+      </c>
+      <c r="J9" s="39">
+        <v>52837</v>
+      </c>
+    </row>
+    <row r="10" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="B10" s="37" t="s">
+        <v>497</v>
+      </c>
+      <c r="C10" s="38" t="s">
+        <v>504</v>
+      </c>
+      <c r="D10" s="52" t="s">
+        <v>1000</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>1001</v>
+      </c>
+      <c r="F10" s="3" t="s">
+        <v>1002</v>
+      </c>
+      <c r="G10" s="3" t="s">
+        <v>1003</v>
+      </c>
+      <c r="H10" s="38"/>
+      <c r="I10" s="39">
+        <v>644</v>
+      </c>
+      <c r="J10" s="39">
+        <v>43979</v>
+      </c>
+    </row>
+    <row r="11" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="B11" s="40" t="s">
+        <v>498</v>
+      </c>
+      <c r="C11" s="41" t="s">
+        <v>504</v>
+      </c>
+      <c r="D11" s="53" t="s">
+        <v>1004</v>
+      </c>
+      <c r="E11" s="42" t="s">
+        <v>1005</v>
+      </c>
+      <c r="F11" s="42" t="s">
+        <v>1006</v>
+      </c>
+      <c r="G11" s="42" t="s">
+        <v>1007</v>
+      </c>
+      <c r="H11" s="41"/>
+      <c r="I11" s="43">
+        <v>631</v>
+      </c>
+      <c r="J11" s="43">
+        <v>41481</v>
+      </c>
+    </row>
+    <row r="12" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="B12" s="32" t="s">
+        <v>516</v>
+      </c>
+      <c r="C12" s="2"/>
+      <c r="D12" s="44"/>
+      <c r="E12" s="44"/>
+      <c r="F12" s="44"/>
+      <c r="G12" s="44"/>
+      <c r="H12" s="2"/>
+      <c r="I12" s="45"/>
+      <c r="J12" s="45"/>
+    </row>
+    <row r="13" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="B13" s="46" t="s">
+        <v>494</v>
+      </c>
+      <c r="C13" s="56" t="s">
+        <v>516</v>
+      </c>
+      <c r="D13" s="59" t="s">
+        <v>1008</v>
+      </c>
+      <c r="E13" s="60" t="s">
+        <v>1009</v>
+      </c>
+      <c r="F13" s="60" t="s">
+        <v>1010</v>
+      </c>
+      <c r="G13" s="60" t="s">
+        <v>1011</v>
+      </c>
+      <c r="H13" s="1"/>
+      <c r="I13" s="48">
+        <v>964</v>
+      </c>
+      <c r="J13" s="48">
+        <v>52837</v>
+      </c>
+    </row>
+    <row r="14" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="B14" s="46" t="s">
+        <v>495</v>
+      </c>
+      <c r="C14" s="56" t="s">
+        <v>516</v>
+      </c>
+      <c r="D14" s="59" t="s">
+        <v>1012</v>
+      </c>
+      <c r="E14" s="60" t="s">
+        <v>1009</v>
+      </c>
+      <c r="F14" s="60" t="s">
+        <v>1013</v>
+      </c>
+      <c r="G14" s="60" t="s">
+        <v>1014</v>
+      </c>
+      <c r="H14" s="1"/>
+      <c r="I14" s="48">
+        <v>964</v>
+      </c>
+      <c r="J14" s="48">
+        <v>52837</v>
+      </c>
+    </row>
+    <row r="15" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="B15" s="46" t="s">
+        <v>496</v>
+      </c>
+      <c r="C15" s="56" t="s">
+        <v>516</v>
+      </c>
+      <c r="D15" s="59" t="s">
+        <v>1015</v>
+      </c>
+      <c r="E15" s="60" t="s">
+        <v>1016</v>
+      </c>
+      <c r="F15" s="60" t="s">
+        <v>1017</v>
+      </c>
+      <c r="G15" s="60" t="s">
+        <v>1018</v>
+      </c>
+      <c r="H15" s="1"/>
+      <c r="I15" s="48">
+        <v>964</v>
+      </c>
+      <c r="J15" s="48">
+        <v>52837</v>
+      </c>
+    </row>
+    <row r="16" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="B16" s="46" t="s">
+        <v>497</v>
+      </c>
+      <c r="C16" s="56" t="s">
+        <v>516</v>
+      </c>
+      <c r="D16" s="59" t="s">
+        <v>1019</v>
+      </c>
+      <c r="E16" s="60" t="s">
+        <v>1020</v>
+      </c>
+      <c r="F16" s="60" t="s">
+        <v>1021</v>
+      </c>
+      <c r="G16" s="60" t="s">
+        <v>1022</v>
+      </c>
+      <c r="H16" s="1"/>
+      <c r="I16" s="48">
+        <v>827</v>
+      </c>
+      <c r="J16" s="48">
+        <v>43979</v>
+      </c>
+    </row>
+    <row r="17" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="B17" s="49" t="s">
+        <v>498</v>
+      </c>
+      <c r="C17" s="57" t="s">
+        <v>516</v>
+      </c>
+      <c r="D17" s="61" t="s">
+        <v>1023</v>
+      </c>
+      <c r="E17" s="62" t="s">
+        <v>1024</v>
+      </c>
+      <c r="F17" s="62" t="s">
+        <v>1025</v>
+      </c>
+      <c r="G17" s="62" t="s">
+        <v>1026</v>
+      </c>
+      <c r="H17" s="2"/>
+      <c r="I17" s="45">
+        <v>790</v>
+      </c>
+      <c r="J17" s="45">
+        <v>41481</v>
+      </c>
+    </row>
+    <row r="18" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="B18" s="63" t="s">
+        <v>529</v>
+      </c>
+      <c r="C18" s="41"/>
+      <c r="D18" s="42"/>
+      <c r="E18" s="42"/>
+      <c r="F18" s="42"/>
+      <c r="G18" s="42"/>
+      <c r="H18" s="41"/>
+      <c r="I18" s="43"/>
+      <c r="J18" s="43"/>
+    </row>
+    <row r="19" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="B19" s="37" t="s">
+        <v>494</v>
+      </c>
+      <c r="C19" s="64" t="s">
+        <v>529</v>
+      </c>
+      <c r="D19" s="65" t="s">
+        <v>1027</v>
+      </c>
+      <c r="E19" s="66" t="s">
+        <v>1028</v>
+      </c>
+      <c r="F19" s="66" t="s">
+        <v>1029</v>
+      </c>
+      <c r="G19" s="66" t="s">
+        <v>1030</v>
+      </c>
+      <c r="H19" s="38"/>
+      <c r="I19" s="39">
+        <v>437</v>
+      </c>
+      <c r="J19" s="39">
+        <v>52837</v>
+      </c>
+    </row>
+    <row r="20" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="B20" s="37" t="s">
+        <v>495</v>
+      </c>
+      <c r="C20" s="64" t="s">
+        <v>529</v>
+      </c>
+      <c r="D20" s="65" t="s">
+        <v>1031</v>
+      </c>
+      <c r="E20" s="66" t="s">
+        <v>1032</v>
+      </c>
+      <c r="F20" s="66" t="s">
+        <v>1033</v>
+      </c>
+      <c r="G20" s="66" t="s">
+        <v>1034</v>
+      </c>
+      <c r="H20" s="38"/>
+      <c r="I20" s="39">
+        <v>437</v>
+      </c>
+      <c r="J20" s="39">
+        <v>52837</v>
+      </c>
+    </row>
+    <row r="21" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="B21" s="37" t="s">
+        <v>496</v>
+      </c>
+      <c r="C21" s="64" t="s">
+        <v>529</v>
+      </c>
+      <c r="D21" s="65" t="s">
+        <v>1035</v>
+      </c>
+      <c r="E21" s="66" t="s">
+        <v>1036</v>
+      </c>
+      <c r="F21" s="66" t="s">
+        <v>1037</v>
+      </c>
+      <c r="G21" s="66" t="s">
+        <v>1038</v>
+      </c>
+      <c r="H21" s="38"/>
+      <c r="I21" s="39">
+        <v>437</v>
+      </c>
+      <c r="J21" s="39">
+        <v>52837</v>
+      </c>
+    </row>
+    <row r="22" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="B22" s="37" t="s">
+        <v>497</v>
+      </c>
+      <c r="C22" s="64" t="s">
+        <v>529</v>
+      </c>
+      <c r="D22" s="65" t="s">
+        <v>1039</v>
+      </c>
+      <c r="E22" s="66" t="s">
+        <v>1040</v>
+      </c>
+      <c r="F22" s="66" t="s">
+        <v>1041</v>
+      </c>
+      <c r="G22" s="66" t="s">
+        <v>1042</v>
+      </c>
+      <c r="H22" s="38"/>
+      <c r="I22" s="39">
+        <v>381</v>
+      </c>
+      <c r="J22" s="39">
+        <v>43979</v>
+      </c>
+    </row>
+    <row r="23" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="B23" s="40" t="s">
+        <v>498</v>
+      </c>
+      <c r="C23" s="67" t="s">
+        <v>529</v>
+      </c>
+      <c r="D23" s="68" t="s">
+        <v>1043</v>
+      </c>
+      <c r="E23" s="69" t="s">
+        <v>1044</v>
+      </c>
+      <c r="F23" s="69" t="s">
+        <v>1045</v>
+      </c>
+      <c r="G23" s="69" t="s">
+        <v>1046</v>
+      </c>
+      <c r="H23" s="41"/>
+      <c r="I23" s="43">
+        <v>359</v>
+      </c>
+      <c r="J23" s="43">
+        <v>41481</v>
+      </c>
+    </row>
+    <row r="24" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="B24" s="58" t="s">
+        <v>547</v>
+      </c>
+      <c r="C24" s="2"/>
+      <c r="D24" s="44"/>
+      <c r="E24" s="44"/>
+      <c r="F24" s="44"/>
+      <c r="G24" s="44"/>
+      <c r="H24" s="2"/>
+      <c r="I24" s="45"/>
+      <c r="J24" s="45"/>
+    </row>
+    <row r="25" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="B25" s="46" t="s">
+        <v>494</v>
+      </c>
+      <c r="C25" s="56" t="s">
+        <v>547</v>
+      </c>
+      <c r="D25" s="59" t="s">
+        <v>1047</v>
+      </c>
+      <c r="E25" s="60" t="s">
+        <v>1048</v>
+      </c>
+      <c r="F25" s="60" t="s">
+        <v>1049</v>
+      </c>
+      <c r="G25" s="60" t="s">
+        <v>1050</v>
+      </c>
+      <c r="H25" s="1"/>
+      <c r="I25" s="48">
+        <v>447</v>
+      </c>
+      <c r="J25" s="48">
+        <v>52837</v>
+      </c>
+    </row>
+    <row r="26" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="B26" s="46" t="s">
+        <v>495</v>
+      </c>
+      <c r="C26" s="56" t="s">
+        <v>547</v>
+      </c>
+      <c r="D26" s="59" t="s">
+        <v>1051</v>
+      </c>
+      <c r="E26" s="60" t="s">
+        <v>1052</v>
+      </c>
+      <c r="F26" s="60" t="s">
+        <v>1053</v>
+      </c>
+      <c r="G26" s="60" t="s">
+        <v>1054</v>
+      </c>
+      <c r="H26" s="1"/>
+      <c r="I26" s="48">
+        <v>447</v>
+      </c>
+      <c r="J26" s="48">
+        <v>52837</v>
+      </c>
+    </row>
+    <row r="27" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="B27" s="46" t="s">
+        <v>496</v>
+      </c>
+      <c r="C27" s="56" t="s">
+        <v>547</v>
+      </c>
+      <c r="D27" s="59" t="s">
+        <v>1055</v>
+      </c>
+      <c r="E27" s="60" t="s">
+        <v>1056</v>
+      </c>
+      <c r="F27" s="60" t="s">
+        <v>1057</v>
+      </c>
+      <c r="G27" s="60" t="s">
+        <v>1058</v>
+      </c>
+      <c r="H27" s="1"/>
+      <c r="I27" s="48">
+        <v>447</v>
+      </c>
+      <c r="J27" s="48">
+        <v>52837</v>
+      </c>
+    </row>
+    <row r="28" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="B28" s="46" t="s">
+        <v>497</v>
+      </c>
+      <c r="C28" s="56" t="s">
+        <v>547</v>
+      </c>
+      <c r="D28" s="59" t="s">
+        <v>1059</v>
+      </c>
+      <c r="E28" s="60" t="s">
+        <v>1060</v>
+      </c>
+      <c r="F28" s="60" t="s">
+        <v>1061</v>
+      </c>
+      <c r="G28" s="60" t="s">
+        <v>1062</v>
+      </c>
+      <c r="H28" s="1"/>
+      <c r="I28" s="48">
+        <v>373</v>
+      </c>
+      <c r="J28" s="48">
+        <v>43979</v>
+      </c>
+    </row>
+    <row r="29" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="B29" s="49" t="s">
+        <v>498</v>
+      </c>
+      <c r="C29" s="57" t="s">
+        <v>547</v>
+      </c>
+      <c r="D29" s="61" t="s">
+        <v>1063</v>
+      </c>
+      <c r="E29" s="62" t="s">
+        <v>1064</v>
+      </c>
+      <c r="F29" s="62" t="s">
+        <v>1065</v>
+      </c>
+      <c r="G29" s="62" t="s">
+        <v>1066</v>
+      </c>
+      <c r="H29" s="2"/>
+      <c r="I29" s="45">
+        <v>361</v>
+      </c>
+      <c r="J29" s="45">
+        <v>41481</v>
+      </c>
+    </row>
+    <row r="30" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="B30" s="63" t="s">
+        <v>566</v>
+      </c>
+      <c r="C30" s="41"/>
+      <c r="D30" s="42"/>
+      <c r="E30" s="42"/>
+      <c r="F30" s="42"/>
+      <c r="G30" s="42"/>
+      <c r="H30" s="41"/>
+      <c r="I30" s="43"/>
+      <c r="J30" s="43"/>
+    </row>
+    <row r="31" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="B31" s="37" t="s">
+        <v>494</v>
+      </c>
+      <c r="C31" s="64" t="s">
+        <v>566</v>
+      </c>
+      <c r="D31" s="65" t="s">
+        <v>1067</v>
+      </c>
+      <c r="E31" s="66" t="s">
+        <v>1068</v>
+      </c>
+      <c r="F31" s="66" t="s">
+        <v>1069</v>
+      </c>
+      <c r="G31" s="66" t="s">
+        <v>1070</v>
+      </c>
+      <c r="H31" s="38"/>
+      <c r="I31" s="39">
+        <v>219</v>
+      </c>
+      <c r="J31" s="39">
+        <v>52837</v>
+      </c>
+    </row>
+    <row r="32" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="B32" s="37" t="s">
+        <v>495</v>
+      </c>
+      <c r="C32" s="64" t="s">
+        <v>566</v>
+      </c>
+      <c r="D32" s="65" t="s">
+        <v>1071</v>
+      </c>
+      <c r="E32" s="66" t="s">
+        <v>1072</v>
+      </c>
+      <c r="F32" s="66" t="s">
+        <v>1073</v>
+      </c>
+      <c r="G32" s="66" t="s">
+        <v>1074</v>
+      </c>
+      <c r="H32" s="38"/>
+      <c r="I32" s="39">
+        <v>219</v>
+      </c>
+      <c r="J32" s="39">
+        <v>52837</v>
+      </c>
+    </row>
+    <row r="33" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="B33" s="37" t="s">
+        <v>496</v>
+      </c>
+      <c r="C33" s="64" t="s">
+        <v>566</v>
+      </c>
+      <c r="D33" s="65" t="s">
+        <v>1075</v>
+      </c>
+      <c r="E33" s="66" t="s">
+        <v>1076</v>
+      </c>
+      <c r="F33" s="66" t="s">
+        <v>1077</v>
+      </c>
+      <c r="G33" s="66" t="s">
+        <v>1078</v>
+      </c>
+      <c r="H33" s="38"/>
+      <c r="I33" s="39">
+        <v>219</v>
+      </c>
+      <c r="J33" s="39">
+        <v>52837</v>
+      </c>
+    </row>
+    <row r="34" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="B34" s="37" t="s">
+        <v>497</v>
+      </c>
+      <c r="C34" s="64" t="s">
+        <v>566</v>
+      </c>
+      <c r="D34" s="65" t="s">
+        <v>1079</v>
+      </c>
+      <c r="E34" s="66" t="s">
+        <v>1080</v>
+      </c>
+      <c r="F34" s="66" t="s">
+        <v>1081</v>
+      </c>
+      <c r="G34" s="66" t="s">
+        <v>1082</v>
+      </c>
+      <c r="H34" s="38"/>
+      <c r="I34" s="39">
+        <v>181</v>
+      </c>
+      <c r="J34" s="39">
+        <v>43979</v>
+      </c>
+    </row>
+    <row r="35" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="B35" s="40" t="s">
+        <v>498</v>
+      </c>
+      <c r="C35" s="67" t="s">
+        <v>566</v>
+      </c>
+      <c r="D35" s="68" t="s">
+        <v>1083</v>
+      </c>
+      <c r="E35" s="69" t="s">
+        <v>1084</v>
+      </c>
+      <c r="F35" s="69" t="s">
+        <v>1085</v>
+      </c>
+      <c r="G35" s="69" t="s">
+        <v>1086</v>
+      </c>
+      <c r="H35" s="41"/>
+      <c r="I35" s="43">
+        <v>174</v>
+      </c>
+      <c r="J35" s="43">
+        <v>41481</v>
+      </c>
+    </row>
+    <row r="36" spans="2:10" ht="64" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B36" s="93" t="s">
+        <v>580</v>
+      </c>
+      <c r="C36" s="93"/>
+      <c r="D36" s="93"/>
+      <c r="E36" s="93"/>
+      <c r="F36" s="93"/>
+      <c r="G36" s="93"/>
+      <c r="H36" s="93"/>
+      <c r="I36" s="93"/>
+      <c r="J36" s="93"/>
+    </row>
+  </sheetData>
+  <mergeCells count="4">
+    <mergeCell ref="B3:J3"/>
+    <mergeCell ref="D4:G4"/>
+    <mergeCell ref="I4:J4"/>
+    <mergeCell ref="B36:J36"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>